--- a/design/editable/card-sheet.xlsx
+++ b/design/editable/card-sheet.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cards'!$A$1:$G$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Numbers'!$A$1:$H$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Numbers'!$A$1:$H$134</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -590,7 +590,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>How strong card benefits are on each difficulty, in percent. The cards are written for Ascent 7–8 (100%); on easier difficulties every benefit shrinks to this share, and the card text shows the smaller number. Drawbacks and Mythics always stay at full strength.</t>
+          <t>How strong card benefits are on each difficulty, in percent. The cards are written for Ascent 7–8 (100%); a lower strength shrinks every benefit to that share, above 100 amplifies it, and the card text shows the number in play. Drawbacks and Mythics always stay at full strength.</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
-          <t>Sprinting uses 12% more stamina.</t>
+          <t>Sprinting uses 5% more stamina.</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>Take 30% more fall Injury.</t>
+          <t>Take 15% more fall Injury.</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr"/>
@@ -764,11 +764,7 @@
           <t>Cold builds 35% slower while climbing blue ice.</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Warming up takes 10% longer.</t>
-        </is>
-      </c>
+      <c r="F4" s="6" t="inlineStr"/>
       <c r="G4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
@@ -828,7 +824,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Each double jump adds 7.5 Drowsy.</t>
+          <t>Each double jump adds 5 Drowsy.</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr"/>
@@ -890,7 +886,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>Dynamite deals 3 times as much Injury.</t>
+          <t>Dynamite deals 50% more Injury.</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr"/>
@@ -921,7 +917,7 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>All stamina costs are 10% higher.</t>
+          <t>All stamina costs are 5% higher.</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr"/>
@@ -952,7 +948,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>Hunger builds 35% faster.</t>
+          <t>Hunger builds 15% faster.</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr"/>
@@ -978,7 +974,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Press {key} below 20 stamina to recover 25. Cooldown: 5 min.</t>
+          <t>Press {key} below 20 stamina to recover 30. Cooldown: 3 min.</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr"/>
@@ -1010,7 +1006,7 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>Climbing uses 15% more stamina.</t>
+          <t>Climbing uses 5% more stamina.</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr"/>
@@ -1036,12 +1032,12 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Stamina regeneration starts 0.3s sooner.</t>
+          <t>Stamina regeneration starts 0.5s sooner.</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Lose 15 maximum stamina.</t>
+          <t>Lose 5 maximum stamina.</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr"/>
@@ -1103,7 +1099,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Lose 12.5 maximum stamina.</t>
+          <t>Lose 7.5 maximum stamina.</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr"/>
@@ -1129,7 +1125,7 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Climb for 3s straight: climbing uses 35% less stamina for the next 1s.</t>
+          <t>Climb for 2s straight: climbing uses 40% less stamina for the next 2s.</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr"/>
@@ -1161,7 +1157,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Cooked food removes 25% less Hunger.</t>
+          <t>Cooked food removes 10% less Hunger.</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr"/>
@@ -1192,7 +1188,7 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>Cold builds 30% faster.</t>
+          <t>Cold builds 10% faster.</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr"/>
@@ -1223,7 +1219,7 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Heat builds 30% faster.</t>
+          <t>Heat builds 10% faster.</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr"/>
@@ -1254,7 +1250,7 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>Heat and Cold build 25% faster.</t>
+          <t>Heat and Cold build 10% faster.</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr"/>
@@ -1310,11 +1306,7 @@
           <t>New Thorns add 40% less status, rounded to the nearest whole thorn.</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>Removing Thorns takes twice as long.</t>
-        </is>
-      </c>
+      <c r="F22" s="6" t="inlineStr"/>
       <c r="G22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
@@ -1343,7 +1335,7 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Heat builds 15% faster.</t>
+          <t>Heat builds 5% faster.</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr"/>
@@ -1374,7 +1366,7 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>Cold builds 15% faster.</t>
+          <t>Cold builds 5% faster.</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr"/>
@@ -1405,7 +1397,7 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Poison wears off 30% slower.</t>
+          <t>Poison wears off 10% slower.</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr"/>
@@ -1458,7 +1450,7 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Healing items remove 25% more Injury from you.</t>
+          <t>Healing removes 25% more Injury from you.</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr"/>
@@ -1490,7 +1482,7 @@
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>Take 10% more Injury.</t>
+          <t>Take 5% more Injury.</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr"/>
@@ -1516,7 +1508,7 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Press {key} at 35+ Poison, Spores or Drowsy to remove 20 from the highest. Once per biome.</t>
+          <t>Press {key} at 25+ Poison, Spores or Drowsy to remove 25 from the highest. Once per biome.</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr"/>
@@ -1604,11 +1596,7 @@
           <t>Reviving does not add Curse.</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>Take 25% more Injury.</t>
-        </is>
-      </c>
+      <c r="F32" s="6" t="inlineStr"/>
       <c r="G32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1690,12 +1678,12 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Held items weigh 25% less.</t>
+          <t>Held items weigh 45% less.</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>Backpack contents weigh 10% more.</t>
+          <t>Backpack contents weigh 5% more.</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr"/>
@@ -1753,7 +1741,7 @@
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>Uncooked food removes 50% less Hunger.</t>
+          <t>Uncooked food removes 15% less Hunger.</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr"/>
@@ -1784,7 +1772,7 @@
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>Eating cookable food raw adds 7.5 Poison.</t>
+          <t>Eating cookable food raw adds 5 Poison.</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr"/>
@@ -1813,11 +1801,7 @@
           <t>Get one Balloon Bunch at the next campfire. Once per run.</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>All stamina costs are 10% higher.</t>
-        </is>
-      </c>
+      <c r="F39" s="6" t="inlineStr"/>
       <c r="G39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
@@ -1873,7 +1857,7 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>One permanent random penalty: climbing or sprinting cost +15%, Injury +20%, or Hunger buildup +20%.</t>
+          <t>One permanent random penalty: climbing or sprinting cost +10%, Injury +10%, or Hunger buildup +10%. It stays even if you give this card up.</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr"/>
@@ -1899,12 +1883,12 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>You and teammates within 6 m use 15% less climbing stamina.</t>
+          <t>You and teammates within 8 m use 20% less climbing stamina.</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>With no teammate within 6 m, climbing uses 15% more stamina.</t>
+          <t>With no teammate within 8 m, climbing uses 5% more stamina.</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr"/>
@@ -1935,7 +1919,7 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>Healing items used on yourself remove 35% less Injury.</t>
+          <t>Healing items used on yourself remove 15% less Injury.</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr"/>
@@ -1964,11 +1948,7 @@
           <t>Carried scouts weigh 35% less.</t>
         </is>
       </c>
-      <c r="F44" s="6" t="inlineStr">
-        <is>
-          <t>Their paused death timer drains at 15% of normal speed. Already-active timers drain 15% faster.</t>
-        </is>
-      </c>
+      <c r="F44" s="6" t="inlineStr"/>
       <c r="G44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
@@ -1995,11 +1975,7 @@
           <t>Huddling warms you 35% more, from 35% farther away.</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>With no teammate within 6 m, Cold builds 20% faster.</t>
-        </is>
-      </c>
+      <c r="F45" s="6" t="inlineStr"/>
       <c r="G45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
@@ -2055,7 +2031,7 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>Starting a pull costs 10 stamina, once per continuous reach.</t>
+          <t>Starting a pull costs a base 5 stamina, once per continuous reach.</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr"/>
@@ -2086,7 +2062,7 @@
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>You take half the prevented Injury, up to 10 per hit.</t>
+          <t>You take a quarter of the prevented Injury, up to 5 per hit.</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr"/>
@@ -2112,14 +2088,10 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Teammates within 6 m recover stamina 12% faster.</t>
-        </is>
-      </c>
-      <c r="F49" s="6" t="inlineStr">
-        <is>
-          <t>With no teammate within 6 m, all stamina costs are 10% higher.</t>
-        </is>
-      </c>
+          <t>You and teammates within 8 m recover stamina 15% faster.</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr"/>
       <c r="G49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
@@ -2148,7 +2120,7 @@
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>Take 40% more fall Injury.</t>
+          <t>Take 25% more fall Injury.</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr"/>
@@ -2179,7 +2151,7 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>Gain 10 Curse now, then 2 at each later campfire.</t>
+          <t>Gain 5 Curse now, then 1 at each later campfire, up to 10 Curse in total.</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr"/>
@@ -2210,7 +2182,7 @@
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>A failed roll adds 20 Injury instead.</t>
+          <t>A failed roll adds 7.5 Injury instead.</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr"/>
@@ -2272,7 +2244,7 @@
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>Stopping after a boost adds 7.5 Drowsy, at most once every 30s.</t>
+          <t>Stopping after a boost adds 2.5 Drowsy, at most once every 60s.</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr"/>
@@ -2330,7 +2302,7 @@
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>Take 50% more Injury.</t>
+          <t>Take 25% more Injury.</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr"/>
@@ -2361,7 +2333,7 @@
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>With a backpack: sprint 15% slower.</t>
+          <t>With a backpack: sprint 5% slower.</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr"/>
@@ -2387,12 +2359,12 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Immediately gain 1 random bonus card, Common to Rare.</t>
+          <t>Immediately gain 2 random bonus cards, Common to Rare.</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>Gain 10 Curse. Your next campfire offers only 1 card.</t>
+          <t>Gain 5 Curse. Your next campfire offers only 2 cards.</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr"/>
@@ -2477,7 +2449,7 @@
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>Lose 15 maximum stamina. The revival leaves 40 Injury.</t>
+          <t>The revival leaves 40 Injury.</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr"/>
@@ -2503,14 +2475,10 @@
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>Petrification builds 35% slower.</t>
-        </is>
-      </c>
-      <c r="F62" s="6" t="inlineStr">
-        <is>
-          <t>Take 15% more fall Injury.</t>
-        </is>
-      </c>
+          <t>Petrification builds 50% slower.</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr"/>
       <c r="G62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
@@ -2539,7 +2507,7 @@
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>Gain 5 Curse at each later campfire.</t>
+          <t>Gain 5 Curse when the sacrifice is made.</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr"/>
@@ -2623,7 +2591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H141"/>
+  <dimension ref="A1:H134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2733,7 +2701,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -2801,7 +2769,7 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
@@ -2853,36 +2821,36 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>To The Bone</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>Cold decay</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr"/>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="A7" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Pitonless Pit Stop</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Climb speed</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>-9.0909</v>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H7" s="12" t="inlineStr">
-        <is>
-          <t>mod:1</t>
+        <v>-30</v>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -2897,56 +2865,52 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Climb speed</t>
+          <t>Stamina recovered per second</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="E8" s="5" t="inlineStr"/>
       <c r="F8" s="13" t="n">
-        <v>-30</v>
+        <v>4</v>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>points</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>mod:0</t>
+          <t>param:regenPerSecond</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Pitonless Pit Stop</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Stamina recovered per second</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="inlineStr"/>
+      <c r="A9" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Bing BOING</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Double jump cooldown</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr"/>
+      <c r="E9" s="12" t="inlineStr"/>
       <c r="F9" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>param:regenPerSecond</t>
+        <v>15</v>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>seconds</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>param:cooldown</t>
         </is>
       </c>
     </row>
@@ -2961,52 +2925,56 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Double jump cooldown</t>
+          <t>Drowsy added</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr"/>
       <c r="E10" s="12" t="inlineStr"/>
       <c r="F10" s="13" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>seconds</t>
+          <t>points</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>param:cooldown</t>
+          <t>param:drowsy</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Bing BOING</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>Drowsy added</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr"/>
-      <c r="E11" s="12" t="inlineStr"/>
+      <c r="A11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Energy Drink Overdose</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Climb speed</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F11" s="13" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>param:drowsy</t>
+        <v>30</v>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -3021,7 +2989,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Climb speed</t>
+          <t>Climbing stamina cost</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr"/>
@@ -3031,7 +2999,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
@@ -3040,41 +3008,41 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
+          <t>mod:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Tenderfoot Insurance</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Fall Injury</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr"/>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>-25</v>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
           <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Energy Drink Overdose</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Climbing stamina cost</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>mod:1</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3057,7 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Fall Injury</t>
+          <t>Dynamite Injury</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr"/>
@@ -3099,7 +3067,7 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>-25</v>
+        <v>50</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -3108,41 +3076,41 @@
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
+          <t>mod:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Daddy</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Wall-grab reach</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
           <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>Tenderfoot Insurance</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>Dynamite Injury</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr"/>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>200</v>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H15" s="12" t="inlineStr">
-        <is>
-          <t>mod:1</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3125,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Wall-grab reach</t>
+          <t>All stamina costs</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr"/>
@@ -3167,7 +3135,7 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
@@ -3176,41 +3144,41 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
+          <t>mod:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Cookie Addiction</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Max stamina</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr"/>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>stamina points</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
           <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Daddy</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>All stamina costs</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>mod:1</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3193,7 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Max stamina</t>
+          <t>Hunger build-up</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr"/>
@@ -3235,50 +3203,46 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>stamina points</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>mod:0</t>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>Cookie Addiction</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>Hunger build-up</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr"/>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="A19" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Nic of Time</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Works below this much stamina</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
       <c r="F19" s="13" t="n">
-        <v>35</v>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
-          <t>mod:1</t>
+        <v>20</v>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>param:threshold</t>
         </is>
       </c>
     </row>
@@ -3293,13 +3257,13 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Works below this much stamina</t>
+          <t>Stamina recovered</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr"/>
       <c r="E20" s="5" t="inlineStr"/>
       <c r="F20" s="13" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
@@ -3308,7 +3272,7 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>param:threshold</t>
+          <t>param:restore</t>
         </is>
       </c>
     </row>
@@ -3323,52 +3287,56 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Stamina recovered</t>
+          <t>Cooldown</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr"/>
       <c r="E21" s="5" t="inlineStr"/>
       <c r="F21" s="13" t="n">
-        <v>25</v>
+        <v>180</v>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>seconds</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>param:restore</t>
+          <t>param:cooldown</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Nic of Time</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Cooldown</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
+      <c r="A22" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Hasty Badge Training</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Sprint stamina cost</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr"/>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F22" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>seconds</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>param:cooldown</t>
+        <v>-15</v>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3351,7 @@
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Sprint stamina cost</t>
+          <t>Climbing stamina cost</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr"/>
@@ -3393,7 +3361,7 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>-15</v>
+        <v>5</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -3402,41 +3370,41 @@
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
+          <t>mod:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Stamina regen delay</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>seconds (negative = sooner)</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
           <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>Hasty Badge Training</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>Climbing stamina cost</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr"/>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F24" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="G24" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H24" s="12" t="inlineStr">
-        <is>
-          <t>mod:1</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3419,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Stamina regen delay</t>
+          <t>Max stamina</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr"/>
@@ -3461,86 +3429,86 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>-0.3</v>
+        <v>-5</v>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>seconds (negative = sooner)</t>
+          <t>stamina points</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
+          <t>mod:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>Meditation</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>Stamina regen rate</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>while you crouch and stay still</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
           <t>mod:0</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Max stamina</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr"/>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F26" s="13" t="n">
-        <v>-15</v>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>stamina points</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>mod:1</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
-      <c r="A27" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>Meditation</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>Stamina regen rate</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>while you crouch and stay still</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="A27" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>I'm getting Scoutmastered</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Sprint speed</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>35</v>
-      </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H27" s="12" t="inlineStr">
+        <v>25</v>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>mod:0</t>
         </is>
@@ -3557,7 +3525,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Sprint speed</t>
+          <t>Max stamina</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr"/>
@@ -3567,50 +3535,54 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>25</v>
+        <v>-7.5</v>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>stamina points</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
+          <t>mod:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Endurance Badge</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>Climbing stamina cost</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>while your climbing boost is on</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>-40</v>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
           <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>I'm getting Scoutmastered</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Max stamina</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F29" s="13" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>stamina points</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>mod:1</t>
         </is>
       </c>
     </row>
@@ -3625,30 +3597,22 @@
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>Climbing stamina cost</t>
-        </is>
-      </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>while your climbing boost is on</t>
-        </is>
-      </c>
-      <c r="E30" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+          <t>Climbing time before the boost</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr"/>
+      <c r="E30" s="12" t="inlineStr"/>
       <c r="F30" s="13" t="n">
-        <v>-35</v>
+        <v>2</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>seconds</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>mod:0</t>
+          <t>param:buildup</t>
         </is>
       </c>
     </row>
@@ -3663,13 +3627,13 @@
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Climbing time before the boost</t>
+          <t>Boost length</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr"/>
       <c r="E31" s="12" t="inlineStr"/>
       <c r="F31" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -3678,69 +3642,73 @@
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>param:buildup</t>
+          <t>param:boost</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="B32" s="12" t="inlineStr">
-        <is>
-          <t>Endurance Badge</t>
-        </is>
-      </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>Boost length</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="inlineStr"/>
-      <c r="E32" s="12" t="inlineStr"/>
+      <c r="A32" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Marshmallow Morale</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Hunger removed by cooked food</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F32" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="12" t="inlineStr">
-        <is>
-          <t>seconds</t>
-        </is>
-      </c>
-      <c r="H32" s="12" t="inlineStr">
-        <is>
-          <t>param:boost</t>
+        <v>-10</v>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>Marshmallow Morale</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Hunger removed by cooked food</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr"/>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="A33" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>Cool, Calm, and Collected.</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>Heat build-up</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr"/>
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>-25</v>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
+        <v>-50</v>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="inlineStr">
         <is>
           <t>mod:0</t>
         </is>
@@ -3757,7 +3725,7 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>Heat build-up</t>
+          <t>Cold build-up</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr"/>
@@ -3767,50 +3735,50 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>mod:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Just hot.</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Cold build-up</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr"/>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="n">
         <v>-50</v>
       </c>
-      <c r="G34" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H34" s="12" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>Cool, Calm, and Collected.</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>Cold build-up</t>
-        </is>
-      </c>
-      <c r="D35" s="12" t="inlineStr"/>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F35" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="G35" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H35" s="12" t="inlineStr">
-        <is>
-          <t>mod:1</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3793,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Cold build-up</t>
+          <t>Heat build-up</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr"/>
@@ -3835,7 +3803,7 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>-50</v>
+        <v>10</v>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
@@ -3844,41 +3812,41 @@
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
+          <t>mod:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>Antidote Enthusiast</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>Poison build-up</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr"/>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>-35</v>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="inlineStr">
+        <is>
           <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Just hot.</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Heat build-up</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr"/>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F37" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>mod:1</t>
         </is>
       </c>
     </row>
@@ -3893,7 +3861,7 @@
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>Poison build-up</t>
+          <t>Heat build-up</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr"/>
@@ -3903,7 +3871,7 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>-35</v>
+        <v>10</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -3912,7 +3880,7 @@
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>mod:0</t>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3895,7 @@
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Heat build-up</t>
+          <t>Cold build-up</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr"/>
@@ -3937,7 +3905,7 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
@@ -3946,162 +3914,162 @@
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
+          <t>mod:2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>ROOTS Survivor</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Spores build-up</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr"/>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>-35</v>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>Cactus? What Cactus?</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>Thorns build-up</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr"/>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>-40</v>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Aloe</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Heat decay</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr"/>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Aloe</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Heat build-up</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr"/>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F43" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
           <t>mod:1</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="B40" s="12" t="inlineStr">
-        <is>
-          <t>Antidote Enthusiast</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>Cold build-up</t>
-        </is>
-      </c>
-      <c r="D40" s="12" t="inlineStr"/>
-      <c r="E40" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F40" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="G40" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H40" s="12" t="inlineStr">
-        <is>
-          <t>mod:2</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>ROOTS Survivor</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>Spores build-up</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr"/>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F41" s="13" t="n">
-        <v>-35</v>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="B42" s="12" t="inlineStr">
-        <is>
-          <t>Cactus? What Cactus?</t>
-        </is>
-      </c>
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>Thorns build-up</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="inlineStr"/>
-      <c r="E42" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F42" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="G42" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H42" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>Cactus? What Cactus?</t>
-        </is>
-      </c>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>Thorn removal time</t>
-        </is>
-      </c>
-      <c r="D43" s="12" t="inlineStr"/>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F43" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="G43" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H43" s="12" t="inlineStr">
-        <is>
-          <t>mod:1</t>
-        </is>
-      </c>
-    </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>Aloe</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>Heat decay</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr"/>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="A44" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>Heat Pack</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>Cold decay</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr"/>
+      <c r="E44" s="12" t="inlineStr">
         <is>
           <t>You</t>
         </is>
@@ -4109,188 +4077,180 @@
       <c r="F44" s="13" t="n">
         <v>60</v>
       </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H44" s="5" t="inlineStr">
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H44" s="12" t="inlineStr">
         <is>
           <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>Aloe</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>Heat build-up</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr"/>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="A45" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>Heat Pack</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>Cold build-up</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr"/>
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H45" s="12" t="inlineStr">
         <is>
           <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="B46" s="12" t="inlineStr">
-        <is>
-          <t>Heat Pack</t>
-        </is>
-      </c>
-      <c r="C46" s="12" t="inlineStr">
-        <is>
-          <t>Cold decay</t>
-        </is>
-      </c>
-      <c r="D46" s="12" t="inlineStr"/>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="A46" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Fartberry Fitness</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Climbing stamina cost</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>while you have more than 20 Poison</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H46" s="12" t="inlineStr">
+        <v>-40</v>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
         <is>
           <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="B47" s="12" t="inlineStr">
-        <is>
-          <t>Heat Pack</t>
-        </is>
-      </c>
-      <c r="C47" s="12" t="inlineStr">
-        <is>
-          <t>Cold build-up</t>
-        </is>
-      </c>
-      <c r="D47" s="12" t="inlineStr"/>
-      <c r="E47" s="12" t="inlineStr">
+      <c r="A47" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Fartberry Fitness</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Poison decay</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr"/>
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="G47" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H47" s="12" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
         <is>
           <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>Fartberry Fitness</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>Climbing stamina cost</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>while you have more than 20 Poison</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="A48" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>BingBong</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>Time between powers</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="inlineStr"/>
+      <c r="E48" s="12" t="inlineStr"/>
       <c r="F48" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
+        <v>300</v>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>seconds</t>
+        </is>
+      </c>
+      <c r="H48" s="12" t="inlineStr">
+        <is>
+          <t>param:interval</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>Fartberry Fitness</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>Poison decay</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr"/>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="A49" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>BingBong</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>Power length</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr"/>
+      <c r="E49" s="12" t="inlineStr"/>
       <c r="F49" s="13" t="n">
-        <v>-30</v>
-      </c>
-      <c r="G49" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>mod:1</t>
+        <v>20</v>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>seconds</t>
+        </is>
+      </c>
+      <c r="H49" s="12" t="inlineStr">
+        <is>
+          <t>param:duration</t>
         </is>
       </c>
     </row>
@@ -4305,116 +4265,132 @@
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>Time between powers</t>
+          <t>Low Gravity strength (the mushroom is 3)</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr"/>
       <c r="E50" s="12" t="inlineStr"/>
       <c r="F50" s="13" t="n">
-        <v>300</v>
+        <v>3</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
-          <t>seconds</t>
+          <t>strength</t>
         </is>
       </c>
       <c r="H50" s="12" t="inlineStr">
         <is>
-          <t>param:interval</t>
+          <t>param:lowGravity</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="12" t="n">
+      <c r="A51" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Injury healed by items (received)</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr"/>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F51" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="B51" s="12" t="inlineStr">
-        <is>
-          <t>BingBong</t>
-        </is>
-      </c>
-      <c r="C51" s="12" t="inlineStr">
-        <is>
-          <t>Power length</t>
-        </is>
-      </c>
-      <c r="D51" s="12" t="inlineStr"/>
-      <c r="E51" s="12" t="inlineStr"/>
-      <c r="F51" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>seconds</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>param:duration</t>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>BingBong</t>
+          <t>Walk It Off</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>Low Gravity strength (the mushroom is 3)</t>
-        </is>
-      </c>
-      <c r="D52" s="12" t="inlineStr"/>
-      <c r="E52" s="12" t="inlineStr"/>
+          <t>Climbing stamina cost</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>while you have 20+ Injury</t>
+        </is>
+      </c>
+      <c r="E52" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F52" s="13" t="n">
-        <v>3</v>
+        <v>-25</v>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
-          <t>strength</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H52" s="12" t="inlineStr">
         <is>
-          <t>param:lowGravity</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>Injury healed by items (received)</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr"/>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="A53" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>Walk It Off</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>Sprint stamina cost</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>while you have 20+ Injury</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
+        <v>-25</v>
+      </c>
+      <c r="G53" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H53" s="12" t="inlineStr">
+        <is>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
@@ -4429,21 +4405,17 @@
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>Climbing stamina cost</t>
-        </is>
-      </c>
-      <c r="D54" s="12" t="inlineStr">
-        <is>
-          <t>while you have 20+ Injury</t>
-        </is>
-      </c>
+          <t>All Injury</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr"/>
       <c r="E54" s="12" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>-25</v>
+        <v>5</v>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
@@ -4452,188 +4424,180 @@
       </c>
       <c r="H54" s="12" t="inlineStr">
         <is>
-          <t>mod:0</t>
+          <t>mod:2</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="B55" s="12" t="inlineStr">
-        <is>
-          <t>Walk It Off</t>
-        </is>
-      </c>
-      <c r="C55" s="12" t="inlineStr">
-        <is>
-          <t>Sprint stamina cost</t>
-        </is>
-      </c>
-      <c r="D55" s="12" t="inlineStr">
-        <is>
-          <t>while you have 20+ Injury</t>
-        </is>
-      </c>
-      <c r="E55" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="A55" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Discount Cure-All</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Needs at least this much of the status</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr"/>
+      <c r="E55" s="5" t="inlineStr"/>
       <c r="F55" s="13" t="n">
-        <v>-25</v>
-      </c>
-      <c r="G55" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H55" s="12" t="inlineStr">
-        <is>
-          <t>mod:1</t>
+        <v>25</v>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>param:threshold</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="B56" s="12" t="inlineStr">
-        <is>
-          <t>Walk It Off</t>
-        </is>
-      </c>
-      <c r="C56" s="12" t="inlineStr">
-        <is>
-          <t>All Injury</t>
-        </is>
-      </c>
-      <c r="D56" s="12" t="inlineStr"/>
-      <c r="E56" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="A56" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Discount Cure-All</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Status removed</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr"/>
+      <c r="E56" s="5" t="inlineStr"/>
       <c r="F56" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G56" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H56" s="12" t="inlineStr">
-        <is>
-          <t>mod:2</t>
+        <v>25</v>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>param:remove</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Discount Cure-All</t>
+          <t>Gourmand's Gut</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Needs at least this much of the status</t>
+          <t>Hunger removed by food</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr"/>
-      <c r="E57" s="5" t="inlineStr"/>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F57" s="13" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>param:threshold</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>Discount Cure-All</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>Status removed</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr"/>
-      <c r="E58" s="5" t="inlineStr"/>
+      <c r="A58" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>Book of Broken Bones</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>Curse added by revival</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="inlineStr"/>
+      <c r="E58" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F58" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H58" s="5" t="inlineStr">
-        <is>
-          <t>param:remove</t>
+        <v>-100</v>
+      </c>
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H58" s="12" t="inlineStr">
+        <is>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Gourmand's Gut</t>
+          <t>Mini Tenacity</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Hunger removed by food</t>
+          <t>Extra status removed</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr"/>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="E59" s="5" t="inlineStr"/>
       <c r="F59" s="13" t="n">
-        <v>20</v>
+        <v>7.5</v>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>points</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>mod:0</t>
+          <t>param:bonus</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B60" s="12" t="inlineStr">
         <is>
-          <t>Book of Broken Bones</t>
+          <t>Bing Bong's Baggage</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>Curse added by revival</t>
+          <t>All carried weight</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr"/>
@@ -4643,7 +4607,7 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
@@ -4657,81 +4621,85 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="B61" s="12" t="inlineStr">
-        <is>
-          <t>Book of Broken Bones</t>
-        </is>
-      </c>
-      <c r="C61" s="12" t="inlineStr">
-        <is>
-          <t>All Injury</t>
-        </is>
-      </c>
-      <c r="D61" s="12" t="inlineStr"/>
-      <c r="E61" s="12" t="inlineStr">
+      <c r="A61" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Carry-On Only</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Held item weight</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr"/>
+      <c r="E61" s="5" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="G61" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H61" s="12" t="inlineStr">
-        <is>
-          <t>mod:1</t>
+        <v>-45</v>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Mini Tenacity</t>
+          <t>Carry-On Only</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Extra status removed</t>
+          <t>Backpack content weight</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr"/>
-      <c r="E62" s="5" t="inlineStr"/>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F62" s="13" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>param:bonus</t>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>Bing Bong's Baggage</t>
+          <t>Idol Hands</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>All carried weight</t>
+          <t>Held item weight</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr"/>
@@ -4741,7 +4709,7 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>-50</v>
+        <v>-35</v>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
@@ -4756,16 +4724,16 @@
     </row>
     <row r="64">
       <c r="A64" s="5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Carry-On Only</t>
+          <t>Cook It, Keep It</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Held item weight</t>
+          <t>Uncooked food nutrition</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr"/>
@@ -4775,7 +4743,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>-25</v>
+        <v>-15</v>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
@@ -4789,191 +4757,175 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>Carry-On Only</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>Backpack content weight</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr"/>
-      <c r="E65" s="5" t="inlineStr">
+      <c r="A65" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>Cooking Badge Deluxe</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>Hunger removed by cooked food</t>
+        </is>
+      </c>
+      <c r="D65" s="12" t="inlineStr"/>
+      <c r="E65" s="12" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H65" s="5" t="inlineStr">
-        <is>
-          <t>mod:1</t>
+        <v>50</v>
+      </c>
+      <c r="G65" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H65" s="12" t="inlineStr">
+        <is>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B66" s="12" t="inlineStr">
         <is>
-          <t>Idol Hands</t>
+          <t>Cooking Badge Deluxe</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>Held item weight</t>
+          <t>Poison added</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr"/>
-      <c r="E66" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="E66" s="12" t="inlineStr"/>
       <c r="F66" s="13" t="n">
-        <v>-35</v>
+        <v>5</v>
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>points</t>
         </is>
       </c>
       <c r="H66" s="12" t="inlineStr">
         <is>
-          <t>mod:0</t>
+          <t>param:poison</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Cook It, Keep It</t>
+          <t>Clown Luggage Special</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Uncooked food nutrition</t>
+          <t>Bonus cards</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr"/>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="E67" s="5" t="inlineStr"/>
       <c r="F67" s="13" t="n">
-        <v>-50</v>
+        <v>2</v>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>cards</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>mod:0</t>
+          <t>param:bonusCards</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="B68" s="12" t="inlineStr">
-        <is>
-          <t>Cooking Badge Deluxe</t>
-        </is>
-      </c>
-      <c r="C68" s="12" t="inlineStr">
-        <is>
-          <t>Hunger removed by cooked food</t>
-        </is>
-      </c>
-      <c r="D68" s="12" t="inlineStr"/>
-      <c r="E68" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="A68" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>Clown Luggage Special</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>Possible penalty: climbing stamina cost</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr"/>
+      <c r="E68" s="5" t="inlineStr"/>
       <c r="F68" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="G68" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H68" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
+        <v>10</v>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>param:climbPenalty</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="B69" s="12" t="inlineStr">
-        <is>
-          <t>Cooking Badge Deluxe</t>
-        </is>
-      </c>
-      <c r="C69" s="12" t="inlineStr">
-        <is>
-          <t>Poison added</t>
-        </is>
-      </c>
-      <c r="D69" s="12" t="inlineStr"/>
-      <c r="E69" s="12" t="inlineStr"/>
+      <c r="A69" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Clown Luggage Special</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Possible penalty: sprint stamina cost</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr"/>
+      <c r="E69" s="5" t="inlineStr"/>
       <c r="F69" s="13" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G69" s="12" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H69" s="12" t="inlineStr">
-        <is>
-          <t>param:poison</t>
+        <v>10</v>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>param:sprintPenalty</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Balright</t>
+          <t>Clown Luggage Special</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>All stamina costs</t>
+          <t>Possible penalty: all Injury</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr"/>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="E70" s="5" t="inlineStr"/>
       <c r="F70" s="13" t="n">
         <v>10</v>
       </c>
@@ -4984,7 +4936,7 @@
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>mod:0</t>
+          <t>param:injuryPenalty</t>
         </is>
       </c>
     </row>
@@ -4999,199 +4951,215 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Bonus cards</t>
+          <t>Possible penalty: Hunger build-up</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr"/>
       <c r="E71" s="5" t="inlineStr"/>
       <c r="F71" s="13" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>cards</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>param:bonusCards</t>
+          <t>param:hungerPenalty</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>Clown Luggage Special</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>Possible penalty: climbing stamina cost</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr"/>
-      <c r="E72" s="5" t="inlineStr"/>
+      <c r="A72" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="B72" s="12" t="inlineStr">
+        <is>
+          <t>Rule Zero</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="inlineStr">
+        <is>
+          <t>Climbing stamina cost</t>
+        </is>
+      </c>
+      <c r="D72" s="12" t="inlineStr"/>
+      <c r="E72" s="12" t="inlineStr">
+        <is>
+          <t>Teammates within 8 m</t>
+        </is>
+      </c>
       <c r="F72" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H72" s="5" t="inlineStr">
-        <is>
-          <t>param:climbPenalty</t>
+        <v>-20</v>
+      </c>
+      <c r="G72" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H72" s="12" t="inlineStr">
+        <is>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>Clown Luggage Special</t>
-        </is>
-      </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>Possible penalty: sprint stamina cost</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="inlineStr"/>
-      <c r="E73" s="5" t="inlineStr"/>
+      <c r="A73" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="B73" s="12" t="inlineStr">
+        <is>
+          <t>Rule Zero</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>Climbing stamina cost</t>
+        </is>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>while a teammate is near you</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F73" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H73" s="5" t="inlineStr">
-        <is>
-          <t>param:sprintPenalty</t>
+        <v>-20</v>
+      </c>
+      <c r="G73" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H73" s="12" t="inlineStr">
+        <is>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>Clown Luggage Special</t>
-        </is>
-      </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>Possible penalty: all Injury</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr"/>
-      <c r="E74" s="5" t="inlineStr"/>
+      <c r="A74" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="B74" s="12" t="inlineStr">
+        <is>
+          <t>Rule Zero</t>
+        </is>
+      </c>
+      <c r="C74" s="12" t="inlineStr">
+        <is>
+          <t>Climbing stamina cost</t>
+        </is>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>while no teammate is near you</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F74" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="G74" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H74" s="5" t="inlineStr">
-        <is>
-          <t>param:injuryPenalty</t>
+        <v>5</v>
+      </c>
+      <c r="G74" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H74" s="12" t="inlineStr">
+        <is>
+          <t>mod:2</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>Clown Luggage Special</t>
-        </is>
-      </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>Possible penalty: Hunger build-up</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="inlineStr"/>
-      <c r="E75" s="5" t="inlineStr"/>
+      <c r="A75" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="B75" s="12" t="inlineStr">
+        <is>
+          <t>Rule Zero</t>
+        </is>
+      </c>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="inlineStr"/>
+      <c r="E75" s="12" t="inlineStr"/>
       <c r="F75" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="G75" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t>param:hungerPenalty</t>
+        <v>8</v>
+      </c>
+      <c r="G75" s="12" t="inlineStr">
+        <is>
+          <t>metres</t>
+        </is>
+      </c>
+      <c r="H75" s="12" t="inlineStr">
+        <is>
+          <t>param:radius</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="B76" s="12" t="inlineStr">
-        <is>
-          <t>Rule Zero</t>
-        </is>
-      </c>
-      <c r="C76" s="12" t="inlineStr">
-        <is>
-          <t>Climbing stamina cost</t>
-        </is>
-      </c>
-      <c r="D76" s="12" t="inlineStr"/>
-      <c r="E76" s="12" t="inlineStr">
-        <is>
-          <t>Teammates within 6 m</t>
+      <c r="A76" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>First Aid Badge</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Injury healed by items (given to teammates)</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr"/>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>-15</v>
-      </c>
-      <c r="G76" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H76" s="12" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
         <is>
           <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="B77" s="12" t="inlineStr">
-        <is>
-          <t>Rule Zero</t>
-        </is>
-      </c>
-      <c r="C77" s="12" t="inlineStr">
-        <is>
-          <t>Climbing stamina cost</t>
-        </is>
-      </c>
-      <c r="D77" s="12" t="inlineStr">
-        <is>
-          <t>while a teammate is near you</t>
-        </is>
-      </c>
-      <c r="E77" s="12" t="inlineStr">
+      <c r="A77" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>First Aid Badge</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Injury healed by items (used on yourself)</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr"/>
+      <c r="E77" s="5" t="inlineStr">
         <is>
           <t>You</t>
         </is>
@@ -5199,12 +5167,12 @@
       <c r="F77" s="13" t="n">
         <v>-15</v>
       </c>
-      <c r="G77" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H77" s="12" t="inlineStr">
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
         <is>
           <t>mod:1</t>
         </is>
@@ -5212,30 +5180,26 @@
     </row>
     <row r="78">
       <c r="A78" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B78" s="12" t="inlineStr">
         <is>
-          <t>Rule Zero</t>
+          <t>Human Carry-On</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>Climbing stamina cost</t>
-        </is>
-      </c>
-      <c r="D78" s="12" t="inlineStr">
-        <is>
-          <t>while no teammate is near you</t>
-        </is>
-      </c>
+          <t>Carried scout weight</t>
+        </is>
+      </c>
+      <c r="D78" s="12" t="inlineStr"/>
       <c r="E78" s="12" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>15</v>
+        <v>-35</v>
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
@@ -5244,86 +5208,86 @@
       </c>
       <c r="H78" s="12" t="inlineStr">
         <is>
-          <t>mod:2</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="B79" s="12" t="inlineStr">
-        <is>
-          <t>Rule Zero</t>
-        </is>
-      </c>
-      <c r="C79" s="12" t="inlineStr">
-        <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="D79" s="12" t="inlineStr"/>
-      <c r="E79" s="12" t="inlineStr"/>
+      <c r="A79" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Happy Camper Huddle</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Huddle radius and cold removal</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr"/>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F79" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="G79" s="12" t="inlineStr">
-        <is>
-          <t>metres</t>
-        </is>
-      </c>
-      <c r="H79" s="12" t="inlineStr">
-        <is>
-          <t>param:radius</t>
+        <v>35</v>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="B80" s="5" t="inlineStr">
-        <is>
-          <t>First Aid Badge</t>
-        </is>
-      </c>
-      <c r="C80" s="5" t="inlineStr">
-        <is>
-          <t>Injury healed by items (given to teammates)</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr"/>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="A80" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="B80" s="12" t="inlineStr">
+        <is>
+          <t>Otto-Matic Clutch</t>
+        </is>
+      </c>
+      <c r="C80" s="12" t="inlineStr">
+        <is>
+          <t>Yellow stamina for both scouts</t>
+        </is>
+      </c>
+      <c r="D80" s="12" t="inlineStr"/>
+      <c r="E80" s="12" t="inlineStr"/>
       <c r="F80" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="G80" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H80" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
+        <v>100</v>
+      </c>
+      <c r="G80" s="12" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H80" s="12" t="inlineStr">
+        <is>
+          <t>param:bonus</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>First Aid Badge</t>
+          <t>You're alright, you're alright</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Injury healed by items (used on yourself)</t>
+          <t>Helping-hand reach</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr"/>
@@ -5333,7 +5297,7 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>-35</v>
+        <v>30</v>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
@@ -5342,232 +5306,224 @@
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>mod:1</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="B82" s="12" t="inlineStr">
-        <is>
-          <t>Human Carry-On</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="inlineStr">
-        <is>
-          <t>Carried scout weight</t>
-        </is>
-      </c>
-      <c r="D82" s="12" t="inlineStr"/>
-      <c r="E82" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="A82" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>You're alright, you're alright</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>Stamina cost to start a pull</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr"/>
+      <c r="E82" s="5" t="inlineStr"/>
       <c r="F82" s="13" t="n">
-        <v>-35</v>
-      </c>
-      <c r="G82" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H82" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
+        <v>5</v>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>param:stamina</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>Human Carry-On</t>
+          <t>Take One for the Troop</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>Carried scout death timer</t>
+          <t>All Injury</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr"/>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Teammates within 6 m</t>
         </is>
       </c>
       <c r="F83" s="13" t="n">
+        <v>-30</v>
+      </c>
+      <c r="G83" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H83" s="12" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="B84" s="12" t="inlineStr">
+        <is>
+          <t>Take One for the Troop</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="D84" s="12" t="inlineStr"/>
+      <c r="E84" s="12" t="inlineStr"/>
+      <c r="F84" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G84" s="12" t="inlineStr">
+        <is>
+          <t>metres</t>
+        </is>
+      </c>
+      <c r="H84" s="12" t="inlineStr">
+        <is>
+          <t>param:radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="B85" s="12" t="inlineStr">
+        <is>
+          <t>Take One for the Troop</t>
+        </is>
+      </c>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>Share of the prevented Injury you take</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="inlineStr"/>
+      <c r="E85" s="12" t="inlineStr"/>
+      <c r="F85" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G85" s="12" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H85" s="12" t="inlineStr">
+        <is>
+          <t>param:absorb</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="B86" s="12" t="inlineStr">
+        <is>
+          <t>Take One for the Troop</t>
+        </is>
+      </c>
+      <c r="C86" s="12" t="inlineStr">
+        <is>
+          <t>Most Injury you take per hit</t>
+        </is>
+      </c>
+      <c r="D86" s="12" t="inlineStr"/>
+      <c r="E86" s="12" t="inlineStr"/>
+      <c r="F86" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G86" s="12" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H86" s="12" t="inlineStr">
+        <is>
+          <t>param:cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>Friendship Bugle Choir</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Stamina regen rate</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr"/>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>Teammates within 8 m</t>
+        </is>
+      </c>
+      <c r="F87" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="G83" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H83" s="12" t="inlineStr">
-        <is>
-          <t>mod:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>Happy Camper Huddle</t>
-        </is>
-      </c>
-      <c r="C84" s="5" t="inlineStr">
-        <is>
-          <t>Huddle radius and cold removal</t>
-        </is>
-      </c>
-      <c r="D84" s="5" t="inlineStr"/>
-      <c r="E84" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F84" s="13" t="n">
-        <v>35</v>
-      </c>
-      <c r="G84" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H84" s="5" t="inlineStr">
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
         <is>
           <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="B85" s="5" t="inlineStr">
-        <is>
-          <t>Happy Camper Huddle</t>
-        </is>
-      </c>
-      <c r="C85" s="5" t="inlineStr">
-        <is>
-          <t>Cold build-up</t>
-        </is>
-      </c>
-      <c r="D85" s="5" t="inlineStr">
-        <is>
-          <t>while no teammate is near you</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F85" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="G85" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H85" s="5" t="inlineStr">
-        <is>
-          <t>mod:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="B86" s="5" t="inlineStr">
-        <is>
-          <t>Happy Camper Huddle</t>
-        </is>
-      </c>
-      <c r="C86" s="5" t="inlineStr">
-        <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="D86" s="5" t="inlineStr"/>
-      <c r="E86" s="5" t="inlineStr"/>
-      <c r="F86" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="G86" s="5" t="inlineStr">
-        <is>
-          <t>metres</t>
-        </is>
-      </c>
-      <c r="H86" s="5" t="inlineStr">
-        <is>
-          <t>param:radius</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="B87" s="12" t="inlineStr">
-        <is>
-          <t>Otto-Matic Clutch</t>
-        </is>
-      </c>
-      <c r="C87" s="12" t="inlineStr">
-        <is>
-          <t>Yellow stamina for both scouts</t>
-        </is>
-      </c>
-      <c r="D87" s="12" t="inlineStr"/>
-      <c r="E87" s="12" t="inlineStr"/>
-      <c r="F87" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="G87" s="12" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H87" s="12" t="inlineStr">
-        <is>
-          <t>param:bonus</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>You're alright, you're alright</t>
+          <t>Friendship Bugle Choir</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Helping-hand reach</t>
-        </is>
-      </c>
-      <c r="D88" s="5" t="inlineStr"/>
+          <t>Stamina regen rate</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>while a teammate is near you</t>
+        </is>
+      </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
@@ -5576,62 +5532,62 @@
       </c>
       <c r="H88" s="5" t="inlineStr">
         <is>
-          <t>mod:0</t>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>You're alright, you're alright</t>
+          <t>Friendship Bugle Choir</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Stamina cost to start a pull</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr"/>
       <c r="E89" s="5" t="inlineStr"/>
       <c r="F89" s="13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>metres</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>param:stamina</t>
+          <t>param:radius</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B90" s="12" t="inlineStr">
         <is>
-          <t>Take One for the Troop</t>
+          <t>Scout Cannon Legs</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>All Injury</t>
+          <t>Sprint speed</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr"/>
       <c r="E90" s="12" t="inlineStr">
         <is>
-          <t>Teammates within 6 m</t>
+          <t>You</t>
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>-30</v>
+        <v>35</v>
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
@@ -5646,242 +5602,234 @@
     </row>
     <row r="91">
       <c r="A91" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>Take One for the Troop</t>
+          <t>Scout Cannon Legs</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Jump height</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr"/>
-      <c r="E91" s="12" t="inlineStr"/>
+      <c r="E91" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F91" s="13" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
-          <t>metres</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H91" s="12" t="inlineStr">
         <is>
-          <t>param:radius</t>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B92" s="12" t="inlineStr">
         <is>
-          <t>Take One for the Troop</t>
+          <t>Scout Cannon Legs</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>Share of the prevented Injury you take</t>
+          <t>Fall Injury</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr"/>
-      <c r="E92" s="12" t="inlineStr"/>
+      <c r="E92" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F92" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G92" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H92" s="12" t="inlineStr">
+        <is>
+          <t>mod:2</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="G92" s="12" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H92" s="12" t="inlineStr">
-        <is>
-          <t>param:absorb</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="B93" s="12" t="inlineStr">
-        <is>
-          <t>Take One for the Troop</t>
-        </is>
-      </c>
-      <c r="C93" s="12" t="inlineStr">
-        <is>
-          <t>Most Injury you take per hit</t>
-        </is>
-      </c>
-      <c r="D93" s="12" t="inlineStr"/>
-      <c r="E93" s="12" t="inlineStr"/>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>Crown of Bad Decisions</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Yellow stamina when picked</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr"/>
+      <c r="E93" s="5" t="inlineStr"/>
       <c r="F93" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G93" s="12" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="H93" s="12" t="inlineStr">
-        <is>
-          <t>param:cap</t>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>param:bonusNow</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>Friendship Bugle Choir</t>
+          <t>Crown of Bad Decisions</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>Stamina regen rate</t>
+          <t>Yellow stamina at each later campfire</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr"/>
-      <c r="E94" s="5" t="inlineStr">
-        <is>
-          <t>Teammates within 6 m</t>
-        </is>
-      </c>
+      <c r="E94" s="5" t="inlineStr"/>
       <c r="F94" s="13" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>points</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
-          <t>mod:0</t>
+          <t>param:bonusFire</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>Friendship Bugle Choir</t>
+          <t>Crown of Bad Decisions</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>All stamina costs</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
-        <is>
-          <t>while no teammate is near you</t>
-        </is>
-      </c>
-      <c r="E95" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+          <t>Curse when picked</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr"/>
+      <c r="E95" s="5" t="inlineStr"/>
       <c r="F95" s="13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>points</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>mod:1</t>
+          <t>param:curseNow</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>Friendship Bugle Choir</t>
+          <t>Crown of Bad Decisions</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Curse at each later campfire</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr"/>
       <c r="E96" s="5" t="inlineStr"/>
       <c r="F96" s="13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>metres</t>
+          <t>points</t>
         </is>
       </c>
       <c r="H96" s="5" t="inlineStr">
         <is>
-          <t>param:radius</t>
+          <t>param:curseFire</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="B97" s="12" t="inlineStr">
-        <is>
-          <t>Scout Cannon Legs</t>
-        </is>
-      </c>
-      <c r="C97" s="12" t="inlineStr">
-        <is>
-          <t>Sprint speed</t>
-        </is>
-      </c>
-      <c r="D97" s="12" t="inlineStr"/>
-      <c r="E97" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="A97" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>Crown of Bad Decisions</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Most Curse this card can ever add</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr"/>
+      <c r="E97" s="5" t="inlineStr"/>
       <c r="F97" s="13" t="n">
-        <v>35</v>
-      </c>
-      <c r="G97" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H97" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
+        <v>10</v>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>param:curseBudget</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B98" s="12" t="inlineStr">
         <is>
-          <t>Scout Cannon Legs</t>
+          <t>Pandora's Pocket Gamble</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>Jump height</t>
+          <t>Carried item weight</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr"/>
@@ -5891,7 +5839,7 @@
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>25</v>
+        <v>-10</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -5900,122 +5848,118 @@
       </c>
       <c r="H98" s="12" t="inlineStr">
         <is>
-          <t>mod:1</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>Scout Cannon Legs</t>
+          <t>Pandora's Pocket Gamble</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>Fall Injury</t>
+          <t>Chance of a lucky roll</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr"/>
-      <c r="E99" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="E99" s="12" t="inlineStr"/>
       <c r="F99" s="13" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H99" s="12" t="inlineStr">
         <is>
-          <t>mod:2</t>
+          <t>param:chance</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B100" s="5" t="inlineStr">
-        <is>
-          <t>Crown of Bad Decisions</t>
-        </is>
-      </c>
-      <c r="C100" s="5" t="inlineStr">
-        <is>
-          <t>Yellow stamina when picked</t>
-        </is>
-      </c>
-      <c r="D100" s="5" t="inlineStr"/>
-      <c r="E100" s="5" t="inlineStr"/>
+      <c r="A100" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="B100" s="12" t="inlineStr">
+        <is>
+          <t>Pandora's Pocket Gamble</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="inlineStr">
+        <is>
+          <t>Yellow stamina on a lucky roll</t>
+        </is>
+      </c>
+      <c r="D100" s="12" t="inlineStr"/>
+      <c r="E100" s="12" t="inlineStr"/>
       <c r="F100" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="G100" s="5" t="inlineStr">
+        <v>25</v>
+      </c>
+      <c r="G100" s="12" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="H100" s="5" t="inlineStr">
-        <is>
-          <t>param:bonusNow</t>
+      <c r="H100" s="12" t="inlineStr">
+        <is>
+          <t>param:bonus</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B101" s="5" t="inlineStr">
-        <is>
-          <t>Crown of Bad Decisions</t>
-        </is>
-      </c>
-      <c r="C101" s="5" t="inlineStr">
-        <is>
-          <t>Yellow stamina at each later campfire</t>
-        </is>
-      </c>
-      <c r="D101" s="5" t="inlineStr"/>
-      <c r="E101" s="5" t="inlineStr"/>
+      <c r="A101" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="B101" s="12" t="inlineStr">
+        <is>
+          <t>Pandora's Pocket Gamble</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>Injury on an unlucky roll</t>
+        </is>
+      </c>
+      <c r="D101" s="12" t="inlineStr"/>
+      <c r="E101" s="12" t="inlineStr"/>
       <c r="F101" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="G101" s="5" t="inlineStr">
+        <v>7.5</v>
+      </c>
+      <c r="G101" s="12" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="H101" s="5" t="inlineStr">
-        <is>
-          <t>param:bonusFire</t>
+      <c r="H101" s="12" t="inlineStr">
+        <is>
+          <t>param:injury</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>Crown of Bad Decisions</t>
+          <t>Bootleg Scoutmaster Bugle</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>Curse when picked</t>
+          <t>Yellow stamina per use</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr"/>
       <c r="E102" s="5" t="inlineStr"/>
       <c r="F102" s="13" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
@@ -6024,28 +5968,28 @@
       </c>
       <c r="H102" s="5" t="inlineStr">
         <is>
-          <t>param:curseNow</t>
+          <t>param:bonus</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>Crown of Bad Decisions</t>
+          <t>Bootleg Scoutmaster Bugle</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Curse at each later campfire</t>
+          <t>Injury per use</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr"/>
       <c r="E103" s="5" t="inlineStr"/>
       <c r="F103" s="13" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
@@ -6054,32 +5998,36 @@
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>param:curseFire</t>
+          <t>param:injury</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B104" s="12" t="inlineStr">
         <is>
-          <t>Pandora's Pocket Gamble</t>
+          <t>Big Lollipop Crash</t>
         </is>
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>Carried item weight</t>
-        </is>
-      </c>
-      <c r="D104" s="12" t="inlineStr"/>
+          <t>Sprint speed</t>
+        </is>
+      </c>
+      <c r="D104" s="12" t="inlineStr">
+        <is>
+          <t>while your sprint speed-up is on</t>
+        </is>
+      </c>
       <c r="E104" s="12" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>-10</v>
+        <v>30</v>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
@@ -6094,52 +6042,52 @@
     </row>
     <row r="105">
       <c r="A105" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>Pandora's Pocket Gamble</t>
+          <t>Big Lollipop Crash</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>Chance of a lucky roll</t>
+          <t>Sprint time before the speed-up</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr"/>
       <c r="E105" s="12" t="inlineStr"/>
       <c r="F105" s="13" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>seconds</t>
         </is>
       </c>
       <c r="H105" s="12" t="inlineStr">
         <is>
-          <t>param:chance</t>
+          <t>param:buildup</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B106" s="12" t="inlineStr">
         <is>
-          <t>Pandora's Pocket Gamble</t>
+          <t>Big Lollipop Crash</t>
         </is>
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>Yellow stamina on a lucky roll</t>
+          <t>Drowsy added</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr"/>
       <c r="E106" s="12" t="inlineStr"/>
       <c r="F106" s="13" t="n">
-        <v>25</v>
+        <v>2.5</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -6148,777 +6096,785 @@
       </c>
       <c r="H106" s="12" t="inlineStr">
         <is>
-          <t>param:bonus</t>
+          <t>param:drowsy</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>Pandora's Pocket Gamble</t>
+          <t>Big Lollipop Crash</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>Injury on an unlucky roll</t>
+          <t>Time between Drowsy penalties</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr"/>
       <c r="E107" s="12" t="inlineStr"/>
       <c r="F107" s="13" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>seconds</t>
         </is>
       </c>
       <c r="H107" s="12" t="inlineStr">
         <is>
-          <t>param:injury</t>
+          <t>param:cooldown</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>Bootleg Scoutmaster Bugle</t>
+          <t>Piton Payment Plan</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>Yellow stamina per use</t>
+          <t>Share of each fall's Injury that is delayed</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr"/>
       <c r="E108" s="5" t="inlineStr"/>
       <c r="F108" s="13" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H108" s="5" t="inlineStr">
         <is>
-          <t>param:bonus</t>
+          <t>param:defer</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>Bootleg Scoutmaster Bugle</t>
+          <t>Piton Payment Plan</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Injury per use</t>
+          <t>Delay before the rest lands</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr"/>
       <c r="E109" s="5" t="inlineStr"/>
       <c r="F109" s="13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>seconds</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr">
         <is>
-          <t>param:injury</t>
+          <t>param:delay</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="B110" s="12" t="inlineStr">
-        <is>
-          <t>Big Lollipop Crash</t>
-        </is>
-      </c>
-      <c r="C110" s="12" t="inlineStr">
-        <is>
-          <t>Sprint speed</t>
-        </is>
-      </c>
-      <c r="D110" s="12" t="inlineStr">
-        <is>
-          <t>while your sprint speed-up is on</t>
-        </is>
-      </c>
-      <c r="E110" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="A110" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>Piton Payment Plan</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>Share of the delayed Injury that still lands</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr"/>
+      <c r="E110" s="5" t="inlineStr"/>
       <c r="F110" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="G110" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H110" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
+        <v>80</v>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="inlineStr">
+        <is>
+          <t>param:keep</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>Big Lollipop Crash</t>
+          <t>Glass Scout Cannon</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>Sprint time before the speed-up</t>
+          <t>Max stamina</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr"/>
-      <c r="E111" s="12" t="inlineStr"/>
+      <c r="E111" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F111" s="13" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
-          <t>seconds</t>
+          <t>stamina points</t>
         </is>
       </c>
       <c r="H111" s="12" t="inlineStr">
         <is>
-          <t>param:buildup</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B112" s="12" t="inlineStr">
         <is>
-          <t>Big Lollipop Crash</t>
+          <t>Glass Scout Cannon</t>
         </is>
       </c>
       <c r="C112" s="12" t="inlineStr">
         <is>
-          <t>Drowsy added</t>
+          <t>All Injury</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr"/>
-      <c r="E112" s="12" t="inlineStr"/>
+      <c r="E112" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F112" s="13" t="n">
-        <v>7.5</v>
+        <v>25</v>
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H112" s="12" t="inlineStr">
         <is>
-          <t>param:drowsy</t>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="B113" s="12" t="inlineStr">
-        <is>
-          <t>Big Lollipop Crash</t>
-        </is>
-      </c>
-      <c r="C113" s="12" t="inlineStr">
-        <is>
-          <t>Time between Drowsy penalties</t>
-        </is>
-      </c>
-      <c r="D113" s="12" t="inlineStr"/>
-      <c r="E113" s="12" t="inlineStr"/>
+      <c r="A113" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>Baggage Claim Escapee</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>Sprint speed</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>while you don't wear a backpack</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F113" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="G113" s="12" t="inlineStr">
-        <is>
-          <t>seconds</t>
-        </is>
-      </c>
-      <c r="H113" s="12" t="inlineStr">
-        <is>
-          <t>param:cooldown</t>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>Piton Payment Plan</t>
+          <t>Baggage Claim Escapee</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>Share of each fall's Injury that is delayed</t>
-        </is>
-      </c>
-      <c r="D114" s="5" t="inlineStr"/>
-      <c r="E114" s="5" t="inlineStr"/>
+          <t>Jump height</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>while you don't wear a backpack</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F114" s="13" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H114" s="5" t="inlineStr">
         <is>
-          <t>param:defer</t>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>Piton Payment Plan</t>
+          <t>Baggage Claim Escapee</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>Delay before the rest lands</t>
-        </is>
-      </c>
-      <c r="D115" s="5" t="inlineStr"/>
-      <c r="E115" s="5" t="inlineStr"/>
+          <t>Sprint speed</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>while you wear a backpack</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F115" s="13" t="n">
-        <v>20</v>
+        <v>-5</v>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>seconds</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>param:delay</t>
+          <t>mod:2</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="5" t="n">
-        <v>54</v>
-      </c>
-      <c r="B116" s="5" t="inlineStr">
-        <is>
-          <t>Piton Payment Plan</t>
-        </is>
-      </c>
-      <c r="C116" s="5" t="inlineStr">
-        <is>
-          <t>Share of the delayed Injury that still lands</t>
-        </is>
-      </c>
-      <c r="D116" s="5" t="inlineStr"/>
-      <c r="E116" s="5" t="inlineStr"/>
+      <c r="A116" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="B116" s="12" t="inlineStr">
+        <is>
+          <t>Scout's Dishonor</t>
+        </is>
+      </c>
+      <c r="C116" s="12" t="inlineStr">
+        <is>
+          <t>Bonus cards (Common to Rare)</t>
+        </is>
+      </c>
+      <c r="D116" s="12" t="inlineStr"/>
+      <c r="E116" s="12" t="inlineStr"/>
       <c r="F116" s="13" t="n">
-        <v>80</v>
-      </c>
-      <c r="G116" s="5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H116" s="5" t="inlineStr">
-        <is>
-          <t>param:keep</t>
+        <v>2</v>
+      </c>
+      <c r="G116" s="12" t="inlineStr">
+        <is>
+          <t>cards</t>
+        </is>
+      </c>
+      <c r="H116" s="12" t="inlineStr">
+        <is>
+          <t>param:bonusCards</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>Glass Scout Cannon</t>
+          <t>Scout's Dishonor</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Max stamina</t>
+          <t>Curse when picked</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr"/>
-      <c r="E117" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="E117" s="12" t="inlineStr"/>
       <c r="F117" s="13" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
-          <t>stamina points</t>
+          <t>points</t>
         </is>
       </c>
       <c r="H117" s="12" t="inlineStr">
         <is>
-          <t>mod:0</t>
+          <t>param:curse</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B118" s="12" t="inlineStr">
         <is>
-          <t>Glass Scout Cannon</t>
+          <t>Scout's Dishonor</t>
         </is>
       </c>
       <c r="C118" s="12" t="inlineStr">
         <is>
-          <t>All Injury</t>
+          <t>Cards in your next offer</t>
         </is>
       </c>
       <c r="D118" s="12" t="inlineStr"/>
-      <c r="E118" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="E118" s="12" t="inlineStr"/>
       <c r="F118" s="13" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>cards</t>
         </is>
       </c>
       <c r="H118" s="12" t="inlineStr">
         <is>
-          <t>mod:1</t>
+          <t>param:nextOffer</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>Baggage Claim Escapee</t>
+          <t>BingBong Baggage Scanner</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>Sprint speed</t>
-        </is>
-      </c>
-      <c r="D119" s="5" t="inlineStr">
-        <is>
-          <t>while you don't wear a backpack</t>
-        </is>
-      </c>
-      <c r="E119" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr"/>
+      <c r="E119" s="5" t="inlineStr"/>
       <c r="F119" s="13" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>metres</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>mod:0</t>
+          <t>param:radius</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="B120" s="5" t="inlineStr">
-        <is>
-          <t>Baggage Claim Escapee</t>
-        </is>
-      </c>
-      <c r="C120" s="5" t="inlineStr">
-        <is>
-          <t>Jump height</t>
-        </is>
-      </c>
-      <c r="D120" s="5" t="inlineStr">
-        <is>
-          <t>while you don't wear a backpack</t>
-        </is>
-      </c>
-      <c r="E120" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="A120" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="B120" s="12" t="inlineStr">
+        <is>
+          <t>Medicinal Munchies</t>
+        </is>
+      </c>
+      <c r="C120" s="12" t="inlineStr">
+        <is>
+          <t>Needs at least this much Injury</t>
+        </is>
+      </c>
+      <c r="D120" s="12" t="inlineStr"/>
+      <c r="E120" s="12" t="inlineStr"/>
       <c r="F120" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="G120" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H120" s="5" t="inlineStr">
-        <is>
-          <t>mod:1</t>
+      <c r="G120" s="12" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H120" s="12" t="inlineStr">
+        <is>
+          <t>param:threshold</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="B121" s="5" t="inlineStr">
-        <is>
-          <t>Baggage Claim Escapee</t>
-        </is>
-      </c>
-      <c r="C121" s="5" t="inlineStr">
-        <is>
-          <t>Sprint speed</t>
-        </is>
-      </c>
-      <c r="D121" s="5" t="inlineStr">
-        <is>
-          <t>while you wear a backpack</t>
-        </is>
-      </c>
-      <c r="E121" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="A121" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="B121" s="12" t="inlineStr">
+        <is>
+          <t>Medicinal Munchies</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>Injury removed</t>
+        </is>
+      </c>
+      <c r="D121" s="12" t="inlineStr"/>
+      <c r="E121" s="12" t="inlineStr"/>
       <c r="F121" s="13" t="n">
-        <v>-15</v>
-      </c>
-      <c r="G121" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H121" s="5" t="inlineStr">
-        <is>
-          <t>mod:2</t>
+        <v>7.5</v>
+      </c>
+      <c r="G121" s="12" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H121" s="12" t="inlineStr">
+        <is>
+          <t>param:heal</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="B122" s="12" t="inlineStr">
-        <is>
-          <t>Scout's Dishonor</t>
-        </is>
-      </c>
-      <c r="C122" s="12" t="inlineStr">
-        <is>
-          <t>Bonus cards (Common to Rare)</t>
-        </is>
-      </c>
-      <c r="D122" s="12" t="inlineStr"/>
-      <c r="E122" s="12" t="inlineStr"/>
+      <c r="A122" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>Budget Checkpoint Flag</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>Injury after the revive</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr"/>
+      <c r="E122" s="5" t="inlineStr"/>
       <c r="F122" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G122" s="12" t="inlineStr">
-        <is>
-          <t>cards</t>
-        </is>
-      </c>
-      <c r="H122" s="12" t="inlineStr">
-        <is>
-          <t>param:bonusCards</t>
+        <v>40</v>
+      </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="inlineStr">
+        <is>
+          <t>param:injury</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>Scout's Dishonor</t>
+          <t>Petrify Procrastination</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>Curse when picked</t>
+          <t>Petrify build-up</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr"/>
-      <c r="E123" s="12" t="inlineStr"/>
+      <c r="E123" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F123" s="13" t="n">
-        <v>10</v>
+        <v>-50</v>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H123" s="12" t="inlineStr">
         <is>
-          <t>param:curse</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>BingBong Baggage Scanner</t>
+          <t>Fine Print</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Max stamina</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr"/>
-      <c r="E124" s="5" t="inlineStr"/>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F124" s="13" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>metres</t>
+          <t>stamina points</t>
         </is>
       </c>
       <c r="H124" s="5" t="inlineStr">
         <is>
-          <t>param:radius</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="12" t="n">
-        <v>59</v>
-      </c>
-      <c r="B125" s="12" t="inlineStr">
-        <is>
-          <t>Medicinal Munchies</t>
-        </is>
-      </c>
-      <c r="C125" s="12" t="inlineStr">
-        <is>
-          <t>Needs at least this much Injury</t>
-        </is>
-      </c>
-      <c r="D125" s="12" t="inlineStr"/>
-      <c r="E125" s="12" t="inlineStr"/>
+      <c r="A125" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>Fine Print</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>Curse when the sacrifice is made</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr"/>
+      <c r="E125" s="5" t="inlineStr"/>
       <c r="F125" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="G125" s="12" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="G125" s="5" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="H125" s="12" t="inlineStr">
-        <is>
-          <t>param:threshold</t>
+      <c r="H125" s="5" t="inlineStr">
+        <is>
+          <t>param:curse</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B126" s="12" t="inlineStr">
         <is>
-          <t>Medicinal Munchies</t>
+          <t>Scoutmaster</t>
         </is>
       </c>
       <c r="C126" s="12" t="inlineStr">
         <is>
-          <t>Injury removed</t>
+          <t>Climbing stamina cost (set, ignores other cards)</t>
         </is>
       </c>
       <c r="D126" s="12" t="inlineStr"/>
-      <c r="E126" s="12" t="inlineStr"/>
+      <c r="E126" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F126" s="13" t="n">
-        <v>7.5</v>
+        <v>-100</v>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H126" s="12" t="inlineStr">
         <is>
-          <t>param:heal</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="B127" s="5" t="inlineStr">
-        <is>
-          <t>Budget Checkpoint Flag</t>
-        </is>
-      </c>
-      <c r="C127" s="5" t="inlineStr">
+      <c r="A127" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="B127" s="12" t="inlineStr">
+        <is>
+          <t>Scoutmaster</t>
+        </is>
+      </c>
+      <c r="C127" s="12" t="inlineStr">
+        <is>
+          <t>Fall Injury (set, ignores other cards)</t>
+        </is>
+      </c>
+      <c r="D127" s="12" t="inlineStr"/>
+      <c r="E127" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F127" s="13" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G127" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H127" s="12" t="inlineStr">
+        <is>
+          <t>mod:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="B128" s="12" t="inlineStr">
+        <is>
+          <t>Scoutmaster</t>
+        </is>
+      </c>
+      <c r="C128" s="12" t="inlineStr">
+        <is>
+          <t>Sprint speed</t>
+        </is>
+      </c>
+      <c r="D128" s="12" t="inlineStr"/>
+      <c r="E128" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F128" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G128" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H128" s="12" t="inlineStr">
+        <is>
+          <t>mod:2</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>The Eternal Campfire</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
         <is>
           <t>Max stamina</t>
         </is>
       </c>
-      <c r="D127" s="5" t="inlineStr"/>
-      <c r="E127" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F127" s="13" t="n">
-        <v>-15</v>
-      </c>
-      <c r="G127" s="5" t="inlineStr">
+      <c r="D129" s="5" t="inlineStr"/>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>You and teammates within 15 m</t>
+        </is>
+      </c>
+      <c r="F129" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="G129" s="5" t="inlineStr">
         <is>
           <t>stamina points</t>
         </is>
       </c>
-      <c r="H127" s="5" t="inlineStr">
+      <c r="H129" s="5" t="inlineStr">
         <is>
           <t>mod:0</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="B128" s="5" t="inlineStr">
-        <is>
-          <t>Budget Checkpoint Flag</t>
-        </is>
-      </c>
-      <c r="C128" s="5" t="inlineStr">
-        <is>
-          <t>Injury after the revive</t>
-        </is>
-      </c>
-      <c r="D128" s="5" t="inlineStr"/>
-      <c r="E128" s="5" t="inlineStr"/>
-      <c r="F128" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="G128" s="5" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H128" s="5" t="inlineStr">
-        <is>
-          <t>param:injury</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="12" t="n">
-        <v>61</v>
-      </c>
-      <c r="B129" s="12" t="inlineStr">
-        <is>
-          <t>Petrify Procrastination</t>
-        </is>
-      </c>
-      <c r="C129" s="12" t="inlineStr">
-        <is>
-          <t>Petrify build-up</t>
-        </is>
-      </c>
-      <c r="D129" s="12" t="inlineStr"/>
-      <c r="E129" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F129" s="13" t="n">
-        <v>-35</v>
-      </c>
-      <c r="G129" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H129" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
-        </is>
-      </c>
-    </row>
     <row r="130">
-      <c r="A130" s="12" t="n">
-        <v>61</v>
-      </c>
-      <c r="B130" s="12" t="inlineStr">
-        <is>
-          <t>Petrify Procrastination</t>
-        </is>
-      </c>
-      <c r="C130" s="12" t="inlineStr">
-        <is>
-          <t>Fall Injury</t>
-        </is>
-      </c>
-      <c r="D130" s="12" t="inlineStr"/>
-      <c r="E130" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
+      <c r="A130" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>The Eternal Campfire</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>All Injury</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr"/>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>You and teammates within 15 m</t>
         </is>
       </c>
       <c r="F130" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="G130" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H130" s="12" t="inlineStr">
+        <v>-60</v>
+      </c>
+      <c r="G130" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H130" s="5" t="inlineStr">
         <is>
           <t>mod:1</t>
         </is>
@@ -6926,364 +6882,130 @@
     </row>
     <row r="131">
       <c r="A131" s="5" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>Fine Print</t>
+          <t>The Eternal Campfire</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>Max stamina</t>
+          <t>All negative status build-up</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr"/>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>You and teammates within 15 m</t>
         </is>
       </c>
       <c r="F131" s="13" t="n">
-        <v>35</v>
+        <v>-60</v>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>stamina points</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
-          <t>mod:0</t>
+          <t>mod:2</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>Fine Print</t>
+          <t>The Eternal Campfire</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>Curse at each later campfire</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr"/>
       <c r="E132" s="5" t="inlineStr"/>
       <c r="F132" s="13" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
+          <t>metres</t>
+        </is>
+      </c>
+      <c r="H132" s="5" t="inlineStr">
+        <is>
+          <t>param:radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>The Eternal Campfire</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>Injury after the revive</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr"/>
+      <c r="E133" s="5" t="inlineStr"/>
+      <c r="F133" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="G133" s="5" t="inlineStr">
+        <is>
           <t>points</t>
         </is>
       </c>
-      <c r="H132" s="5" t="inlineStr">
-        <is>
-          <t>param:curseFire</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="B133" s="12" t="inlineStr">
-        <is>
-          <t>Scoutmaster</t>
-        </is>
-      </c>
-      <c r="C133" s="12" t="inlineStr">
-        <is>
-          <t>Climbing stamina cost (set, ignores other cards)</t>
-        </is>
-      </c>
-      <c r="D133" s="12" t="inlineStr"/>
-      <c r="E133" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F133" s="13" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G133" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H133" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
+      <c r="H133" s="5" t="inlineStr">
+        <is>
+          <t>param:injury</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="B134" s="12" t="inlineStr">
-        <is>
-          <t>Scoutmaster</t>
-        </is>
-      </c>
-      <c r="C134" s="12" t="inlineStr">
-        <is>
-          <t>Fall Injury (set, ignores other cards)</t>
-        </is>
-      </c>
-      <c r="D134" s="12" t="inlineStr"/>
-      <c r="E134" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="A134" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>The Eternal Campfire</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>Stamina after the revive (at least)</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr"/>
+      <c r="E134" s="5" t="inlineStr"/>
       <c r="F134" s="13" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G134" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H134" s="12" t="inlineStr">
-        <is>
-          <t>mod:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="B135" s="12" t="inlineStr">
-        <is>
-          <t>Scoutmaster</t>
-        </is>
-      </c>
-      <c r="C135" s="12" t="inlineStr">
-        <is>
-          <t>Sprint speed</t>
-        </is>
-      </c>
-      <c r="D135" s="12" t="inlineStr"/>
-      <c r="E135" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F135" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="G135" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H135" s="12" t="inlineStr">
-        <is>
-          <t>mod:2</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>The Eternal Campfire</t>
-        </is>
-      </c>
-      <c r="C136" s="5" t="inlineStr">
-        <is>
-          <t>Max stamina</t>
-        </is>
-      </c>
-      <c r="D136" s="5" t="inlineStr"/>
-      <c r="E136" s="5" t="inlineStr">
-        <is>
-          <t>You and teammates within 15 m</t>
-        </is>
-      </c>
-      <c r="F136" s="13" t="n">
-        <v>35</v>
-      </c>
-      <c r="G136" s="5" t="inlineStr">
-        <is>
-          <t>stamina points</t>
-        </is>
-      </c>
-      <c r="H136" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B137" s="5" t="inlineStr">
-        <is>
-          <t>The Eternal Campfire</t>
-        </is>
-      </c>
-      <c r="C137" s="5" t="inlineStr">
-        <is>
-          <t>All Injury</t>
-        </is>
-      </c>
-      <c r="D137" s="5" t="inlineStr"/>
-      <c r="E137" s="5" t="inlineStr">
-        <is>
-          <t>You and teammates within 15 m</t>
-        </is>
-      </c>
-      <c r="F137" s="13" t="n">
-        <v>-60</v>
-      </c>
-      <c r="G137" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H137" s="5" t="inlineStr">
-        <is>
-          <t>mod:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B138" s="5" t="inlineStr">
-        <is>
-          <t>The Eternal Campfire</t>
-        </is>
-      </c>
-      <c r="C138" s="5" t="inlineStr">
-        <is>
-          <t>All negative status build-up</t>
-        </is>
-      </c>
-      <c r="D138" s="5" t="inlineStr"/>
-      <c r="E138" s="5" t="inlineStr">
-        <is>
-          <t>You and teammates within 15 m</t>
-        </is>
-      </c>
-      <c r="F138" s="13" t="n">
-        <v>-60</v>
-      </c>
-      <c r="G138" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H138" s="5" t="inlineStr">
-        <is>
-          <t>mod:2</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B139" s="5" t="inlineStr">
-        <is>
-          <t>The Eternal Campfire</t>
-        </is>
-      </c>
-      <c r="C139" s="5" t="inlineStr">
-        <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="D139" s="5" t="inlineStr"/>
-      <c r="E139" s="5" t="inlineStr"/>
-      <c r="F139" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="G139" s="5" t="inlineStr">
-        <is>
-          <t>metres</t>
-        </is>
-      </c>
-      <c r="H139" s="5" t="inlineStr">
-        <is>
-          <t>param:radius</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B140" s="5" t="inlineStr">
-        <is>
-          <t>The Eternal Campfire</t>
-        </is>
-      </c>
-      <c r="C140" s="5" t="inlineStr">
-        <is>
-          <t>Injury after the revive</t>
-        </is>
-      </c>
-      <c r="D140" s="5" t="inlineStr"/>
-      <c r="E140" s="5" t="inlineStr"/>
-      <c r="F140" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="G140" s="5" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="G134" s="5" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="H140" s="5" t="inlineStr">
-        <is>
-          <t>param:injury</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B141" s="5" t="inlineStr">
-        <is>
-          <t>The Eternal Campfire</t>
-        </is>
-      </c>
-      <c r="C141" s="5" t="inlineStr">
-        <is>
-          <t>Stamina after the revive (at least)</t>
-        </is>
-      </c>
-      <c r="D141" s="5" t="inlineStr"/>
-      <c r="E141" s="5" t="inlineStr"/>
-      <c r="F141" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="G141" s="5" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H141" s="5" t="inlineStr">
+      <c r="H134" s="5" t="inlineStr">
         <is>
           <t>param:stamina</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H141"/>
+  <autoFilter ref="A1:H134"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7332,7 +7054,7 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
@@ -7352,7 +7074,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
@@ -7372,7 +7094,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>

--- a/design/editable/card-sheet.xlsx
+++ b/design/editable/card-sheet.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cards'!$A$1:$G$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Numbers'!$A$1:$H$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Numbers'!$A$1:$H$135</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Stamina regeneration starts 0.5s sooner.</t>
+          <t>Hanging still on a wall drains 75% less stamina.</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Crouch and stay still to recover stamina 35% faster.</t>
+          <t>Crouch and stay still for 3s to gain 25 yellow stamina. Once per biome.</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr"/>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>You and teammates within 8 m recover stamina 15% faster.</t>
+          <t>You and teammates within 8 m gain 10 maximum stamina.</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr"/>
@@ -2591,7 +2591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H134"/>
+  <dimension ref="A1:H135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Stamina regen delay</t>
+          <t>Max stamina</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr"/>
@@ -3395,11 +3395,11 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>-0.5</v>
+        <v>-5</v>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>seconds (negative = sooner)</t>
+          <t>stamina points</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -3419,26 +3419,22 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Max stamina</t>
+          <t>Hanging drain refunded</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr"/>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="E25" s="5" t="inlineStr"/>
       <c r="F25" s="13" t="n">
-        <v>-5</v>
+        <v>75</v>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>stamina points</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>mod:1</t>
+          <t>param:refund</t>
         </is>
       </c>
     </row>
@@ -3453,64 +3449,52 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>Stamina regen rate</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>while you crouch and stay still</t>
-        </is>
-      </c>
-      <c r="E26" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+          <t>Crouch time required</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr"/>
+      <c r="E26" s="12" t="inlineStr"/>
       <c r="F26" s="13" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>seconds</t>
         </is>
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>mod:0</t>
+          <t>param:hold</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>I'm getting Scoutmastered</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Sprint speed</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr"/>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="A27" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Meditation</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>Yellow stamina gained</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr"/>
+      <c r="E27" s="12" t="inlineStr"/>
       <c r="F27" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>param:bonus</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3509,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Max stamina</t>
+          <t>Sprint speed</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr"/>
@@ -3535,54 +3519,50 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>I'm getting Scoutmastered</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Max stamina</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="n">
         <v>-7.5</v>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>stamina points</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>mod:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>Endurance Badge</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>Climbing stamina cost</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>while your climbing boost is on</t>
-        </is>
-      </c>
-      <c r="E29" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F29" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="G29" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H29" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -3597,22 +3577,30 @@
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>Climbing time before the boost</t>
-        </is>
-      </c>
-      <c r="D30" s="12" t="inlineStr"/>
-      <c r="E30" s="12" t="inlineStr"/>
+          <t>Climbing stamina cost</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>while your climbing boost is on</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F30" s="13" t="n">
-        <v>2</v>
+        <v>-40</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>seconds</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>param:buildup</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -3627,7 +3615,7 @@
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Boost length</t>
+          <t>Climbing time before the boost</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr"/>
@@ -3642,73 +3630,69 @@
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
+          <t>param:buildup</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>Endurance Badge</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>Boost length</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr"/>
+      <c r="E32" s="12" t="inlineStr"/>
+      <c r="F32" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>seconds</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
           <t>param:boost</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="n">
+    <row r="33">
+      <c r="A33" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Marshmallow Morale</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Hunger removed by cooked food</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr"/>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr"/>
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
-      <c r="F32" s="13" t="n">
+      <c r="F33" s="13" t="n">
         <v>-10</v>
       </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>Cool, Calm, and Collected.</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="inlineStr">
-        <is>
-          <t>Heat build-up</t>
-        </is>
-      </c>
-      <c r="D33" s="12" t="inlineStr"/>
-      <c r="E33" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F33" s="13" t="n">
-        <v>-50</v>
-      </c>
-      <c r="G33" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H33" s="12" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>mod:0</t>
         </is>
@@ -3725,7 +3709,7 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>Cold build-up</t>
+          <t>Heat build-up</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr"/>
@@ -3735,50 +3719,50 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
+        <v>-50</v>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>Cool, Calm, and Collected.</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>Cold build-up</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr"/>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="G34" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H34" s="12" t="inlineStr">
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="inlineStr">
         <is>
           <t>mod:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>Just hot.</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>Cold build-up</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr"/>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F35" s="13" t="n">
-        <v>-50</v>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -3793,7 +3777,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Heat build-up</t>
+          <t>Cold build-up</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr"/>
@@ -3803,50 +3787,50 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
+        <v>-50</v>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Just hot.</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Heat build-up</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr"/>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>mod:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="B37" s="12" t="inlineStr">
-        <is>
-          <t>Antidote Enthusiast</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="inlineStr">
-        <is>
-          <t>Poison build-up</t>
-        </is>
-      </c>
-      <c r="D37" s="12" t="inlineStr"/>
-      <c r="E37" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F37" s="13" t="n">
-        <v>-35</v>
-      </c>
-      <c r="G37" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H37" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3845,7 @@
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>Heat build-up</t>
+          <t>Poison build-up</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr"/>
@@ -3871,7 +3855,7 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>10</v>
+        <v>-35</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -3880,7 +3864,7 @@
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>mod:1</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3879,7 @@
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Cold build-up</t>
+          <t>Heat build-up</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr"/>
@@ -3914,107 +3898,107 @@
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
+          <t>mod:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>Antidote Enthusiast</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>Cold build-up</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr"/>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
           <t>mod:2</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="n">
+    <row r="41">
+      <c r="A41" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>ROOTS Survivor</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>Spores build-up</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr"/>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr"/>
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
-      <c r="F40" s="13" t="n">
+      <c r="F41" s="13" t="n">
         <v>-35</v>
       </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>mod:0</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="12" t="n">
+    <row r="42">
+      <c r="A42" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="B41" s="12" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>Cactus? What Cactus?</t>
         </is>
       </c>
-      <c r="C41" s="12" t="inlineStr">
+      <c r="C42" s="12" t="inlineStr">
         <is>
           <t>Thorns build-up</t>
         </is>
       </c>
-      <c r="D41" s="12" t="inlineStr"/>
-      <c r="E41" s="12" t="inlineStr">
+      <c r="D42" s="12" t="inlineStr"/>
+      <c r="E42" s="12" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
-      <c r="F41" s="13" t="n">
+      <c r="F42" s="13" t="n">
         <v>-40</v>
       </c>
-      <c r="G41" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H41" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>Aloe</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>Heat decay</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr"/>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F42" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H42" s="12" t="inlineStr">
         <is>
           <t>mod:0</t>
         </is>
@@ -4031,7 +4015,7 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Heat build-up</t>
+          <t>Heat decay</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr"/>
@@ -4041,50 +4025,50 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Aloe</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Heat build-up</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr"/>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F44" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
         <is>
           <t>mod:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="B44" s="12" t="inlineStr">
-        <is>
-          <t>Heat Pack</t>
-        </is>
-      </c>
-      <c r="C44" s="12" t="inlineStr">
-        <is>
-          <t>Cold decay</t>
-        </is>
-      </c>
-      <c r="D44" s="12" t="inlineStr"/>
-      <c r="E44" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F44" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="G44" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H44" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -4099,7 +4083,7 @@
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Cold build-up</t>
+          <t>Cold decay</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr"/>
@@ -4109,54 +4093,50 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H45" s="12" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>Heat Pack</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>Cold build-up</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr"/>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F46" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H45" s="12" t="inlineStr">
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H46" s="12" t="inlineStr">
         <is>
           <t>mod:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>Fartberry Fitness</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>Climbing stamina cost</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>while you have more than 20 Poison</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F46" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -4171,56 +4151,64 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
+          <t>Climbing stamina cost</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>while you have more than 20 Poison</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>-40</v>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Fartberry Fitness</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
           <t>Poison decay</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr"/>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr"/>
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
-      <c r="F47" s="13" t="n">
+      <c r="F48" s="13" t="n">
         <v>-10</v>
       </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H47" s="5" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
         <is>
           <t>mod:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="B48" s="12" t="inlineStr">
-        <is>
-          <t>BingBong</t>
-        </is>
-      </c>
-      <c r="C48" s="12" t="inlineStr">
-        <is>
-          <t>Time between powers</t>
-        </is>
-      </c>
-      <c r="D48" s="12" t="inlineStr"/>
-      <c r="E48" s="12" t="inlineStr"/>
-      <c r="F48" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G48" s="12" t="inlineStr">
-        <is>
-          <t>seconds</t>
-        </is>
-      </c>
-      <c r="H48" s="12" t="inlineStr">
-        <is>
-          <t>param:interval</t>
         </is>
       </c>
     </row>
@@ -4235,13 +4223,13 @@
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Power length</t>
+          <t>Time between powers</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr"/>
       <c r="E49" s="12" t="inlineStr"/>
       <c r="F49" s="13" t="n">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -4250,7 +4238,7 @@
       </c>
       <c r="H49" s="12" t="inlineStr">
         <is>
-          <t>param:duration</t>
+          <t>param:interval</t>
         </is>
       </c>
     </row>
@@ -4265,92 +4253,84 @@
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>Low Gravity strength (the mushroom is 3)</t>
+          <t>Power length</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr"/>
       <c r="E50" s="12" t="inlineStr"/>
       <c r="F50" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>seconds</t>
+        </is>
+      </c>
+      <c r="H50" s="12" t="inlineStr">
+        <is>
+          <t>param:duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>BingBong</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>Low Gravity strength (the mushroom is 3)</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr"/>
+      <c r="E51" s="12" t="inlineStr"/>
+      <c r="F51" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G50" s="12" t="inlineStr">
+      <c r="G51" s="12" t="inlineStr">
         <is>
           <t>strength</t>
         </is>
       </c>
-      <c r="H50" s="12" t="inlineStr">
+      <c r="H51" s="12" t="inlineStr">
         <is>
           <t>param:lowGravity</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="n">
+    <row r="52">
+      <c r="A52" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>Tara</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>Injury healed by items (received)</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr"/>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr"/>
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
-      <c r="F51" s="13" t="n">
+      <c r="F52" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="B52" s="12" t="inlineStr">
-        <is>
-          <t>Walk It Off</t>
-        </is>
-      </c>
-      <c r="C52" s="12" t="inlineStr">
-        <is>
-          <t>Climbing stamina cost</t>
-        </is>
-      </c>
-      <c r="D52" s="12" t="inlineStr">
-        <is>
-          <t>while you have 20+ Injury</t>
-        </is>
-      </c>
-      <c r="E52" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F52" s="13" t="n">
-        <v>-25</v>
-      </c>
-      <c r="G52" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H52" s="12" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
         <is>
           <t>mod:0</t>
         </is>
@@ -4367,7 +4347,7 @@
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Sprint stamina cost</t>
+          <t>Climbing stamina cost</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
@@ -4390,7 +4370,7 @@
       </c>
       <c r="H53" s="12" t="inlineStr">
         <is>
-          <t>mod:1</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -4405,56 +4385,64 @@
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
+          <t>Sprint stamina cost</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>while you have 20+ Injury</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F54" s="13" t="n">
+        <v>-25</v>
+      </c>
+      <c r="G54" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H54" s="12" t="inlineStr">
+        <is>
+          <t>mod:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>Walk It Off</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
           <t>All Injury</t>
         </is>
       </c>
-      <c r="D54" s="12" t="inlineStr"/>
-      <c r="E54" s="12" t="inlineStr">
+      <c r="D55" s="12" t="inlineStr"/>
+      <c r="E55" s="12" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
-      <c r="F54" s="13" t="n">
+      <c r="F55" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G54" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H54" s="12" t="inlineStr">
+      <c r="G55" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H55" s="12" t="inlineStr">
         <is>
           <t>mod:2</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>Discount Cure-All</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>Needs at least this much of the status</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr"/>
-      <c r="E55" s="5" t="inlineStr"/>
-      <c r="F55" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>param:threshold</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4457,7 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Status removed</t>
+          <t>Needs at least this much of the status</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr"/>
@@ -4484,171 +4472,167 @@
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>param:remove</t>
+          <t>param:threshold</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Discount Cure-All</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Status removed</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr"/>
+      <c r="E57" s="5" t="inlineStr"/>
+      <c r="F57" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>param:remove</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>Gourmand's Gut</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>Hunger removed by food</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr"/>
-      <c r="E57" s="5" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr"/>
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
-      <c r="F57" s="13" t="n">
+      <c r="F58" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="G57" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H57" s="5" t="inlineStr">
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
         <is>
           <t>mod:0</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="12" t="n">
+    <row r="59">
+      <c r="A59" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="B58" s="12" t="inlineStr">
+      <c r="B59" s="12" t="inlineStr">
         <is>
           <t>Book of Broken Bones</t>
         </is>
       </c>
-      <c r="C58" s="12" t="inlineStr">
+      <c r="C59" s="12" t="inlineStr">
         <is>
           <t>Curse added by revival</t>
         </is>
       </c>
-      <c r="D58" s="12" t="inlineStr"/>
-      <c r="E58" s="12" t="inlineStr">
+      <c r="D59" s="12" t="inlineStr"/>
+      <c r="E59" s="12" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
-      <c r="F58" s="13" t="n">
+      <c r="F59" s="13" t="n">
         <v>-100</v>
       </c>
-      <c r="G58" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H58" s="12" t="inlineStr">
+      <c r="G59" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H59" s="12" t="inlineStr">
         <is>
           <t>mod:0</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="5" t="n">
+    <row r="60">
+      <c r="A60" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>Mini Tenacity</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>Extra status removed</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr"/>
-      <c r="E59" s="5" t="inlineStr"/>
-      <c r="F59" s="13" t="n">
+      <c r="D60" s="5" t="inlineStr"/>
+      <c r="E60" s="5" t="inlineStr"/>
+      <c r="F60" s="13" t="n">
         <v>7.5</v>
       </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="G60" s="5" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr">
+      <c r="H60" s="5" t="inlineStr">
         <is>
           <t>param:bonus</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="12" t="n">
+    <row r="61">
+      <c r="A61" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="B60" s="12" t="inlineStr">
+      <c r="B61" s="12" t="inlineStr">
         <is>
           <t>Bing Bong's Baggage</t>
         </is>
       </c>
-      <c r="C60" s="12" t="inlineStr">
+      <c r="C61" s="12" t="inlineStr">
         <is>
           <t>All carried weight</t>
         </is>
       </c>
-      <c r="D60" s="12" t="inlineStr"/>
-      <c r="E60" s="12" t="inlineStr">
+      <c r="D61" s="12" t="inlineStr"/>
+      <c r="E61" s="12" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
-      <c r="F60" s="13" t="n">
+      <c r="F61" s="13" t="n">
         <v>-50</v>
       </c>
-      <c r="G60" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H60" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>Carry-On Only</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>Held item weight</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr"/>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F61" s="13" t="n">
-        <v>-45</v>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="inlineStr">
+      <c r="G61" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H61" s="12" t="inlineStr">
         <is>
           <t>mod:0</t>
         </is>
@@ -4665,7 +4649,7 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Backpack content weight</t>
+          <t>Held item weight</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr"/>
@@ -4675,116 +4659,116 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
+        <v>-45</v>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Carry-On Only</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Backpack content weight</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr"/>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F63" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H62" s="5" t="inlineStr">
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
         <is>
           <t>mod:1</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="12" t="n">
+    <row r="64">
+      <c r="A64" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="B63" s="12" t="inlineStr">
+      <c r="B64" s="12" t="inlineStr">
         <is>
           <t>Idol Hands</t>
         </is>
       </c>
-      <c r="C63" s="12" t="inlineStr">
+      <c r="C64" s="12" t="inlineStr">
         <is>
           <t>Held item weight</t>
         </is>
       </c>
-      <c r="D63" s="12" t="inlineStr"/>
-      <c r="E63" s="12" t="inlineStr">
+      <c r="D64" s="12" t="inlineStr"/>
+      <c r="E64" s="12" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
-      <c r="F63" s="13" t="n">
+      <c r="F64" s="13" t="n">
         <v>-35</v>
       </c>
-      <c r="G63" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H63" s="12" t="inlineStr">
+      <c r="G64" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H64" s="12" t="inlineStr">
         <is>
           <t>mod:0</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="5" t="n">
+    <row r="65">
+      <c r="A65" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>Cook It, Keep It</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>Uncooked food nutrition</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr"/>
-      <c r="E64" s="5" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr"/>
+      <c r="E65" s="5" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
-      <c r="F64" s="13" t="n">
+      <c r="F65" s="13" t="n">
         <v>-15</v>
       </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H64" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="B65" s="12" t="inlineStr">
-        <is>
-          <t>Cooking Badge Deluxe</t>
-        </is>
-      </c>
-      <c r="C65" s="12" t="inlineStr">
-        <is>
-          <t>Hunger removed by cooked food</t>
-        </is>
-      </c>
-      <c r="D65" s="12" t="inlineStr"/>
-      <c r="E65" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F65" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="G65" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H65" s="12" t="inlineStr">
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
         <is>
           <t>mod:0</t>
         </is>
@@ -4801,52 +4785,56 @@
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
+          <t>Hunger removed by cooked food</t>
+        </is>
+      </c>
+      <c r="D66" s="12" t="inlineStr"/>
+      <c r="E66" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F66" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="G66" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H66" s="12" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t>Cooking Badge Deluxe</t>
+        </is>
+      </c>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
           <t>Poison added</t>
         </is>
       </c>
-      <c r="D66" s="12" t="inlineStr"/>
-      <c r="E66" s="12" t="inlineStr"/>
-      <c r="F66" s="13" t="n">
+      <c r="D67" s="12" t="inlineStr"/>
+      <c r="E67" s="12" t="inlineStr"/>
+      <c r="F67" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G66" s="12" t="inlineStr">
+      <c r="G67" s="12" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="H66" s="12" t="inlineStr">
+      <c r="H67" s="12" t="inlineStr">
         <is>
           <t>param:poison</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>Clown Luggage Special</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>Bonus cards</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="inlineStr"/>
-      <c r="E67" s="5" t="inlineStr"/>
-      <c r="F67" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>cards</t>
-        </is>
-      </c>
-      <c r="H67" s="5" t="inlineStr">
-        <is>
-          <t>param:bonusCards</t>
         </is>
       </c>
     </row>
@@ -4861,22 +4849,22 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Possible penalty: climbing stamina cost</t>
+          <t>Bonus cards</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr"/>
       <c r="E68" s="5" t="inlineStr"/>
       <c r="F68" s="13" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>cards</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>param:climbPenalty</t>
+          <t>param:bonusCards</t>
         </is>
       </c>
     </row>
@@ -4891,7 +4879,7 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Possible penalty: sprint stamina cost</t>
+          <t>Possible penalty: climbing stamina cost</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr"/>
@@ -4906,7 +4894,7 @@
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>param:sprintPenalty</t>
+          <t>param:climbPenalty</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4909,7 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Possible penalty: all Injury</t>
+          <t>Possible penalty: sprint stamina cost</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr"/>
@@ -4936,7 +4924,7 @@
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>param:injuryPenalty</t>
+          <t>param:sprintPenalty</t>
         </is>
       </c>
     </row>
@@ -4951,7 +4939,7 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Possible penalty: Hunger build-up</t>
+          <t>Possible penalty: all Injury</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr"/>
@@ -4966,41 +4954,37 @@
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
+          <t>param:injuryPenalty</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Clown Luggage Special</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>Possible penalty: Hunger build-up</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr"/>
+      <c r="E72" s="5" t="inlineStr"/>
+      <c r="F72" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
           <t>param:hungerPenalty</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="B72" s="12" t="inlineStr">
-        <is>
-          <t>Rule Zero</t>
-        </is>
-      </c>
-      <c r="C72" s="12" t="inlineStr">
-        <is>
-          <t>Climbing stamina cost</t>
-        </is>
-      </c>
-      <c r="D72" s="12" t="inlineStr"/>
-      <c r="E72" s="12" t="inlineStr">
-        <is>
-          <t>Teammates within 8 m</t>
-        </is>
-      </c>
-      <c r="F72" s="13" t="n">
-        <v>-20</v>
-      </c>
-      <c r="G72" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H72" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -5018,14 +5002,10 @@
           <t>Climbing stamina cost</t>
         </is>
       </c>
-      <c r="D73" s="12" t="inlineStr">
-        <is>
-          <t>while a teammate is near you</t>
-        </is>
-      </c>
+      <c r="D73" s="12" t="inlineStr"/>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Teammates within 8 m</t>
         </is>
       </c>
       <c r="F73" s="13" t="n">
@@ -5038,7 +5018,7 @@
       </c>
       <c r="H73" s="12" t="inlineStr">
         <is>
-          <t>mod:1</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5038,7 @@
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>while no teammate is near you</t>
+          <t>while a teammate is near you</t>
         </is>
       </c>
       <c r="E74" s="12" t="inlineStr">
@@ -5067,7 +5047,7 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>5</v>
+        <v>-20</v>
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
@@ -5076,7 +5056,7 @@
       </c>
       <c r="H74" s="12" t="inlineStr">
         <is>
-          <t>mod:2</t>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
@@ -5091,56 +5071,60 @@
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
+          <t>Climbing stamina cost</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>while no teammate is near you</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F75" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G75" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H75" s="12" t="inlineStr">
+        <is>
+          <t>mod:2</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="B76" s="12" t="inlineStr">
+        <is>
+          <t>Rule Zero</t>
+        </is>
+      </c>
+      <c r="C76" s="12" t="inlineStr">
+        <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="D75" s="12" t="inlineStr"/>
-      <c r="E75" s="12" t="inlineStr"/>
-      <c r="F75" s="13" t="n">
+      <c r="D76" s="12" t="inlineStr"/>
+      <c r="E76" s="12" t="inlineStr"/>
+      <c r="F76" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="G75" s="12" t="inlineStr">
+      <c r="G76" s="12" t="inlineStr">
         <is>
           <t>metres</t>
         </is>
       </c>
-      <c r="H75" s="12" t="inlineStr">
+      <c r="H76" s="12" t="inlineStr">
         <is>
           <t>param:radius</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>First Aid Badge</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>Injury healed by items (given to teammates)</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr"/>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F76" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H76" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5139,7 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Injury healed by items (used on yourself)</t>
+          <t>Injury healed by items (given to teammates)</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr"/>
@@ -5165,148 +5149,148 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>First Aid Badge</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Injury healed by items (used on yourself)</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr"/>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F78" s="13" t="n">
         <v>-15</v>
       </c>
-      <c r="G77" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H77" s="5" t="inlineStr">
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
         <is>
           <t>mod:1</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="12" t="n">
+    <row r="79">
+      <c r="A79" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="B78" s="12" t="inlineStr">
+      <c r="B79" s="12" t="inlineStr">
         <is>
           <t>Human Carry-On</t>
         </is>
       </c>
-      <c r="C78" s="12" t="inlineStr">
+      <c r="C79" s="12" t="inlineStr">
         <is>
           <t>Carried scout weight</t>
         </is>
       </c>
-      <c r="D78" s="12" t="inlineStr"/>
-      <c r="E78" s="12" t="inlineStr">
+      <c r="D79" s="12" t="inlineStr"/>
+      <c r="E79" s="12" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
-      <c r="F78" s="13" t="n">
+      <c r="F79" s="13" t="n">
         <v>-35</v>
       </c>
-      <c r="G78" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H78" s="12" t="inlineStr">
+      <c r="G79" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H79" s="12" t="inlineStr">
         <is>
           <t>mod:0</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="5" t="n">
+    <row r="80">
+      <c r="A80" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="B79" s="5" t="inlineStr">
+      <c r="B80" s="5" t="inlineStr">
         <is>
           <t>Happy Camper Huddle</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
         <is>
           <t>Huddle radius and cold removal</t>
         </is>
       </c>
-      <c r="D79" s="5" t="inlineStr"/>
-      <c r="E79" s="5" t="inlineStr">
+      <c r="D80" s="5" t="inlineStr"/>
+      <c r="E80" s="5" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
-      <c r="F79" s="13" t="n">
+      <c r="F80" s="13" t="n">
         <v>35</v>
       </c>
-      <c r="G79" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H79" s="5" t="inlineStr">
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
         <is>
           <t>mod:0</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="12" t="n">
+    <row r="81">
+      <c r="A81" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="B80" s="12" t="inlineStr">
+      <c r="B81" s="12" t="inlineStr">
         <is>
           <t>Otto-Matic Clutch</t>
         </is>
       </c>
-      <c r="C80" s="12" t="inlineStr">
+      <c r="C81" s="12" t="inlineStr">
         <is>
           <t>Yellow stamina for both scouts</t>
         </is>
       </c>
-      <c r="D80" s="12" t="inlineStr"/>
-      <c r="E80" s="12" t="inlineStr"/>
-      <c r="F80" s="13" t="n">
+      <c r="D81" s="12" t="inlineStr"/>
+      <c r="E81" s="12" t="inlineStr"/>
+      <c r="F81" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="G80" s="12" t="inlineStr">
+      <c r="G81" s="12" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="H80" s="12" t="inlineStr">
+      <c r="H81" s="12" t="inlineStr">
         <is>
           <t>param:bonus</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>You're alright, you're alright</t>
-        </is>
-      </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>Helping-hand reach</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="inlineStr"/>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F81" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="G81" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H81" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -5321,56 +5305,56 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
+          <t>Helping-hand reach</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr"/>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F82" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>You're alright, you're alright</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
           <t>Stamina cost to start a pull</t>
         </is>
       </c>
-      <c r="D82" s="5" t="inlineStr"/>
-      <c r="E82" s="5" t="inlineStr"/>
-      <c r="F82" s="13" t="n">
+      <c r="D83" s="5" t="inlineStr"/>
+      <c r="E83" s="5" t="inlineStr"/>
+      <c r="F83" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G82" s="5" t="inlineStr">
+      <c r="G83" s="5" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="H82" s="5" t="inlineStr">
+      <c r="H83" s="5" t="inlineStr">
         <is>
           <t>param:stamina</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="B83" s="12" t="inlineStr">
-        <is>
-          <t>Take One for the Troop</t>
-        </is>
-      </c>
-      <c r="C83" s="12" t="inlineStr">
-        <is>
-          <t>All Injury</t>
-        </is>
-      </c>
-      <c r="D83" s="12" t="inlineStr"/>
-      <c r="E83" s="12" t="inlineStr">
-        <is>
-          <t>Teammates within 6 m</t>
-        </is>
-      </c>
-      <c r="F83" s="13" t="n">
-        <v>-30</v>
-      </c>
-      <c r="G83" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H83" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -5385,22 +5369,26 @@
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>All Injury</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr"/>
-      <c r="E84" s="12" t="inlineStr"/>
+      <c r="E84" s="12" t="inlineStr">
+        <is>
+          <t>Teammates within 6 m</t>
+        </is>
+      </c>
       <c r="F84" s="13" t="n">
-        <v>6</v>
+        <v>-30</v>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
-          <t>metres</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H84" s="12" t="inlineStr">
         <is>
-          <t>param:radius</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -5415,22 +5403,22 @@
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>Share of the prevented Injury you take</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr"/>
       <c r="E85" s="12" t="inlineStr"/>
       <c r="F85" s="13" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>metres</t>
         </is>
       </c>
       <c r="H85" s="12" t="inlineStr">
         <is>
-          <t>param:absorb</t>
+          <t>param:radius</t>
         </is>
       </c>
     </row>
@@ -5445,56 +5433,52 @@
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>Most Injury you take per hit</t>
+          <t>Share of the prevented Injury you take</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr"/>
       <c r="E86" s="12" t="inlineStr"/>
       <c r="F86" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G86" s="12" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H86" s="12" t="inlineStr">
+        <is>
+          <t>param:absorb</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="B87" s="12" t="inlineStr">
+        <is>
+          <t>Take One for the Troop</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="inlineStr">
+        <is>
+          <t>Most Injury you take per hit</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="inlineStr"/>
+      <c r="E87" s="12" t="inlineStr"/>
+      <c r="F87" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G86" s="12" t="inlineStr">
+      <c r="G87" s="12" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="H86" s="12" t="inlineStr">
+      <c r="H87" s="12" t="inlineStr">
         <is>
           <t>param:cap</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="B87" s="5" t="inlineStr">
-        <is>
-          <t>Friendship Bugle Choir</t>
-        </is>
-      </c>
-      <c r="C87" s="5" t="inlineStr">
-        <is>
-          <t>Stamina regen rate</t>
-        </is>
-      </c>
-      <c r="D87" s="5" t="inlineStr"/>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>Teammates within 8 m</t>
-        </is>
-      </c>
-      <c r="F87" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="G87" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H87" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -5509,30 +5493,26 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Stamina regen rate</t>
-        </is>
-      </c>
-      <c r="D88" s="5" t="inlineStr">
-        <is>
-          <t>while a teammate is near you</t>
-        </is>
-      </c>
+          <t>Max stamina</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr"/>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Teammates within 8 m</t>
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>stamina points</t>
         </is>
       </c>
       <c r="H88" s="5" t="inlineStr">
         <is>
-          <t>mod:1</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -5547,56 +5527,60 @@
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
+          <t>Max stamina</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>while a teammate is near you</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F89" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>stamina points</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>mod:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>Friendship Bugle Choir</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="D89" s="5" t="inlineStr"/>
-      <c r="E89" s="5" t="inlineStr"/>
-      <c r="F89" s="13" t="n">
+      <c r="D90" s="5" t="inlineStr"/>
+      <c r="E90" s="5" t="inlineStr"/>
+      <c r="F90" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="G89" s="5" t="inlineStr">
+      <c r="G90" s="5" t="inlineStr">
         <is>
           <t>metres</t>
         </is>
       </c>
-      <c r="H89" s="5" t="inlineStr">
+      <c r="H90" s="5" t="inlineStr">
         <is>
           <t>param:radius</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="B90" s="12" t="inlineStr">
-        <is>
-          <t>Scout Cannon Legs</t>
-        </is>
-      </c>
-      <c r="C90" s="12" t="inlineStr">
-        <is>
-          <t>Sprint speed</t>
-        </is>
-      </c>
-      <c r="D90" s="12" t="inlineStr"/>
-      <c r="E90" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F90" s="13" t="n">
-        <v>35</v>
-      </c>
-      <c r="G90" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H90" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -5611,7 +5595,7 @@
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>Jump height</t>
+          <t>Sprint speed</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr"/>
@@ -5621,7 +5605,7 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
@@ -5630,7 +5614,7 @@
       </c>
       <c r="H91" s="12" t="inlineStr">
         <is>
-          <t>mod:1</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -5645,7 +5629,7 @@
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>Fall Injury</t>
+          <t>Jump height</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr"/>
@@ -5664,37 +5648,41 @@
       </c>
       <c r="H92" s="12" t="inlineStr">
         <is>
+          <t>mod:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="B93" s="12" t="inlineStr">
+        <is>
+          <t>Scout Cannon Legs</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>Fall Injury</t>
+        </is>
+      </c>
+      <c r="D93" s="12" t="inlineStr"/>
+      <c r="E93" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F93" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G93" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H93" s="12" t="inlineStr">
+        <is>
           <t>mod:2</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B93" s="5" t="inlineStr">
-        <is>
-          <t>Crown of Bad Decisions</t>
-        </is>
-      </c>
-      <c r="C93" s="5" t="inlineStr">
-        <is>
-          <t>Yellow stamina when picked</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="inlineStr"/>
-      <c r="E93" s="5" t="inlineStr"/>
-      <c r="F93" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="G93" s="5" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H93" s="5" t="inlineStr">
-        <is>
-          <t>param:bonusNow</t>
         </is>
       </c>
     </row>
@@ -5709,13 +5697,13 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>Yellow stamina at each later campfire</t>
+          <t>Yellow stamina when picked</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr"/>
       <c r="E94" s="5" t="inlineStr"/>
       <c r="F94" s="13" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
@@ -5724,7 +5712,7 @@
       </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
-          <t>param:bonusFire</t>
+          <t>param:bonusNow</t>
         </is>
       </c>
     </row>
@@ -5739,13 +5727,13 @@
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Curse when picked</t>
+          <t>Yellow stamina at each later campfire</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr"/>
       <c r="E95" s="5" t="inlineStr"/>
       <c r="F95" s="13" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
@@ -5754,7 +5742,7 @@
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>param:curseNow</t>
+          <t>param:bonusFire</t>
         </is>
       </c>
     </row>
@@ -5769,13 +5757,13 @@
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Curse at each later campfire</t>
+          <t>Curse when picked</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr"/>
       <c r="E96" s="5" t="inlineStr"/>
       <c r="F96" s="13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
@@ -5784,7 +5772,7 @@
       </c>
       <c r="H96" s="5" t="inlineStr">
         <is>
-          <t>param:curseFire</t>
+          <t>param:curseNow</t>
         </is>
       </c>
     </row>
@@ -5799,56 +5787,52 @@
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Most Curse this card can ever add</t>
+          <t>Curse at each later campfire</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr"/>
       <c r="E97" s="5" t="inlineStr"/>
       <c r="F97" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>param:curseFire</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>Crown of Bad Decisions</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>Most Curse this card can ever add</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr"/>
+      <c r="E98" s="5" t="inlineStr"/>
+      <c r="F98" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="G97" s="5" t="inlineStr">
+      <c r="G98" s="5" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="H97" s="5" t="inlineStr">
+      <c r="H98" s="5" t="inlineStr">
         <is>
           <t>param:curseBudget</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="B98" s="12" t="inlineStr">
-        <is>
-          <t>Pandora's Pocket Gamble</t>
-        </is>
-      </c>
-      <c r="C98" s="12" t="inlineStr">
-        <is>
-          <t>Carried item weight</t>
-        </is>
-      </c>
-      <c r="D98" s="12" t="inlineStr"/>
-      <c r="E98" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F98" s="13" t="n">
-        <v>-10</v>
-      </c>
-      <c r="G98" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H98" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -5863,22 +5847,26 @@
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>Chance of a lucky roll</t>
+          <t>Carried item weight</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr"/>
-      <c r="E99" s="12" t="inlineStr"/>
+      <c r="E99" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F99" s="13" t="n">
-        <v>65</v>
+        <v>-10</v>
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H99" s="12" t="inlineStr">
         <is>
-          <t>param:chance</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -5893,22 +5881,22 @@
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>Yellow stamina on a lucky roll</t>
+          <t>Chance of a lucky roll</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr"/>
       <c r="E100" s="12" t="inlineStr"/>
       <c r="F100" s="13" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H100" s="12" t="inlineStr">
         <is>
-          <t>param:bonus</t>
+          <t>param:chance</t>
         </is>
       </c>
     </row>
@@ -5923,52 +5911,52 @@
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Injury on an unlucky roll</t>
+          <t>Yellow stamina on a lucky roll</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr"/>
       <c r="E101" s="12" t="inlineStr"/>
       <c r="F101" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G101" s="12" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H101" s="12" t="inlineStr">
+        <is>
+          <t>param:bonus</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="B102" s="12" t="inlineStr">
+        <is>
+          <t>Pandora's Pocket Gamble</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="inlineStr">
+        <is>
+          <t>Injury on an unlucky roll</t>
+        </is>
+      </c>
+      <c r="D102" s="12" t="inlineStr"/>
+      <c r="E102" s="12" t="inlineStr"/>
+      <c r="F102" s="13" t="n">
         <v>7.5</v>
       </c>
-      <c r="G101" s="12" t="inlineStr">
+      <c r="G102" s="12" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="H101" s="12" t="inlineStr">
+      <c r="H102" s="12" t="inlineStr">
         <is>
           <t>param:injury</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="5" t="n">
-        <v>52</v>
-      </c>
-      <c r="B102" s="5" t="inlineStr">
-        <is>
-          <t>Bootleg Scoutmaster Bugle</t>
-        </is>
-      </c>
-      <c r="C102" s="5" t="inlineStr">
-        <is>
-          <t>Yellow stamina per use</t>
-        </is>
-      </c>
-      <c r="D102" s="5" t="inlineStr"/>
-      <c r="E102" s="5" t="inlineStr"/>
-      <c r="F102" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="G102" s="5" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H102" s="5" t="inlineStr">
-        <is>
-          <t>param:bonus</t>
         </is>
       </c>
     </row>
@@ -5983,60 +5971,52 @@
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Injury per use</t>
+          <t>Yellow stamina per use</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr"/>
       <c r="E103" s="5" t="inlineStr"/>
       <c r="F103" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>param:bonus</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>Bootleg Scoutmaster Bugle</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>Injury per use</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr"/>
+      <c r="E104" s="5" t="inlineStr"/>
+      <c r="F104" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="G103" s="5" t="inlineStr">
+      <c r="G104" s="5" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="H103" s="5" t="inlineStr">
+      <c r="H104" s="5" t="inlineStr">
         <is>
           <t>param:injury</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="B104" s="12" t="inlineStr">
-        <is>
-          <t>Big Lollipop Crash</t>
-        </is>
-      </c>
-      <c r="C104" s="12" t="inlineStr">
-        <is>
-          <t>Sprint speed</t>
-        </is>
-      </c>
-      <c r="D104" s="12" t="inlineStr">
-        <is>
-          <t>while your sprint speed-up is on</t>
-        </is>
-      </c>
-      <c r="E104" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F104" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="G104" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H104" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -6051,22 +6031,30 @@
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>Sprint time before the speed-up</t>
-        </is>
-      </c>
-      <c r="D105" s="12" t="inlineStr"/>
-      <c r="E105" s="12" t="inlineStr"/>
+          <t>Sprint speed</t>
+        </is>
+      </c>
+      <c r="D105" s="12" t="inlineStr">
+        <is>
+          <t>while your sprint speed-up is on</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F105" s="13" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
-          <t>seconds</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H105" s="12" t="inlineStr">
         <is>
-          <t>param:buildup</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -6081,22 +6069,22 @@
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>Drowsy added</t>
+          <t>Sprint time before the speed-up</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr"/>
       <c r="E106" s="12" t="inlineStr"/>
       <c r="F106" s="13" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>seconds</t>
         </is>
       </c>
       <c r="H106" s="12" t="inlineStr">
         <is>
-          <t>param:drowsy</t>
+          <t>param:buildup</t>
         </is>
       </c>
     </row>
@@ -6111,52 +6099,52 @@
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>Time between Drowsy penalties</t>
+          <t>Drowsy added</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr"/>
       <c r="E107" s="12" t="inlineStr"/>
       <c r="F107" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G107" s="12" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H107" s="12" t="inlineStr">
+        <is>
+          <t>param:drowsy</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="B108" s="12" t="inlineStr">
+        <is>
+          <t>Big Lollipop Crash</t>
+        </is>
+      </c>
+      <c r="C108" s="12" t="inlineStr">
+        <is>
+          <t>Time between Drowsy penalties</t>
+        </is>
+      </c>
+      <c r="D108" s="12" t="inlineStr"/>
+      <c r="E108" s="12" t="inlineStr"/>
+      <c r="F108" s="13" t="n">
         <v>60</v>
       </c>
-      <c r="G107" s="12" t="inlineStr">
+      <c r="G108" s="12" t="inlineStr">
         <is>
           <t>seconds</t>
         </is>
       </c>
-      <c r="H107" s="12" t="inlineStr">
+      <c r="H108" s="12" t="inlineStr">
         <is>
           <t>param:cooldown</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="5" t="n">
-        <v>54</v>
-      </c>
-      <c r="B108" s="5" t="inlineStr">
-        <is>
-          <t>Piton Payment Plan</t>
-        </is>
-      </c>
-      <c r="C108" s="5" t="inlineStr">
-        <is>
-          <t>Share of each fall's Injury that is delayed</t>
-        </is>
-      </c>
-      <c r="D108" s="5" t="inlineStr"/>
-      <c r="E108" s="5" t="inlineStr"/>
-      <c r="F108" s="13" t="n">
-        <v>75</v>
-      </c>
-      <c r="G108" s="5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H108" s="5" t="inlineStr">
-        <is>
-          <t>param:defer</t>
         </is>
       </c>
     </row>
@@ -6171,22 +6159,22 @@
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Delay before the rest lands</t>
+          <t>Share of each fall's Injury that is delayed</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr"/>
       <c r="E109" s="5" t="inlineStr"/>
       <c r="F109" s="13" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>seconds</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr">
         <is>
-          <t>param:delay</t>
+          <t>param:defer</t>
         </is>
       </c>
     </row>
@@ -6201,56 +6189,52 @@
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>Share of the delayed Injury that still lands</t>
+          <t>Delay before the rest lands</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr"/>
       <c r="E110" s="5" t="inlineStr"/>
       <c r="F110" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>seconds</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="inlineStr">
+        <is>
+          <t>param:delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>Piton Payment Plan</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>Share of the delayed Injury that still lands</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr"/>
+      <c r="E111" s="5" t="inlineStr"/>
+      <c r="F111" s="13" t="n">
         <v>80</v>
       </c>
-      <c r="G110" s="5" t="inlineStr">
+      <c r="G111" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H110" s="5" t="inlineStr">
+      <c r="H111" s="5" t="inlineStr">
         <is>
           <t>param:keep</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="B111" s="12" t="inlineStr">
-        <is>
-          <t>Glass Scout Cannon</t>
-        </is>
-      </c>
-      <c r="C111" s="12" t="inlineStr">
-        <is>
-          <t>Max stamina</t>
-        </is>
-      </c>
-      <c r="D111" s="12" t="inlineStr"/>
-      <c r="E111" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F111" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="G111" s="12" t="inlineStr">
-        <is>
-          <t>stamina points</t>
-        </is>
-      </c>
-      <c r="H111" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -6265,7 +6249,7 @@
       </c>
       <c r="C112" s="12" t="inlineStr">
         <is>
-          <t>All Injury</t>
+          <t>Max stamina</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr"/>
@@ -6275,54 +6259,50 @@
         </is>
       </c>
       <c r="F112" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="G112" s="12" t="inlineStr">
+        <is>
+          <t>stamina points</t>
+        </is>
+      </c>
+      <c r="H112" s="12" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="B113" s="12" t="inlineStr">
+        <is>
+          <t>Glass Scout Cannon</t>
+        </is>
+      </c>
+      <c r="C113" s="12" t="inlineStr">
+        <is>
+          <t>All Injury</t>
+        </is>
+      </c>
+      <c r="D113" s="12" t="inlineStr"/>
+      <c r="E113" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F113" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="G112" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H112" s="12" t="inlineStr">
+      <c r="G113" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H113" s="12" t="inlineStr">
         <is>
           <t>mod:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="B113" s="5" t="inlineStr">
-        <is>
-          <t>Baggage Claim Escapee</t>
-        </is>
-      </c>
-      <c r="C113" s="5" t="inlineStr">
-        <is>
-          <t>Sprint speed</t>
-        </is>
-      </c>
-      <c r="D113" s="5" t="inlineStr">
-        <is>
-          <t>while you don't wear a backpack</t>
-        </is>
-      </c>
-      <c r="E113" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F113" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="G113" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H113" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -6337,7 +6317,7 @@
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>Jump height</t>
+          <t>Sprint speed</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
@@ -6351,7 +6331,7 @@
         </is>
       </c>
       <c r="F114" s="13" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
@@ -6360,7 +6340,7 @@
       </c>
       <c r="H114" s="5" t="inlineStr">
         <is>
-          <t>mod:1</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -6375,60 +6355,68 @@
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
+          <t>Jump height</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>while you don't wear a backpack</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F115" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t>mod:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>Baggage Claim Escapee</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
           <t>Sprint speed</t>
         </is>
       </c>
-      <c r="D115" s="5" t="inlineStr">
+      <c r="D116" s="5" t="inlineStr">
         <is>
           <t>while you wear a backpack</t>
         </is>
       </c>
-      <c r="E115" s="5" t="inlineStr">
+      <c r="E116" s="5" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
-      <c r="F115" s="13" t="n">
+      <c r="F116" s="13" t="n">
         <v>-5</v>
       </c>
-      <c r="G115" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H115" s="5" t="inlineStr">
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="inlineStr">
         <is>
           <t>mod:2</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="B116" s="12" t="inlineStr">
-        <is>
-          <t>Scout's Dishonor</t>
-        </is>
-      </c>
-      <c r="C116" s="12" t="inlineStr">
-        <is>
-          <t>Bonus cards (Common to Rare)</t>
-        </is>
-      </c>
-      <c r="D116" s="12" t="inlineStr"/>
-      <c r="E116" s="12" t="inlineStr"/>
-      <c r="F116" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G116" s="12" t="inlineStr">
-        <is>
-          <t>cards</t>
-        </is>
-      </c>
-      <c r="H116" s="12" t="inlineStr">
-        <is>
-          <t>param:bonusCards</t>
         </is>
       </c>
     </row>
@@ -6443,22 +6431,22 @@
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Curse when picked</t>
+          <t>Bonus cards (Common to Rare)</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr"/>
       <c r="E117" s="12" t="inlineStr"/>
       <c r="F117" s="13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>cards</t>
         </is>
       </c>
       <c r="H117" s="12" t="inlineStr">
         <is>
-          <t>param:curse</t>
+          <t>param:bonusCards</t>
         </is>
       </c>
     </row>
@@ -6473,82 +6461,82 @@
       </c>
       <c r="C118" s="12" t="inlineStr">
         <is>
-          <t>Cards in your next offer</t>
+          <t>Curse when picked</t>
         </is>
       </c>
       <c r="D118" s="12" t="inlineStr"/>
       <c r="E118" s="12" t="inlineStr"/>
       <c r="F118" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G118" s="12" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H118" s="12" t="inlineStr">
+        <is>
+          <t>param:curse</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="B119" s="12" t="inlineStr">
+        <is>
+          <t>Scout's Dishonor</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>Cards in your next offer</t>
+        </is>
+      </c>
+      <c r="D119" s="12" t="inlineStr"/>
+      <c r="E119" s="12" t="inlineStr"/>
+      <c r="F119" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G118" s="12" t="inlineStr">
+      <c r="G119" s="12" t="inlineStr">
         <is>
           <t>cards</t>
         </is>
       </c>
-      <c r="H118" s="12" t="inlineStr">
+      <c r="H119" s="12" t="inlineStr">
         <is>
           <t>param:nextOffer</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="5" t="n">
+    <row r="120">
+      <c r="A120" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="B119" s="5" t="inlineStr">
+      <c r="B120" s="5" t="inlineStr">
         <is>
           <t>BingBong Baggage Scanner</t>
         </is>
       </c>
-      <c r="C119" s="5" t="inlineStr">
+      <c r="C120" s="5" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="D119" s="5" t="inlineStr"/>
-      <c r="E119" s="5" t="inlineStr"/>
-      <c r="F119" s="13" t="n">
+      <c r="D120" s="5" t="inlineStr"/>
+      <c r="E120" s="5" t="inlineStr"/>
+      <c r="F120" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="G119" s="5" t="inlineStr">
+      <c r="G120" s="5" t="inlineStr">
         <is>
           <t>metres</t>
         </is>
       </c>
-      <c r="H119" s="5" t="inlineStr">
+      <c r="H120" s="5" t="inlineStr">
         <is>
           <t>param:radius</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="12" t="n">
-        <v>59</v>
-      </c>
-      <c r="B120" s="12" t="inlineStr">
-        <is>
-          <t>Medicinal Munchies</t>
-        </is>
-      </c>
-      <c r="C120" s="12" t="inlineStr">
-        <is>
-          <t>Needs at least this much Injury</t>
-        </is>
-      </c>
-      <c r="D120" s="12" t="inlineStr"/>
-      <c r="E120" s="12" t="inlineStr"/>
-      <c r="F120" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="G120" s="12" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H120" s="12" t="inlineStr">
-        <is>
-          <t>param:threshold</t>
         </is>
       </c>
     </row>
@@ -6563,118 +6551,114 @@
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>Injury removed</t>
+          <t>Needs at least this much Injury</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr"/>
       <c r="E121" s="12" t="inlineStr"/>
       <c r="F121" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="G121" s="12" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H121" s="12" t="inlineStr">
+        <is>
+          <t>param:threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="B122" s="12" t="inlineStr">
+        <is>
+          <t>Medicinal Munchies</t>
+        </is>
+      </c>
+      <c r="C122" s="12" t="inlineStr">
+        <is>
+          <t>Injury removed</t>
+        </is>
+      </c>
+      <c r="D122" s="12" t="inlineStr"/>
+      <c r="E122" s="12" t="inlineStr"/>
+      <c r="F122" s="13" t="n">
         <v>7.5</v>
       </c>
-      <c r="G121" s="12" t="inlineStr">
+      <c r="G122" s="12" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="H121" s="12" t="inlineStr">
+      <c r="H122" s="12" t="inlineStr">
         <is>
           <t>param:heal</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="5" t="n">
+    <row r="123">
+      <c r="A123" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="B122" s="5" t="inlineStr">
+      <c r="B123" s="5" t="inlineStr">
         <is>
           <t>Budget Checkpoint Flag</t>
         </is>
       </c>
-      <c r="C122" s="5" t="inlineStr">
+      <c r="C123" s="5" t="inlineStr">
         <is>
           <t>Injury after the revive</t>
         </is>
       </c>
-      <c r="D122" s="5" t="inlineStr"/>
-      <c r="E122" s="5" t="inlineStr"/>
-      <c r="F122" s="13" t="n">
+      <c r="D123" s="5" t="inlineStr"/>
+      <c r="E123" s="5" t="inlineStr"/>
+      <c r="F123" s="13" t="n">
         <v>40</v>
       </c>
-      <c r="G122" s="5" t="inlineStr">
+      <c r="G123" s="5" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="H122" s="5" t="inlineStr">
+      <c r="H123" s="5" t="inlineStr">
         <is>
           <t>param:injury</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="12" t="n">
+    <row r="124">
+      <c r="A124" s="12" t="n">
         <v>61</v>
       </c>
-      <c r="B123" s="12" t="inlineStr">
+      <c r="B124" s="12" t="inlineStr">
         <is>
           <t>Petrify Procrastination</t>
         </is>
       </c>
-      <c r="C123" s="12" t="inlineStr">
+      <c r="C124" s="12" t="inlineStr">
         <is>
           <t>Petrify build-up</t>
         </is>
       </c>
-      <c r="D123" s="12" t="inlineStr"/>
-      <c r="E123" s="12" t="inlineStr">
+      <c r="D124" s="12" t="inlineStr"/>
+      <c r="E124" s="12" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
-      <c r="F123" s="13" t="n">
+      <c r="F124" s="13" t="n">
         <v>-50</v>
       </c>
-      <c r="G123" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H123" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="B124" s="5" t="inlineStr">
-        <is>
-          <t>Fine Print</t>
-        </is>
-      </c>
-      <c r="C124" s="5" t="inlineStr">
-        <is>
-          <t>Max stamina</t>
-        </is>
-      </c>
-      <c r="D124" s="5" t="inlineStr"/>
-      <c r="E124" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F124" s="13" t="n">
-        <v>35</v>
-      </c>
-      <c r="G124" s="5" t="inlineStr">
-        <is>
-          <t>stamina points</t>
-        </is>
-      </c>
-      <c r="H124" s="5" t="inlineStr">
+      <c r="G124" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H124" s="12" t="inlineStr">
         <is>
           <t>mod:0</t>
         </is>
@@ -6691,56 +6675,56 @@
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
+          <t>Max stamina</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr"/>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F125" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>stamina points</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>Fine Print</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
           <t>Curse when the sacrifice is made</t>
         </is>
       </c>
-      <c r="D125" s="5" t="inlineStr"/>
-      <c r="E125" s="5" t="inlineStr"/>
-      <c r="F125" s="13" t="n">
+      <c r="D126" s="5" t="inlineStr"/>
+      <c r="E126" s="5" t="inlineStr"/>
+      <c r="F126" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G125" s="5" t="inlineStr">
+      <c r="G126" s="5" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="H125" s="5" t="inlineStr">
+      <c r="H126" s="5" t="inlineStr">
         <is>
           <t>param:curse</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="B126" s="12" t="inlineStr">
-        <is>
-          <t>Scoutmaster</t>
-        </is>
-      </c>
-      <c r="C126" s="12" t="inlineStr">
-        <is>
-          <t>Climbing stamina cost (set, ignores other cards)</t>
-        </is>
-      </c>
-      <c r="D126" s="12" t="inlineStr"/>
-      <c r="E126" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F126" s="13" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G126" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H126" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -6755,7 +6739,7 @@
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>Fall Injury (set, ignores other cards)</t>
+          <t>Climbing stamina cost (set, ignores other cards)</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr"/>
@@ -6774,7 +6758,7 @@
       </c>
       <c r="H127" s="12" t="inlineStr">
         <is>
-          <t>mod:1</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6773,7 @@
       </c>
       <c r="C128" s="12" t="inlineStr">
         <is>
-          <t>Sprint speed</t>
+          <t>Fall Injury (set, ignores other cards)</t>
         </is>
       </c>
       <c r="D128" s="12" t="inlineStr"/>
@@ -6799,50 +6783,50 @@
         </is>
       </c>
       <c r="F128" s="13" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G128" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H128" s="12" t="inlineStr">
+        <is>
+          <t>mod:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="B129" s="12" t="inlineStr">
+        <is>
+          <t>Scoutmaster</t>
+        </is>
+      </c>
+      <c r="C129" s="12" t="inlineStr">
+        <is>
+          <t>Sprint speed</t>
+        </is>
+      </c>
+      <c r="D129" s="12" t="inlineStr"/>
+      <c r="E129" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F129" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="G128" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H128" s="12" t="inlineStr">
+      <c r="G129" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H129" s="12" t="inlineStr">
         <is>
           <t>mod:2</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B129" s="5" t="inlineStr">
-        <is>
-          <t>The Eternal Campfire</t>
-        </is>
-      </c>
-      <c r="C129" s="5" t="inlineStr">
-        <is>
-          <t>Max stamina</t>
-        </is>
-      </c>
-      <c r="D129" s="5" t="inlineStr"/>
-      <c r="E129" s="5" t="inlineStr">
-        <is>
-          <t>You and teammates within 15 m</t>
-        </is>
-      </c>
-      <c r="F129" s="13" t="n">
-        <v>35</v>
-      </c>
-      <c r="G129" s="5" t="inlineStr">
-        <is>
-          <t>stamina points</t>
-        </is>
-      </c>
-      <c r="H129" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -6857,7 +6841,7 @@
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>All Injury</t>
+          <t>Max stamina</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr"/>
@@ -6867,16 +6851,16 @@
         </is>
       </c>
       <c r="F130" s="13" t="n">
-        <v>-60</v>
+        <v>35</v>
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>stamina points</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
         <is>
-          <t>mod:1</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -6891,7 +6875,7 @@
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>All negative status build-up</t>
+          <t>All Injury</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr"/>
@@ -6910,7 +6894,7 @@
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
-          <t>mod:2</t>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
@@ -6925,22 +6909,26 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>All negative status build-up</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr"/>
-      <c r="E132" s="5" t="inlineStr"/>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>You and teammates within 15 m</t>
+        </is>
+      </c>
       <c r="F132" s="13" t="n">
-        <v>15</v>
+        <v>-60</v>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>metres</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H132" s="5" t="inlineStr">
         <is>
-          <t>param:radius</t>
+          <t>mod:2</t>
         </is>
       </c>
     </row>
@@ -6955,22 +6943,22 @@
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>Injury after the revive</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr"/>
       <c r="E133" s="5" t="inlineStr"/>
       <c r="F133" s="13" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>metres</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>param:injury</t>
+          <t>param:radius</t>
         </is>
       </c>
     </row>
@@ -6985,27 +6973,57 @@
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>Stamina after the revive (at least)</t>
+          <t>Injury after the revive</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr"/>
       <c r="E134" s="5" t="inlineStr"/>
       <c r="F134" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="G134" s="5" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H134" s="5" t="inlineStr">
+        <is>
+          <t>param:injury</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>The Eternal Campfire</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>Stamina after the revive (at least)</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr"/>
+      <c r="E135" s="5" t="inlineStr"/>
+      <c r="F135" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="G134" s="5" t="inlineStr">
+      <c r="G135" s="5" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="H134" s="5" t="inlineStr">
+      <c r="H135" s="5" t="inlineStr">
         <is>
           <t>param:stamina</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H134"/>
+  <autoFilter ref="A1:H135"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/design/editable/card-sheet.xlsx
+++ b/design/editable/card-sheet.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cards'!$A$1:$G$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Numbers'!$A$1:$H$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Numbers'!$A$1:$H$145</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -761,7 +761,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Cold builds 35% slower while climbing blue ice.</t>
+          <t>Cold builds 30% slower, and another 50% slower while climbing blue ice.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr"/>
@@ -788,12 +788,12 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Hang still on a wall to recover 4 stamina per second.</t>
+          <t>Hang still on a wall to recover 10 stamina per second.</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Climb 30% slower.</t>
+          <t>Climb 10% slower.</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr"/>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Sprinting uses 15% less stamina.</t>
+          <t>Sprinting uses 30% less stamina.</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>Climbing uses 5% more stamina.</t>
+          <t>You get hungry 10% faster.</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr"/>
@@ -1032,14 +1032,10 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Hanging still on a wall drains 75% less stamina.</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>Lose 5 maximum stamina.</t>
-        </is>
-      </c>
+          <t>Hanging still on a wall costs no stamina, and you slip and slide 40% less.</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr"/>
       <c r="G13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1094,12 +1090,12 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Sprint 25% faster.</t>
+          <t>Sprint 35% faster.</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Lose 7.5 maximum stamina.</t>
+          <t>Lose 2.5 maximum stamina.</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr"/>
@@ -1183,7 +1179,7 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Heat builds 50% slower.</t>
+          <t>Heat builds 70% slower, and you get drowsy 30% slower.</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -1214,7 +1210,7 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Cold builds 50% slower.</t>
+          <t>Cold builds 70% slower, and huddling warms you 30% more.</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -1245,7 +1241,7 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Poison builds 35% slower.</t>
+          <t>Poison builds 70% slower and wears off 50% faster.</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -1276,7 +1272,7 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Spores build 35% slower.</t>
+          <t>Spores build 80% slower, and Poison 15% slower.</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr"/>
@@ -1303,7 +1299,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>New Thorns add 40% less status, rounded to the nearest whole thorn.</t>
+          <t>New Thorns add 80% less status, thorns take 50% less time to remove, and hits that are not falls hurt 20% less.</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr"/>
@@ -1330,7 +1326,7 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Heat wears off 60% faster.</t>
+          <t>Heat wears off 150% faster.</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -1361,7 +1357,7 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Cold wears off 60% faster.</t>
+          <t>Cold wears off 150% faster.</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -1450,7 +1446,7 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Healing removes 25% more Injury from you.</t>
+          <t>Healing removes 60% more Injury from you.</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr"/>
@@ -1709,7 +1705,7 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Held items weigh 35% less.</t>
+          <t>Held items weigh 65% less, and climbing with an item in hand uses 15% less stamina.</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr"/>
@@ -1736,7 +1732,7 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Once per biome, your first cooked meal is not consumed.</t>
+          <t>Cooked food fills you up 30% more, and once per biome your first cooked meal is not consumed.</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -1883,7 +1879,7 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>You and teammates within 8 m use 20% less climbing stamina.</t>
+          <t>You and teammates within 8 m use 10% less climbing stamina.</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -1914,14 +1910,10 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Healing items used on teammates remove 60% more Injury.</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>Healing items used on yourself remove 15% less Injury.</t>
-        </is>
-      </c>
+          <t>Healing items used on teammates remove 100% more Injury.</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr"/>
       <c r="G43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
@@ -1945,7 +1937,7 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Carried scouts weigh 35% less.</t>
+          <t>Carried scouts weigh 75% less, and you pull teammates up from 20% farther away.</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr"/>
@@ -1972,7 +1964,7 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Huddling warms you 35% more, from 35% farther away.</t>
+          <t>Huddling warms you 75% more, from farther away, and you get cold 20% slower.</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr"/>
@@ -2146,12 +2138,12 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Gain 30 yellow stamina now, then 20 at each later campfire.</t>
+          <t>Gain 40 yellow stamina now, then 30 at each later campfire.</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>Gain 5 Curse now, then 1 at each later campfire, up to 10 Curse in total.</t>
+          <t>Gain 3 Curse now, then 1 at each later campfire, up to 5 total.</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr"/>
@@ -2591,7 +2583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H135"/>
+  <dimension ref="A1:H145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2796,61 +2788,61 @@
           <t>Cold build-up</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr"/>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>-30</v>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>To The Bone</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Cold build-up</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>while you climb on blue ice</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="n">
-        <v>-35</v>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H6" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Pitonless Pit Stop</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Climb speed</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>-30</v>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
+        <v>-50</v>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
@@ -2865,52 +2857,56 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
+          <t>Climb speed</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>-10</v>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Pitonless Pit Stop</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
           <t>Stamina recovered per second</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>param:regenPerSecond</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Bing BOING</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>Double jump cooldown</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr"/>
-      <c r="E9" s="12" t="inlineStr"/>
-      <c r="F9" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>seconds</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>param:cooldown</t>
         </is>
       </c>
     </row>
@@ -2925,56 +2921,52 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Drowsy added</t>
+          <t>Double jump cooldown</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr"/>
       <c r="E10" s="12" t="inlineStr"/>
       <c r="F10" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>seconds</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>param:cooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Bing BOING</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Drowsy added</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr"/>
+      <c r="E11" s="12" t="inlineStr"/>
+      <c r="F11" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>param:drowsy</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Energy Drink Overdose</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Climb speed</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -2989,7 +2981,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Climbing stamina cost</t>
+          <t>Climb speed</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr"/>
@@ -2999,50 +2991,50 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Energy Drink Overdose</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Climbing stamina cost</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>mod:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>Tenderfoot Insurance</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>Fall Injury</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr"/>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>-25</v>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3049,7 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Dynamite Injury</t>
+          <t>Fall Injury</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr"/>
@@ -3067,50 +3059,50 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
+        <v>-25</v>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Tenderfoot Insurance</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Dynamite Injury</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr"/>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H14" s="12" t="inlineStr">
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
         <is>
           <t>mod:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Daddy</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Wall-grab reach</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3117,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>All stamina costs</t>
+          <t>Wall-grab reach</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr"/>
@@ -3135,50 +3127,50 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Daddy</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>All stamina costs</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>mod:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>Cookie Addiction</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>Max stamina</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr"/>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>stamina points</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -3193,7 +3185,7 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Hunger build-up</t>
+          <t>Max stamina</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr"/>
@@ -3203,46 +3195,50 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>stamina points</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>Cookie Addiction</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Hunger build-up</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr"/>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="inlineStr">
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
         <is>
           <t>mod:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Nic of Time</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Works below this much stamina</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="5" t="inlineStr"/>
-      <c r="F19" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>param:threshold</t>
         </is>
       </c>
     </row>
@@ -3257,13 +3253,13 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Stamina recovered</t>
+          <t>Works below this much stamina</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr"/>
       <c r="E20" s="5" t="inlineStr"/>
       <c r="F20" s="13" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
@@ -3272,7 +3268,7 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>param:restore</t>
+          <t>param:threshold</t>
         </is>
       </c>
     </row>
@@ -3287,56 +3283,52 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Cooldown</t>
+          <t>Stamina recovered</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr"/>
       <c r="E21" s="5" t="inlineStr"/>
       <c r="F21" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>param:restore</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Nic of Time</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="13" t="n">
         <v>180</v>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>seconds</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>param:cooldown</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>Hasty Badge Training</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>Sprint stamina cost</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr"/>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="n">
-        <v>-15</v>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3343,7 @@
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Climbing stamina cost</t>
+          <t>Sprint stamina cost</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr"/>
@@ -3361,7 +3353,7 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>5</v>
+        <v>-30</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -3370,41 +3362,41 @@
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Hasty Badge Training</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Hunger build-up</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr"/>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
           <t>mod:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Max stamina</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F24" s="13" t="n">
-        <v>-5</v>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>stamina points</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -3419,52 +3411,56 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
+          <t>Slip and slide force</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>-40</v>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
           <t>Hanging drain refunded</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr"/>
-      <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="13" t="n">
-        <v>75</v>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>param:refund</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>Meditation</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>Crouch time required</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr"/>
-      <c r="E26" s="12" t="inlineStr"/>
-      <c r="F26" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G26" s="12" t="inlineStr">
-        <is>
-          <t>seconds</t>
-        </is>
-      </c>
-      <c r="H26" s="12" t="inlineStr">
-        <is>
-          <t>param:hold</t>
         </is>
       </c>
     </row>
@@ -3479,56 +3475,52 @@
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Yellow stamina gained</t>
+          <t>Crouch time required</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr"/>
       <c r="E27" s="12" t="inlineStr"/>
       <c r="F27" s="13" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>seconds</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>param:bonus</t>
+          <t>param:hold</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>I'm getting Scoutmastered</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Sprint speed</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="A28" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>Meditation</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>Yellow stamina gained</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr"/>
+      <c r="E28" s="12" t="inlineStr"/>
       <c r="F28" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>param:bonus</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3535,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Max stamina</t>
+          <t>Sprint speed</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr"/>
@@ -3553,54 +3545,50 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>-7.5</v>
+        <v>35</v>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>I'm getting Scoutmastered</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Max stamina</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
           <t>stamina points</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>mod:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>Endurance Badge</t>
-        </is>
-      </c>
-      <c r="C30" s="12" t="inlineStr">
-        <is>
-          <t>Climbing stamina cost</t>
-        </is>
-      </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>while your climbing boost is on</t>
-        </is>
-      </c>
-      <c r="E30" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F30" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="G30" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H30" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -3615,22 +3603,30 @@
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Climbing time before the boost</t>
-        </is>
-      </c>
-      <c r="D31" s="12" t="inlineStr"/>
-      <c r="E31" s="12" t="inlineStr"/>
+          <t>Climbing stamina cost</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>while your climbing boost is on</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F31" s="13" t="n">
-        <v>2</v>
+        <v>-40</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>seconds</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>param:buildup</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3641,7 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Boost length</t>
+          <t>Climbing time before the boost</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr"/>
@@ -3660,73 +3656,69 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
+          <t>param:buildup</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>Endurance Badge</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>Boost length</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr"/>
+      <c r="E33" s="12" t="inlineStr"/>
+      <c r="F33" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>seconds</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
           <t>param:boost</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="5" t="n">
+    <row r="34">
+      <c r="A34" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Marshmallow Morale</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Hunger removed by cooked food</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr"/>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F33" s="13" t="n">
+      <c r="D34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="n">
         <v>-10</v>
       </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="B34" s="12" t="inlineStr">
-        <is>
-          <t>Cool, Calm, and Collected.</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>Heat build-up</t>
-        </is>
-      </c>
-      <c r="D34" s="12" t="inlineStr"/>
-      <c r="E34" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F34" s="13" t="n">
-        <v>-50</v>
-      </c>
-      <c r="G34" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H34" s="12" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>mod:0</t>
         </is>
@@ -3743,7 +3735,7 @@
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Cold build-up</t>
+          <t>Heat build-up</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr"/>
@@ -3753,7 +3745,7 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>10</v>
+        <v>-70</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -3762,60 +3754,60 @@
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>Cool, Calm, and Collected.</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>Drowsy build-up</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr"/>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>-30</v>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
           <t>mod:1</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>Just hot.</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>Cool, Calm, and Collected.</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
         <is>
           <t>Cold build-up</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr"/>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F36" s="13" t="n">
-        <v>-50</v>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Just hot.</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Heat build-up</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr"/>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="D37" s="12" t="inlineStr"/>
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>You</t>
         </is>
@@ -3823,101 +3815,101 @@
       <c r="F37" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="inlineStr">
+        <is>
+          <t>mod:2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Just hot.</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Cold build-up</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr"/>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>-70</v>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Just hot.</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Huddle radius and cold removal</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr"/>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>mod:1</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="B38" s="12" t="inlineStr">
-        <is>
-          <t>Antidote Enthusiast</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="inlineStr">
-        <is>
-          <t>Poison build-up</t>
-        </is>
-      </c>
-      <c r="D38" s="12" t="inlineStr"/>
-      <c r="E38" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F38" s="13" t="n">
-        <v>-35</v>
-      </c>
-      <c r="G38" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H38" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>Antidote Enthusiast</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Just hot.</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>Heat build-up</t>
         </is>
       </c>
-      <c r="D39" s="12" t="inlineStr"/>
-      <c r="E39" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F39" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G39" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
-          <t>mod:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="B40" s="12" t="inlineStr">
-        <is>
-          <t>Antidote Enthusiast</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>Cold build-up</t>
-        </is>
-      </c>
-      <c r="D40" s="12" t="inlineStr"/>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr"/>
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>You</t>
         </is>
@@ -3925,46 +3917,46 @@
       <c r="F40" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="G40" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H40" s="12" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>mod:2</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>ROOTS Survivor</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>Spores build-up</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr"/>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="A41" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>Antidote Enthusiast</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>Poison build-up</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr"/>
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>-35</v>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
+        <v>-70</v>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="inlineStr">
         <is>
           <t>mod:0</t>
         </is>
@@ -3972,16 +3964,16 @@
     </row>
     <row r="42">
       <c r="A42" s="12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>Cactus? What Cactus?</t>
+          <t>Antidote Enthusiast</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>Thorns build-up</t>
+          <t>Poison decay</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr"/>
@@ -3991,7 +3983,7 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>-40</v>
+        <v>50</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -4000,213 +3992,209 @@
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
+          <t>mod:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>Antidote Enthusiast</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>Heat build-up</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr"/>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F43" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H43" s="12" t="inlineStr">
+        <is>
+          <t>mod:2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>Antidote Enthusiast</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>Cold build-up</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr"/>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F44" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t>mod:3</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>ROOTS Survivor</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Spores build-up</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr"/>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>-80</v>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
           <t>mod:0</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>Aloe</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>Heat decay</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr"/>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F43" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>ROOTS Survivor</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Poison build-up</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr"/>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F46" s="13" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>mod:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>Cactus? What Cactus?</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>Thorns build-up</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr"/>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>-80</v>
+      </c>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H47" s="12" t="inlineStr">
         <is>
           <t>mod:0</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>Aloe</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>Heat build-up</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr"/>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F44" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>mod:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="B45" s="12" t="inlineStr">
-        <is>
-          <t>Heat Pack</t>
-        </is>
-      </c>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>Cold decay</t>
-        </is>
-      </c>
-      <c r="D45" s="12" t="inlineStr"/>
-      <c r="E45" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F45" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H45" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="B46" s="12" t="inlineStr">
-        <is>
-          <t>Heat Pack</t>
-        </is>
-      </c>
-      <c r="C46" s="12" t="inlineStr">
-        <is>
-          <t>Cold build-up</t>
-        </is>
-      </c>
-      <c r="D46" s="12" t="inlineStr"/>
-      <c r="E46" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F46" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H46" s="12" t="inlineStr">
-        <is>
-          <t>mod:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>Fartberry Fitness</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>Climbing stamina cost</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>while you have more than 20 Poison</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F47" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
-        </is>
-      </c>
-    </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>Fartberry Fitness</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>Poison decay</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr"/>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="A48" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>Cactus? What Cactus?</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>Thorn removal time</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="inlineStr"/>
+      <c r="E48" s="12" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>-10</v>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
+        <v>-50</v>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H48" s="12" t="inlineStr">
         <is>
           <t>mod:1</t>
         </is>
@@ -4214,123 +4202,135 @@
     </row>
     <row r="49">
       <c r="A49" s="12" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>BingBong</t>
+          <t>Cactus? What Cactus?</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Time between powers</t>
+          <t>Non-fall Injury</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr"/>
-      <c r="E49" s="12" t="inlineStr"/>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F49" s="13" t="n">
-        <v>300</v>
+        <v>-20</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>seconds</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H49" s="12" t="inlineStr">
         <is>
-          <t>param:interval</t>
+          <t>mod:2</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="B50" s="12" t="inlineStr">
-        <is>
-          <t>BingBong</t>
-        </is>
-      </c>
-      <c r="C50" s="12" t="inlineStr">
-        <is>
-          <t>Power length</t>
-        </is>
-      </c>
-      <c r="D50" s="12" t="inlineStr"/>
-      <c r="E50" s="12" t="inlineStr"/>
+      <c r="A50" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Aloe</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Heat decay</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr"/>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F50" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="G50" s="12" t="inlineStr">
-        <is>
-          <t>seconds</t>
-        </is>
-      </c>
-      <c r="H50" s="12" t="inlineStr">
-        <is>
-          <t>param:duration</t>
+        <v>150</v>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="B51" s="12" t="inlineStr">
-        <is>
-          <t>BingBong</t>
-        </is>
-      </c>
-      <c r="C51" s="12" t="inlineStr">
-        <is>
-          <t>Low Gravity strength (the mushroom is 3)</t>
-        </is>
-      </c>
-      <c r="D51" s="12" t="inlineStr"/>
-      <c r="E51" s="12" t="inlineStr"/>
+      <c r="A51" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Aloe</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Heat build-up</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr"/>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F51" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>strength</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>param:lowGravity</t>
+        <v>5</v>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>Injury healed by items (received)</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr"/>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="A52" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>Heat Pack</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>Cold decay</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr"/>
+      <c r="E52" s="12" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr">
+        <v>150</v>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H52" s="12" t="inlineStr">
         <is>
           <t>mod:0</t>
         </is>
@@ -4338,294 +4338,298 @@
     </row>
     <row r="53">
       <c r="A53" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>Heat Pack</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>Cold build-up</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr"/>
+      <c r="E53" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F53" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G53" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H53" s="12" t="inlineStr">
+        <is>
+          <t>mod:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Fartberry Fitness</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Climbing stamina cost</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>while you have more than 20 Poison</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F54" s="13" t="n">
+        <v>-40</v>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Fartberry Fitness</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Poison decay</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr"/>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F55" s="13" t="n">
+        <v>-10</v>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>mod:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>BingBong</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>Time between powers</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="inlineStr"/>
+      <c r="E56" s="12" t="inlineStr"/>
+      <c r="F56" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>seconds</t>
+        </is>
+      </c>
+      <c r="H56" s="12" t="inlineStr">
+        <is>
+          <t>param:interval</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>BingBong</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>Power length</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr"/>
+      <c r="E57" s="12" t="inlineStr"/>
+      <c r="F57" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="G57" s="12" t="inlineStr">
+        <is>
+          <t>seconds</t>
+        </is>
+      </c>
+      <c r="H57" s="12" t="inlineStr">
+        <is>
+          <t>param:duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>BingBong</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>Low Gravity strength (the mushroom is 3)</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="inlineStr"/>
+      <c r="E58" s="12" t="inlineStr"/>
+      <c r="F58" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t>strength</t>
+        </is>
+      </c>
+      <c r="H58" s="12" t="inlineStr">
+        <is>
+          <t>param:lowGravity</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Injury healed by items (received)</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr"/>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F59" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="B53" s="12" t="inlineStr">
+      <c r="B60" s="12" t="inlineStr">
         <is>
           <t>Walk It Off</t>
         </is>
       </c>
-      <c r="C53" s="12" t="inlineStr">
+      <c r="C60" s="12" t="inlineStr">
         <is>
           <t>Climbing stamina cost</t>
         </is>
       </c>
-      <c r="D53" s="12" t="inlineStr">
+      <c r="D60" s="12" t="inlineStr">
         <is>
           <t>while you have 20+ Injury</t>
         </is>
       </c>
-      <c r="E53" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F53" s="13" t="n">
+      <c r="E60" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F60" s="13" t="n">
         <v>-25</v>
       </c>
-      <c r="G53" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H53" s="12" t="inlineStr">
+      <c r="G60" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H60" s="12" t="inlineStr">
         <is>
           <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="B54" s="12" t="inlineStr">
-        <is>
-          <t>Walk It Off</t>
-        </is>
-      </c>
-      <c r="C54" s="12" t="inlineStr">
-        <is>
-          <t>Sprint stamina cost</t>
-        </is>
-      </c>
-      <c r="D54" s="12" t="inlineStr">
-        <is>
-          <t>while you have 20+ Injury</t>
-        </is>
-      </c>
-      <c r="E54" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F54" s="13" t="n">
-        <v>-25</v>
-      </c>
-      <c r="G54" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H54" s="12" t="inlineStr">
-        <is>
-          <t>mod:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="B55" s="12" t="inlineStr">
-        <is>
-          <t>Walk It Off</t>
-        </is>
-      </c>
-      <c r="C55" s="12" t="inlineStr">
-        <is>
-          <t>All Injury</t>
-        </is>
-      </c>
-      <c r="D55" s="12" t="inlineStr"/>
-      <c r="E55" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F55" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="G55" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H55" s="12" t="inlineStr">
-        <is>
-          <t>mod:2</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>Discount Cure-All</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>Needs at least this much of the status</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr"/>
-      <c r="E56" s="5" t="inlineStr"/>
-      <c r="F56" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="G56" s="5" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>param:threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>Discount Cure-All</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>Status removed</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr"/>
-      <c r="E57" s="5" t="inlineStr"/>
-      <c r="F57" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>param:remove</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>Gourmand's Gut</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>Hunger removed by food</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr"/>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F58" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H58" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="B59" s="12" t="inlineStr">
-        <is>
-          <t>Book of Broken Bones</t>
-        </is>
-      </c>
-      <c r="C59" s="12" t="inlineStr">
-        <is>
-          <t>Curse added by revival</t>
-        </is>
-      </c>
-      <c r="D59" s="12" t="inlineStr"/>
-      <c r="E59" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F59" s="13" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G59" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H59" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>Mini Tenacity</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>Extra status removed</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr"/>
-      <c r="E60" s="5" t="inlineStr"/>
-      <c r="F60" s="13" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G60" s="5" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H60" s="5" t="inlineStr">
-        <is>
-          <t>param:bonus</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="12" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>Bing Bong's Baggage</t>
+          <t>Walk It Off</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>All carried weight</t>
-        </is>
-      </c>
-      <c r="D61" s="12" t="inlineStr"/>
+          <t>Sprint stamina cost</t>
+        </is>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>while you have 20+ Injury</t>
+        </is>
+      </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
@@ -4634,124 +4638,116 @@
       </c>
       <c r="H61" s="12" t="inlineStr">
         <is>
-          <t>mod:0</t>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>Carry-On Only</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>Held item weight</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr"/>
-      <c r="E62" s="5" t="inlineStr">
+      <c r="A62" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>Walk It Off</t>
+        </is>
+      </c>
+      <c r="C62" s="12" t="inlineStr">
+        <is>
+          <t>All Injury</t>
+        </is>
+      </c>
+      <c r="D62" s="12" t="inlineStr"/>
+      <c r="E62" s="12" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>-45</v>
-      </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H62" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
+        <v>5</v>
+      </c>
+      <c r="G62" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H62" s="12" t="inlineStr">
+        <is>
+          <t>mod:2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Carry-On Only</t>
+          <t>Discount Cure-All</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Backpack content weight</t>
+          <t>Needs at least this much of the status</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr"/>
-      <c r="E63" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="E63" s="5" t="inlineStr"/>
       <c r="F63" s="13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>points</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>mod:1</t>
+          <t>param:threshold</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="B64" s="12" t="inlineStr">
-        <is>
-          <t>Idol Hands</t>
-        </is>
-      </c>
-      <c r="C64" s="12" t="inlineStr">
-        <is>
-          <t>Held item weight</t>
-        </is>
-      </c>
-      <c r="D64" s="12" t="inlineStr"/>
-      <c r="E64" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="A64" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Discount Cure-All</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Status removed</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr"/>
+      <c r="E64" s="5" t="inlineStr"/>
       <c r="F64" s="13" t="n">
-        <v>-35</v>
-      </c>
-      <c r="G64" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H64" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
+        <v>25</v>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>param:remove</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Cook It, Keep It</t>
+          <t>Gourmand's Gut</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Uncooked food nutrition</t>
+          <t>Hunger removed by food</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr"/>
@@ -4761,7 +4757,7 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>-15</v>
+        <v>20</v>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
@@ -4776,16 +4772,16 @@
     </row>
     <row r="66">
       <c r="A66" s="12" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B66" s="12" t="inlineStr">
         <is>
-          <t>Cooking Badge Deluxe</t>
+          <t>Book of Broken Bones</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>Hunger removed by cooked food</t>
+          <t>Curse added by revival</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr"/>
@@ -4795,7 +4791,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>50</v>
+        <v>-100</v>
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
@@ -4809,83 +4805,91 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="B67" s="12" t="inlineStr">
-        <is>
-          <t>Cooking Badge Deluxe</t>
-        </is>
-      </c>
-      <c r="C67" s="12" t="inlineStr">
-        <is>
-          <t>Poison added</t>
-        </is>
-      </c>
-      <c r="D67" s="12" t="inlineStr"/>
-      <c r="E67" s="12" t="inlineStr"/>
+      <c r="A67" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Mini Tenacity</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Extra status removed</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr"/>
+      <c r="E67" s="5" t="inlineStr"/>
       <c r="F67" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="G67" s="12" t="inlineStr">
+        <v>7.5</v>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="H67" s="12" t="inlineStr">
-        <is>
-          <t>param:poison</t>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>param:bonus</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>Clown Luggage Special</t>
-        </is>
-      </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>Bonus cards</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr"/>
-      <c r="E68" s="5" t="inlineStr"/>
+      <c r="A68" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="B68" s="12" t="inlineStr">
+        <is>
+          <t>Bing Bong's Baggage</t>
+        </is>
+      </c>
+      <c r="C68" s="12" t="inlineStr">
+        <is>
+          <t>All carried weight</t>
+        </is>
+      </c>
+      <c r="D68" s="12" t="inlineStr"/>
+      <c r="E68" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F68" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G68" s="5" t="inlineStr">
-        <is>
-          <t>cards</t>
-        </is>
-      </c>
-      <c r="H68" s="5" t="inlineStr">
-        <is>
-          <t>param:bonusCards</t>
+        <v>-50</v>
+      </c>
+      <c r="G68" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H68" s="12" t="inlineStr">
+        <is>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Clown Luggage Special</t>
+          <t>Carry-On Only</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Possible penalty: climbing stamina cost</t>
+          <t>Held item weight</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr"/>
-      <c r="E69" s="5" t="inlineStr"/>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F69" s="13" t="n">
-        <v>10</v>
+        <v>-45</v>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
@@ -4894,28 +4898,32 @@
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>param:climbPenalty</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Clown Luggage Special</t>
+          <t>Carry-On Only</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Possible penalty: sprint stamina cost</t>
+          <t>Backpack content weight</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr"/>
-      <c r="E70" s="5" t="inlineStr"/>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F70" s="13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
@@ -4924,137 +4932,145 @@
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>param:sprintPenalty</t>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>Clown Luggage Special</t>
-        </is>
-      </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>Possible penalty: all Injury</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="inlineStr"/>
-      <c r="E71" s="5" t="inlineStr"/>
+      <c r="A71" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>Idol Hands</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>Held item weight</t>
+        </is>
+      </c>
+      <c r="D71" s="12" t="inlineStr"/>
+      <c r="E71" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F71" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G71" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>param:injuryPenalty</t>
+        <v>-65</v>
+      </c>
+      <c r="G71" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H71" s="12" t="inlineStr">
+        <is>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>Clown Luggage Special</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>Possible penalty: Hunger build-up</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr"/>
-      <c r="E72" s="5" t="inlineStr"/>
+      <c r="A72" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="B72" s="12" t="inlineStr">
+        <is>
+          <t>Idol Hands</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="inlineStr">
+        <is>
+          <t>Climbing stamina cost</t>
+        </is>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>while you climb with an item in your hands</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F72" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H72" s="5" t="inlineStr">
-        <is>
-          <t>param:hungerPenalty</t>
+        <v>-15</v>
+      </c>
+      <c r="G72" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H72" s="12" t="inlineStr">
+        <is>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="B73" s="12" t="inlineStr">
-        <is>
-          <t>Rule Zero</t>
-        </is>
-      </c>
-      <c r="C73" s="12" t="inlineStr">
-        <is>
-          <t>Climbing stamina cost</t>
-        </is>
-      </c>
-      <c r="D73" s="12" t="inlineStr"/>
-      <c r="E73" s="12" t="inlineStr">
-        <is>
-          <t>Teammates within 8 m</t>
+      <c r="A73" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Cook It, Keep It</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Hunger removed by cooked food</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr"/>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>-20</v>
-      </c>
-      <c r="G73" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H73" s="12" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
         <is>
           <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="B74" s="12" t="inlineStr">
-        <is>
-          <t>Rule Zero</t>
-        </is>
-      </c>
-      <c r="C74" s="12" t="inlineStr">
-        <is>
-          <t>Climbing stamina cost</t>
-        </is>
-      </c>
-      <c r="D74" s="12" t="inlineStr">
-        <is>
-          <t>while a teammate is near you</t>
-        </is>
-      </c>
-      <c r="E74" s="12" t="inlineStr">
+      <c r="A74" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>Cook It, Keep It</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>Uncooked food nutrition</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr"/>
+      <c r="E74" s="5" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>-20</v>
-      </c>
-      <c r="G74" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H74" s="12" t="inlineStr">
+        <v>-15</v>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
         <is>
           <t>mod:1</t>
         </is>
@@ -5062,30 +5078,26 @@
     </row>
     <row r="75">
       <c r="A75" s="12" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>Rule Zero</t>
+          <t>Cooking Badge Deluxe</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Climbing stamina cost</t>
-        </is>
-      </c>
-      <c r="D75" s="12" t="inlineStr">
-        <is>
-          <t>while no teammate is near you</t>
-        </is>
-      </c>
+          <t>Hunger removed by cooked food</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="inlineStr"/>
       <c r="E75" s="12" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
@@ -5094,96 +5106,88 @@
       </c>
       <c r="H75" s="12" t="inlineStr">
         <is>
-          <t>mod:2</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="12" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B76" s="12" t="inlineStr">
         <is>
-          <t>Rule Zero</t>
+          <t>Cooking Badge Deluxe</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Poison added</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr"/>
       <c r="E76" s="12" t="inlineStr"/>
       <c r="F76" s="13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
-          <t>metres</t>
+          <t>points</t>
         </is>
       </c>
       <c r="H76" s="12" t="inlineStr">
         <is>
-          <t>param:radius</t>
+          <t>param:poison</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>First Aid Badge</t>
+          <t>Clown Luggage Special</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Injury healed by items (given to teammates)</t>
+          <t>Bonus cards</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr"/>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="E77" s="5" t="inlineStr"/>
       <c r="F77" s="13" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>cards</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>mod:0</t>
+          <t>param:bonusCards</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>First Aid Badge</t>
+          <t>Clown Luggage Special</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Injury healed by items (used on yourself)</t>
+          <t>Possible penalty: climbing stamina cost</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr"/>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="E78" s="5" t="inlineStr"/>
       <c r="F78" s="13" t="n">
-        <v>-15</v>
+        <v>10</v>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
@@ -5192,66 +5196,58 @@
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>mod:1</t>
+          <t>param:climbPenalty</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="B79" s="12" t="inlineStr">
-        <is>
-          <t>Human Carry-On</t>
-        </is>
-      </c>
-      <c r="C79" s="12" t="inlineStr">
-        <is>
-          <t>Carried scout weight</t>
-        </is>
-      </c>
-      <c r="D79" s="12" t="inlineStr"/>
-      <c r="E79" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="A79" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Clown Luggage Special</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Possible penalty: sprint stamina cost</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr"/>
+      <c r="E79" s="5" t="inlineStr"/>
       <c r="F79" s="13" t="n">
-        <v>-35</v>
-      </c>
-      <c r="G79" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H79" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
+        <v>10</v>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>param:sprintPenalty</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Happy Camper Huddle</t>
+          <t>Clown Luggage Special</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Huddle radius and cold removal</t>
+          <t>Possible penalty: all Injury</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr"/>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="E80" s="5" t="inlineStr"/>
       <c r="F80" s="13" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
@@ -5260,126 +5256,138 @@
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
+          <t>param:injuryPenalty</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Clown Luggage Special</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Possible penalty: Hunger build-up</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr"/>
+      <c r="E81" s="5" t="inlineStr"/>
+      <c r="F81" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>param:hungerPenalty</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="B82" s="12" t="inlineStr">
+        <is>
+          <t>Rule Zero</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>Climbing stamina cost</t>
+        </is>
+      </c>
+      <c r="D82" s="12" t="inlineStr"/>
+      <c r="E82" s="12" t="inlineStr">
+        <is>
+          <t>Teammates within 8 m</t>
+        </is>
+      </c>
+      <c r="F82" s="13" t="n">
+        <v>-10</v>
+      </c>
+      <c r="G82" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H82" s="12" t="inlineStr">
+        <is>
           <t>mod:0</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="B81" s="12" t="inlineStr">
-        <is>
-          <t>Otto-Matic Clutch</t>
-        </is>
-      </c>
-      <c r="C81" s="12" t="inlineStr">
-        <is>
-          <t>Yellow stamina for both scouts</t>
-        </is>
-      </c>
-      <c r="D81" s="12" t="inlineStr"/>
-      <c r="E81" s="12" t="inlineStr"/>
-      <c r="F81" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="G81" s="12" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H81" s="12" t="inlineStr">
-        <is>
-          <t>param:bonus</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>You're alright, you're alright</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>Helping-hand reach</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr"/>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F82" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="G82" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H82" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
-        </is>
-      </c>
-    </row>
     <row r="83">
-      <c r="A83" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="B83" s="5" t="inlineStr">
-        <is>
-          <t>You're alright, you're alright</t>
-        </is>
-      </c>
-      <c r="C83" s="5" t="inlineStr">
-        <is>
-          <t>Stamina cost to start a pull</t>
-        </is>
-      </c>
-      <c r="D83" s="5" t="inlineStr"/>
-      <c r="E83" s="5" t="inlineStr"/>
+      <c r="A83" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="B83" s="12" t="inlineStr">
+        <is>
+          <t>Rule Zero</t>
+        </is>
+      </c>
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t>Climbing stamina cost</t>
+        </is>
+      </c>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>while a teammate is near you</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F83" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H83" s="5" t="inlineStr">
-        <is>
-          <t>param:stamina</t>
+        <v>-10</v>
+      </c>
+      <c r="G83" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H83" s="12" t="inlineStr">
+        <is>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="12" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B84" s="12" t="inlineStr">
         <is>
-          <t>Take One for the Troop</t>
+          <t>Rule Zero</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>All Injury</t>
-        </is>
-      </c>
-      <c r="D84" s="12" t="inlineStr"/>
+          <t>Climbing stamina cost</t>
+        </is>
+      </c>
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t>while no teammate is near you</t>
+        </is>
+      </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
-          <t>Teammates within 6 m</t>
+          <t>You</t>
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
@@ -5388,17 +5396,17 @@
       </c>
       <c r="H84" s="12" t="inlineStr">
         <is>
-          <t>mod:0</t>
+          <t>mod:2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="12" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>Take One for the Troop</t>
+          <t>Rule Zero</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
@@ -5409,7 +5417,7 @@
       <c r="D85" s="12" t="inlineStr"/>
       <c r="E85" s="12" t="inlineStr"/>
       <c r="F85" s="13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
@@ -5423,591 +5431,615 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="B86" s="12" t="inlineStr">
-        <is>
-          <t>Take One for the Troop</t>
-        </is>
-      </c>
-      <c r="C86" s="12" t="inlineStr">
-        <is>
-          <t>Share of the prevented Injury you take</t>
-        </is>
-      </c>
-      <c r="D86" s="12" t="inlineStr"/>
-      <c r="E86" s="12" t="inlineStr"/>
+      <c r="A86" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>First Aid Badge</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>Injury healed by items (given to teammates)</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr"/>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F86" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="G86" s="12" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H86" s="12" t="inlineStr">
-        <is>
-          <t>param:absorb</t>
+        <v>100</v>
+      </c>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="12" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>Take One for the Troop</t>
+          <t>Human Carry-On</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>Most Injury you take per hit</t>
+          <t>Carried scout weight</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr"/>
-      <c r="E87" s="12" t="inlineStr"/>
+      <c r="E87" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F87" s="13" t="n">
-        <v>5</v>
+        <v>-75</v>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H87" s="12" t="inlineStr">
         <is>
-          <t>param:cap</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="B88" s="5" t="inlineStr">
-        <is>
-          <t>Friendship Bugle Choir</t>
-        </is>
-      </c>
-      <c r="C88" s="5" t="inlineStr">
-        <is>
-          <t>Max stamina</t>
-        </is>
-      </c>
-      <c r="D88" s="5" t="inlineStr"/>
-      <c r="E88" s="5" t="inlineStr">
-        <is>
-          <t>Teammates within 8 m</t>
+      <c r="A88" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="B88" s="12" t="inlineStr">
+        <is>
+          <t>Human Carry-On</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>Helping-hand reach</t>
+        </is>
+      </c>
+      <c r="D88" s="12" t="inlineStr"/>
+      <c r="E88" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G88" s="5" t="inlineStr">
-        <is>
-          <t>stamina points</t>
-        </is>
-      </c>
-      <c r="H88" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
+        <v>20</v>
+      </c>
+      <c r="G88" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H88" s="12" t="inlineStr">
+        <is>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Friendship Bugle Choir</t>
+          <t>Happy Camper Huddle</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Max stamina</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="inlineStr">
-        <is>
-          <t>while a teammate is near you</t>
-        </is>
-      </c>
+          <t>Huddle radius and cold removal</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr"/>
       <c r="E89" s="5" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>stamina points</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>mod:1</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>Friendship Bugle Choir</t>
+          <t>Happy Camper Huddle</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Cold build-up</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr"/>
-      <c r="E90" s="5" t="inlineStr"/>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F90" s="13" t="n">
-        <v>8</v>
+        <v>-20</v>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>metres</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H90" s="5" t="inlineStr">
         <is>
-          <t>param:radius</t>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="12" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>Scout Cannon Legs</t>
+          <t>Otto-Matic Clutch</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>Sprint speed</t>
+          <t>Yellow stamina for both scouts</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr"/>
-      <c r="E91" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="E91" s="12" t="inlineStr"/>
       <c r="F91" s="13" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>points</t>
         </is>
       </c>
       <c r="H91" s="12" t="inlineStr">
         <is>
+          <t>param:bonus</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>You're alright, you're alright</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Helping-hand reach</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr"/>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F92" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
           <t>mod:0</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="B92" s="12" t="inlineStr">
-        <is>
-          <t>Scout Cannon Legs</t>
-        </is>
-      </c>
-      <c r="C92" s="12" t="inlineStr">
-        <is>
-          <t>Jump height</t>
-        </is>
-      </c>
-      <c r="D92" s="12" t="inlineStr"/>
-      <c r="E92" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F92" s="13" t="n">
+    <row r="93">
+      <c r="A93" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>You're alright, you're alright</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Stamina cost to start a pull</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr"/>
+      <c r="E93" s="5" t="inlineStr"/>
+      <c r="F93" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>param:stamina</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="B94" s="12" t="inlineStr">
+        <is>
+          <t>Take One for the Troop</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t>All Injury</t>
+        </is>
+      </c>
+      <c r="D94" s="12" t="inlineStr"/>
+      <c r="E94" s="12" t="inlineStr">
+        <is>
+          <t>Teammates within 6 m</t>
+        </is>
+      </c>
+      <c r="F94" s="13" t="n">
+        <v>-30</v>
+      </c>
+      <c r="G94" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H94" s="12" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="B95" s="12" t="inlineStr">
+        <is>
+          <t>Take One for the Troop</t>
+        </is>
+      </c>
+      <c r="C95" s="12" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="D95" s="12" t="inlineStr"/>
+      <c r="E95" s="12" t="inlineStr"/>
+      <c r="F95" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G95" s="12" t="inlineStr">
+        <is>
+          <t>metres</t>
+        </is>
+      </c>
+      <c r="H95" s="12" t="inlineStr">
+        <is>
+          <t>param:radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="B96" s="12" t="inlineStr">
+        <is>
+          <t>Take One for the Troop</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>Share of the prevented Injury you take</t>
+        </is>
+      </c>
+      <c r="D96" s="12" t="inlineStr"/>
+      <c r="E96" s="12" t="inlineStr"/>
+      <c r="F96" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="G92" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H92" s="12" t="inlineStr">
-        <is>
-          <t>mod:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="B93" s="12" t="inlineStr">
-        <is>
-          <t>Scout Cannon Legs</t>
-        </is>
-      </c>
-      <c r="C93" s="12" t="inlineStr">
-        <is>
-          <t>Fall Injury</t>
-        </is>
-      </c>
-      <c r="D93" s="12" t="inlineStr"/>
-      <c r="E93" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F93" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="G93" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H93" s="12" t="inlineStr">
-        <is>
-          <t>mod:2</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B94" s="5" t="inlineStr">
-        <is>
-          <t>Crown of Bad Decisions</t>
-        </is>
-      </c>
-      <c r="C94" s="5" t="inlineStr">
-        <is>
-          <t>Yellow stamina when picked</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="inlineStr"/>
-      <c r="E94" s="5" t="inlineStr"/>
-      <c r="F94" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="G94" s="5" t="inlineStr">
+      <c r="G96" s="12" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H96" s="12" t="inlineStr">
+        <is>
+          <t>param:absorb</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="B97" s="12" t="inlineStr">
+        <is>
+          <t>Take One for the Troop</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="inlineStr">
+        <is>
+          <t>Most Injury you take per hit</t>
+        </is>
+      </c>
+      <c r="D97" s="12" t="inlineStr"/>
+      <c r="E97" s="12" t="inlineStr"/>
+      <c r="F97" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G97" s="12" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="H94" s="5" t="inlineStr">
-        <is>
-          <t>param:bonusNow</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>Crown of Bad Decisions</t>
-        </is>
-      </c>
-      <c r="C95" s="5" t="inlineStr">
-        <is>
-          <t>Yellow stamina at each later campfire</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr"/>
-      <c r="E95" s="5" t="inlineStr"/>
-      <c r="F95" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="G95" s="5" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H95" s="5" t="inlineStr">
-        <is>
-          <t>param:bonusFire</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B96" s="5" t="inlineStr">
-        <is>
-          <t>Crown of Bad Decisions</t>
-        </is>
-      </c>
-      <c r="C96" s="5" t="inlineStr">
-        <is>
-          <t>Curse when picked</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="inlineStr"/>
-      <c r="E96" s="5" t="inlineStr"/>
-      <c r="F96" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="G96" s="5" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H96" s="5" t="inlineStr">
-        <is>
-          <t>param:curseNow</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B97" s="5" t="inlineStr">
-        <is>
-          <t>Crown of Bad Decisions</t>
-        </is>
-      </c>
-      <c r="C97" s="5" t="inlineStr">
-        <is>
-          <t>Curse at each later campfire</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="inlineStr"/>
-      <c r="E97" s="5" t="inlineStr"/>
-      <c r="F97" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G97" s="5" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H97" s="5" t="inlineStr">
-        <is>
-          <t>param:curseFire</t>
+      <c r="H97" s="12" t="inlineStr">
+        <is>
+          <t>param:cap</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>Crown of Bad Decisions</t>
+          <t>Friendship Bugle Choir</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Most Curse this card can ever add</t>
+          <t>Max stamina</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr"/>
-      <c r="E98" s="5" t="inlineStr"/>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>Teammates within 8 m</t>
+        </is>
+      </c>
       <c r="F98" s="13" t="n">
         <v>10</v>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>stamina points</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
         <is>
-          <t>param:curseBudget</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="B99" s="12" t="inlineStr">
-        <is>
-          <t>Pandora's Pocket Gamble</t>
-        </is>
-      </c>
-      <c r="C99" s="12" t="inlineStr">
-        <is>
-          <t>Carried item weight</t>
-        </is>
-      </c>
-      <c r="D99" s="12" t="inlineStr"/>
-      <c r="E99" s="12" t="inlineStr">
+      <c r="A99" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>Friendship Bugle Choir</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>Max stamina</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>while a teammate is near you</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>-10</v>
-      </c>
-      <c r="G99" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H99" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
+        <v>10</v>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>stamina points</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="B100" s="12" t="inlineStr">
-        <is>
-          <t>Pandora's Pocket Gamble</t>
-        </is>
-      </c>
-      <c r="C100" s="12" t="inlineStr">
-        <is>
-          <t>Chance of a lucky roll</t>
-        </is>
-      </c>
-      <c r="D100" s="12" t="inlineStr"/>
-      <c r="E100" s="12" t="inlineStr"/>
+      <c r="A100" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>Friendship Bugle Choir</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr"/>
+      <c r="E100" s="5" t="inlineStr"/>
       <c r="F100" s="13" t="n">
-        <v>65</v>
-      </c>
-      <c r="G100" s="12" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H100" s="12" t="inlineStr">
-        <is>
-          <t>param:chance</t>
+        <v>8</v>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>metres</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
+          <t>param:radius</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="12" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>Pandora's Pocket Gamble</t>
+          <t>Scout Cannon Legs</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Yellow stamina on a lucky roll</t>
+          <t>Sprint speed</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr"/>
-      <c r="E101" s="12" t="inlineStr"/>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F101" s="13" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H101" s="12" t="inlineStr">
         <is>
-          <t>param:bonus</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="12" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B102" s="12" t="inlineStr">
         <is>
-          <t>Pandora's Pocket Gamble</t>
+          <t>Scout Cannon Legs</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>Injury on an unlucky roll</t>
+          <t>Jump height</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr"/>
-      <c r="E102" s="12" t="inlineStr"/>
+      <c r="E102" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F102" s="13" t="n">
-        <v>7.5</v>
+        <v>25</v>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H102" s="12" t="inlineStr">
         <is>
-          <t>param:injury</t>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="5" t="n">
-        <v>52</v>
-      </c>
-      <c r="B103" s="5" t="inlineStr">
-        <is>
-          <t>Bootleg Scoutmaster Bugle</t>
-        </is>
-      </c>
-      <c r="C103" s="5" t="inlineStr">
-        <is>
-          <t>Yellow stamina per use</t>
-        </is>
-      </c>
-      <c r="D103" s="5" t="inlineStr"/>
-      <c r="E103" s="5" t="inlineStr"/>
+      <c r="A103" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t>Scout Cannon Legs</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>Fall Injury</t>
+        </is>
+      </c>
+      <c r="D103" s="12" t="inlineStr"/>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F103" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="G103" s="5" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H103" s="5" t="inlineStr">
-        <is>
-          <t>param:bonus</t>
+        <v>25</v>
+      </c>
+      <c r="G103" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H103" s="12" t="inlineStr">
+        <is>
+          <t>mod:2</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>Bootleg Scoutmaster Bugle</t>
+          <t>Crown of Bad Decisions</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>Injury per use</t>
+          <t>Yellow stamina when picked</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr"/>
       <c r="E104" s="5" t="inlineStr"/>
       <c r="F104" s="13" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
@@ -6016,649 +6048,633 @@
       </c>
       <c r="H104" s="5" t="inlineStr">
         <is>
-          <t>param:injury</t>
+          <t>param:bonusNow</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="B105" s="12" t="inlineStr">
-        <is>
-          <t>Big Lollipop Crash</t>
-        </is>
-      </c>
-      <c r="C105" s="12" t="inlineStr">
-        <is>
-          <t>Sprint speed</t>
-        </is>
-      </c>
-      <c r="D105" s="12" t="inlineStr">
-        <is>
-          <t>while your sprint speed-up is on</t>
-        </is>
-      </c>
-      <c r="E105" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="A105" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>Crown of Bad Decisions</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>Yellow stamina at each later campfire</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr"/>
+      <c r="E105" s="5" t="inlineStr"/>
       <c r="F105" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="G105" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H105" s="12" t="inlineStr">
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>param:bonusFire</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>Crown of Bad Decisions</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>Curse when picked</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr"/>
+      <c r="E106" s="5" t="inlineStr"/>
+      <c r="F106" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="inlineStr">
+        <is>
+          <t>param:curseNow</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>Crown of Bad Decisions</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>Curse at each later campfire</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr"/>
+      <c r="E107" s="5" t="inlineStr"/>
+      <c r="F107" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>param:curseFire</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>Crown of Bad Decisions</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>Most Curse this card can ever add</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr"/>
+      <c r="E108" s="5" t="inlineStr"/>
+      <c r="F108" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>param:curseBudget</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>Pandora's Pocket Gamble</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>Carried item weight</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr"/>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F109" s="13" t="n">
+        <v>-10</v>
+      </c>
+      <c r="G109" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H109" s="12" t="inlineStr">
         <is>
           <t>mod:0</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="B106" s="12" t="inlineStr">
-        <is>
-          <t>Big Lollipop Crash</t>
-        </is>
-      </c>
-      <c r="C106" s="12" t="inlineStr">
-        <is>
-          <t>Sprint time before the speed-up</t>
-        </is>
-      </c>
-      <c r="D106" s="12" t="inlineStr"/>
-      <c r="E106" s="12" t="inlineStr"/>
-      <c r="F106" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G106" s="12" t="inlineStr">
-        <is>
-          <t>seconds</t>
-        </is>
-      </c>
-      <c r="H106" s="12" t="inlineStr">
-        <is>
-          <t>param:buildup</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="B107" s="12" t="inlineStr">
-        <is>
-          <t>Big Lollipop Crash</t>
-        </is>
-      </c>
-      <c r="C107" s="12" t="inlineStr">
-        <is>
-          <t>Drowsy added</t>
-        </is>
-      </c>
-      <c r="D107" s="12" t="inlineStr"/>
-      <c r="E107" s="12" t="inlineStr"/>
-      <c r="F107" s="13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G107" s="12" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="B110" s="12" t="inlineStr">
+        <is>
+          <t>Pandora's Pocket Gamble</t>
+        </is>
+      </c>
+      <c r="C110" s="12" t="inlineStr">
+        <is>
+          <t>Chance of a lucky roll</t>
+        </is>
+      </c>
+      <c r="D110" s="12" t="inlineStr"/>
+      <c r="E110" s="12" t="inlineStr"/>
+      <c r="F110" s="13" t="n">
+        <v>65</v>
+      </c>
+      <c r="G110" s="12" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H110" s="12" t="inlineStr">
+        <is>
+          <t>param:chance</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="B111" s="12" t="inlineStr">
+        <is>
+          <t>Pandora's Pocket Gamble</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>Yellow stamina on a lucky roll</t>
+        </is>
+      </c>
+      <c r="D111" s="12" t="inlineStr"/>
+      <c r="E111" s="12" t="inlineStr"/>
+      <c r="F111" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G111" s="12" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="H107" s="12" t="inlineStr">
-        <is>
-          <t>param:drowsy</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="B108" s="12" t="inlineStr">
-        <is>
-          <t>Big Lollipop Crash</t>
-        </is>
-      </c>
-      <c r="C108" s="12" t="inlineStr">
-        <is>
-          <t>Time between Drowsy penalties</t>
-        </is>
-      </c>
-      <c r="D108" s="12" t="inlineStr"/>
-      <c r="E108" s="12" t="inlineStr"/>
-      <c r="F108" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="G108" s="12" t="inlineStr">
-        <is>
-          <t>seconds</t>
-        </is>
-      </c>
-      <c r="H108" s="12" t="inlineStr">
-        <is>
-          <t>param:cooldown</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="n">
-        <v>54</v>
-      </c>
-      <c r="B109" s="5" t="inlineStr">
-        <is>
-          <t>Piton Payment Plan</t>
-        </is>
-      </c>
-      <c r="C109" s="5" t="inlineStr">
-        <is>
-          <t>Share of each fall's Injury that is delayed</t>
-        </is>
-      </c>
-      <c r="D109" s="5" t="inlineStr"/>
-      <c r="E109" s="5" t="inlineStr"/>
-      <c r="F109" s="13" t="n">
-        <v>75</v>
-      </c>
-      <c r="G109" s="5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H109" s="5" t="inlineStr">
-        <is>
-          <t>param:defer</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="5" t="n">
-        <v>54</v>
-      </c>
-      <c r="B110" s="5" t="inlineStr">
-        <is>
-          <t>Piton Payment Plan</t>
-        </is>
-      </c>
-      <c r="C110" s="5" t="inlineStr">
-        <is>
-          <t>Delay before the rest lands</t>
-        </is>
-      </c>
-      <c r="D110" s="5" t="inlineStr"/>
-      <c r="E110" s="5" t="inlineStr"/>
-      <c r="F110" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="G110" s="5" t="inlineStr">
-        <is>
-          <t>seconds</t>
-        </is>
-      </c>
-      <c r="H110" s="5" t="inlineStr">
-        <is>
-          <t>param:delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="5" t="n">
-        <v>54</v>
-      </c>
-      <c r="B111" s="5" t="inlineStr">
-        <is>
-          <t>Piton Payment Plan</t>
-        </is>
-      </c>
-      <c r="C111" s="5" t="inlineStr">
-        <is>
-          <t>Share of the delayed Injury that still lands</t>
-        </is>
-      </c>
-      <c r="D111" s="5" t="inlineStr"/>
-      <c r="E111" s="5" t="inlineStr"/>
-      <c r="F111" s="13" t="n">
-        <v>80</v>
-      </c>
-      <c r="G111" s="5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H111" s="5" t="inlineStr">
-        <is>
-          <t>param:keep</t>
+      <c r="H111" s="12" t="inlineStr">
+        <is>
+          <t>param:bonus</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="12" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B112" s="12" t="inlineStr">
         <is>
-          <t>Glass Scout Cannon</t>
+          <t>Pandora's Pocket Gamble</t>
         </is>
       </c>
       <c r="C112" s="12" t="inlineStr">
         <is>
-          <t>Max stamina</t>
+          <t>Injury on an unlucky roll</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr"/>
-      <c r="E112" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="E112" s="12" t="inlineStr"/>
       <c r="F112" s="13" t="n">
-        <v>40</v>
+        <v>7.5</v>
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
-          <t>stamina points</t>
+          <t>points</t>
         </is>
       </c>
       <c r="H112" s="12" t="inlineStr">
         <is>
-          <t>mod:0</t>
+          <t>param:injury</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="B113" s="12" t="inlineStr">
-        <is>
-          <t>Glass Scout Cannon</t>
-        </is>
-      </c>
-      <c r="C113" s="12" t="inlineStr">
-        <is>
-          <t>All Injury</t>
-        </is>
-      </c>
-      <c r="D113" s="12" t="inlineStr"/>
-      <c r="E113" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="A113" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>Bootleg Scoutmaster Bugle</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>Yellow stamina per use</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr"/>
+      <c r="E113" s="5" t="inlineStr"/>
       <c r="F113" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="G113" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H113" s="12" t="inlineStr">
-        <is>
-          <t>mod:1</t>
+        <v>60</v>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>param:bonus</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>Baggage Claim Escapee</t>
+          <t>Bootleg Scoutmaster Bugle</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
+          <t>Injury per use</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr"/>
+      <c r="E114" s="5" t="inlineStr"/>
+      <c r="F114" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="inlineStr">
+        <is>
+          <t>param:injury</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="B115" s="12" t="inlineStr">
+        <is>
+          <t>Big Lollipop Crash</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="inlineStr">
+        <is>
           <t>Sprint speed</t>
         </is>
       </c>
-      <c r="D114" s="5" t="inlineStr">
-        <is>
-          <t>while you don't wear a backpack</t>
-        </is>
-      </c>
-      <c r="E114" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F114" s="13" t="n">
+      <c r="D115" s="12" t="inlineStr">
+        <is>
+          <t>while your sprint speed-up is on</t>
+        </is>
+      </c>
+      <c r="E115" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F115" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="G114" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H114" s="5" t="inlineStr">
+      <c r="G115" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H115" s="12" t="inlineStr">
         <is>
           <t>mod:0</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="B115" s="5" t="inlineStr">
-        <is>
-          <t>Baggage Claim Escapee</t>
-        </is>
-      </c>
-      <c r="C115" s="5" t="inlineStr">
-        <is>
-          <t>Jump height</t>
-        </is>
-      </c>
-      <c r="D115" s="5" t="inlineStr">
-        <is>
-          <t>while you don't wear a backpack</t>
-        </is>
-      </c>
-      <c r="E115" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F115" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="G115" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H115" s="5" t="inlineStr">
-        <is>
-          <t>mod:1</t>
-        </is>
-      </c>
-    </row>
     <row r="116">
-      <c r="A116" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="B116" s="5" t="inlineStr">
-        <is>
-          <t>Baggage Claim Escapee</t>
-        </is>
-      </c>
-      <c r="C116" s="5" t="inlineStr">
-        <is>
-          <t>Sprint speed</t>
-        </is>
-      </c>
-      <c r="D116" s="5" t="inlineStr">
-        <is>
-          <t>while you wear a backpack</t>
-        </is>
-      </c>
-      <c r="E116" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="A116" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="B116" s="12" t="inlineStr">
+        <is>
+          <t>Big Lollipop Crash</t>
+        </is>
+      </c>
+      <c r="C116" s="12" t="inlineStr">
+        <is>
+          <t>Sprint time before the speed-up</t>
+        </is>
+      </c>
+      <c r="D116" s="12" t="inlineStr"/>
+      <c r="E116" s="12" t="inlineStr"/>
       <c r="F116" s="13" t="n">
-        <v>-5</v>
-      </c>
-      <c r="G116" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H116" s="5" t="inlineStr">
-        <is>
-          <t>mod:2</t>
+        <v>2</v>
+      </c>
+      <c r="G116" s="12" t="inlineStr">
+        <is>
+          <t>seconds</t>
+        </is>
+      </c>
+      <c r="H116" s="12" t="inlineStr">
+        <is>
+          <t>param:buildup</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="12" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>Scout's Dishonor</t>
+          <t>Big Lollipop Crash</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Bonus cards (Common to Rare)</t>
+          <t>Drowsy added</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr"/>
       <c r="E117" s="12" t="inlineStr"/>
       <c r="F117" s="13" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
-          <t>cards</t>
+          <t>points</t>
         </is>
       </c>
       <c r="H117" s="12" t="inlineStr">
         <is>
-          <t>param:bonusCards</t>
+          <t>param:drowsy</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="12" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B118" s="12" t="inlineStr">
         <is>
-          <t>Scout's Dishonor</t>
+          <t>Big Lollipop Crash</t>
         </is>
       </c>
       <c r="C118" s="12" t="inlineStr">
         <is>
-          <t>Curse when picked</t>
+          <t>Time between Drowsy penalties</t>
         </is>
       </c>
       <c r="D118" s="12" t="inlineStr"/>
       <c r="E118" s="12" t="inlineStr"/>
       <c r="F118" s="13" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>seconds</t>
         </is>
       </c>
       <c r="H118" s="12" t="inlineStr">
         <is>
-          <t>param:curse</t>
+          <t>param:cooldown</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="B119" s="12" t="inlineStr">
-        <is>
-          <t>Scout's Dishonor</t>
-        </is>
-      </c>
-      <c r="C119" s="12" t="inlineStr">
-        <is>
-          <t>Cards in your next offer</t>
-        </is>
-      </c>
-      <c r="D119" s="12" t="inlineStr"/>
-      <c r="E119" s="12" t="inlineStr"/>
+      <c r="A119" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>Piton Payment Plan</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>Share of each fall's Injury that is delayed</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr"/>
+      <c r="E119" s="5" t="inlineStr"/>
       <c r="F119" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G119" s="12" t="inlineStr">
-        <is>
-          <t>cards</t>
-        </is>
-      </c>
-      <c r="H119" s="12" t="inlineStr">
-        <is>
-          <t>param:nextOffer</t>
+        <v>75</v>
+      </c>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="inlineStr">
+        <is>
+          <t>param:defer</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>BingBong Baggage Scanner</t>
+          <t>Piton Payment Plan</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Delay before the rest lands</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr"/>
       <c r="E120" s="5" t="inlineStr"/>
       <c r="F120" s="13" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>metres</t>
+          <t>seconds</t>
         </is>
       </c>
       <c r="H120" s="5" t="inlineStr">
         <is>
-          <t>param:radius</t>
+          <t>param:delay</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="12" t="n">
-        <v>59</v>
-      </c>
-      <c r="B121" s="12" t="inlineStr">
-        <is>
-          <t>Medicinal Munchies</t>
-        </is>
-      </c>
-      <c r="C121" s="12" t="inlineStr">
-        <is>
-          <t>Needs at least this much Injury</t>
-        </is>
-      </c>
-      <c r="D121" s="12" t="inlineStr"/>
-      <c r="E121" s="12" t="inlineStr"/>
+      <c r="A121" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>Piton Payment Plan</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>Share of the delayed Injury that still lands</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr"/>
+      <c r="E121" s="5" t="inlineStr"/>
       <c r="F121" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="G121" s="12" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H121" s="12" t="inlineStr">
-        <is>
-          <t>param:threshold</t>
+        <v>80</v>
+      </c>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="inlineStr">
+        <is>
+          <t>param:keep</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="12" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B122" s="12" t="inlineStr">
         <is>
-          <t>Medicinal Munchies</t>
+          <t>Glass Scout Cannon</t>
         </is>
       </c>
       <c r="C122" s="12" t="inlineStr">
         <is>
-          <t>Injury removed</t>
+          <t>Max stamina</t>
         </is>
       </c>
       <c r="D122" s="12" t="inlineStr"/>
-      <c r="E122" s="12" t="inlineStr"/>
+      <c r="E122" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F122" s="13" t="n">
-        <v>7.5</v>
+        <v>40</v>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>stamina points</t>
         </is>
       </c>
       <c r="H122" s="12" t="inlineStr">
         <is>
-          <t>param:heal</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="B123" s="5" t="inlineStr">
-        <is>
-          <t>Budget Checkpoint Flag</t>
-        </is>
-      </c>
-      <c r="C123" s="5" t="inlineStr">
-        <is>
-          <t>Injury after the revive</t>
-        </is>
-      </c>
-      <c r="D123" s="5" t="inlineStr"/>
-      <c r="E123" s="5" t="inlineStr"/>
+      <c r="A123" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="B123" s="12" t="inlineStr">
+        <is>
+          <t>Glass Scout Cannon</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="inlineStr">
+        <is>
+          <t>All Injury</t>
+        </is>
+      </c>
+      <c r="D123" s="12" t="inlineStr"/>
+      <c r="E123" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F123" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="G123" s="5" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H123" s="5" t="inlineStr">
-        <is>
-          <t>param:injury</t>
+        <v>25</v>
+      </c>
+      <c r="G123" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H123" s="12" t="inlineStr">
+        <is>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="12" t="n">
-        <v>61</v>
-      </c>
-      <c r="B124" s="12" t="inlineStr">
-        <is>
-          <t>Petrify Procrastination</t>
-        </is>
-      </c>
-      <c r="C124" s="12" t="inlineStr">
-        <is>
-          <t>Petrify build-up</t>
-        </is>
-      </c>
-      <c r="D124" s="12" t="inlineStr"/>
-      <c r="E124" s="12" t="inlineStr">
+      <c r="A124" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>Baggage Claim Escapee</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>Sprint speed</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>while you don't wear a backpack</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F124" s="13" t="n">
-        <v>-50</v>
-      </c>
-      <c r="G124" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H124" s="12" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="inlineStr">
         <is>
           <t>mod:0</t>
         </is>
@@ -6666,364 +6682,684 @@
     </row>
     <row r="125">
       <c r="A125" s="5" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>Fine Print</t>
+          <t>Baggage Claim Escapee</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>Max stamina</t>
-        </is>
-      </c>
-      <c r="D125" s="5" t="inlineStr"/>
+          <t>Jump height</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>while you don't wear a backpack</t>
+        </is>
+      </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F125" s="13" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>stamina points</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
-          <t>mod:0</t>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>Fine Print</t>
+          <t>Baggage Claim Escapee</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>Curse when the sacrifice is made</t>
-        </is>
-      </c>
-      <c r="D126" s="5" t="inlineStr"/>
-      <c r="E126" s="5" t="inlineStr"/>
+          <t>Sprint speed</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>while you wear a backpack</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F126" s="13" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H126" s="5" t="inlineStr">
         <is>
-          <t>param:curse</t>
+          <t>mod:2</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="12" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>Scoutmaster</t>
+          <t>Scout's Dishonor</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>Climbing stamina cost (set, ignores other cards)</t>
+          <t>Bonus cards (Common to Rare)</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr"/>
-      <c r="E127" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="E127" s="12" t="inlineStr"/>
       <c r="F127" s="13" t="n">
-        <v>-100</v>
+        <v>2</v>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>cards</t>
         </is>
       </c>
       <c r="H127" s="12" t="inlineStr">
         <is>
-          <t>mod:0</t>
+          <t>param:bonusCards</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="12" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B128" s="12" t="inlineStr">
         <is>
-          <t>Scoutmaster</t>
+          <t>Scout's Dishonor</t>
         </is>
       </c>
       <c r="C128" s="12" t="inlineStr">
         <is>
-          <t>Fall Injury (set, ignores other cards)</t>
+          <t>Curse when picked</t>
         </is>
       </c>
       <c r="D128" s="12" t="inlineStr"/>
-      <c r="E128" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="E128" s="12" t="inlineStr"/>
       <c r="F128" s="13" t="n">
-        <v>-100</v>
+        <v>5</v>
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>points</t>
         </is>
       </c>
       <c r="H128" s="12" t="inlineStr">
         <is>
-          <t>mod:1</t>
+          <t>param:curse</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="12" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>Scoutmaster</t>
+          <t>Scout's Dishonor</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>Sprint speed</t>
+          <t>Cards in your next offer</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr"/>
-      <c r="E129" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="E129" s="12" t="inlineStr"/>
       <c r="F129" s="13" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>cards</t>
         </is>
       </c>
       <c r="H129" s="12" t="inlineStr">
         <is>
-          <t>mod:2</t>
+          <t>param:nextOffer</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>The Eternal Campfire</t>
+          <t>BingBong Baggage Scanner</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>Max stamina</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr"/>
-      <c r="E130" s="5" t="inlineStr">
-        <is>
-          <t>You and teammates within 15 m</t>
-        </is>
-      </c>
+      <c r="E130" s="5" t="inlineStr"/>
       <c r="F130" s="13" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>stamina points</t>
+          <t>metres</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
         <is>
-          <t>mod:0</t>
+          <t>param:radius</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B131" s="5" t="inlineStr">
-        <is>
-          <t>The Eternal Campfire</t>
-        </is>
-      </c>
-      <c r="C131" s="5" t="inlineStr">
-        <is>
-          <t>All Injury</t>
-        </is>
-      </c>
-      <c r="D131" s="5" t="inlineStr"/>
-      <c r="E131" s="5" t="inlineStr">
-        <is>
-          <t>You and teammates within 15 m</t>
-        </is>
-      </c>
+      <c r="A131" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="B131" s="12" t="inlineStr">
+        <is>
+          <t>Medicinal Munchies</t>
+        </is>
+      </c>
+      <c r="C131" s="12" t="inlineStr">
+        <is>
+          <t>Needs at least this much Injury</t>
+        </is>
+      </c>
+      <c r="D131" s="12" t="inlineStr"/>
+      <c r="E131" s="12" t="inlineStr"/>
       <c r="F131" s="13" t="n">
-        <v>-60</v>
-      </c>
-      <c r="G131" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H131" s="5" t="inlineStr">
-        <is>
-          <t>mod:1</t>
+        <v>20</v>
+      </c>
+      <c r="G131" s="12" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H131" s="12" t="inlineStr">
+        <is>
+          <t>param:threshold</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B132" s="5" t="inlineStr">
-        <is>
-          <t>The Eternal Campfire</t>
-        </is>
-      </c>
-      <c r="C132" s="5" t="inlineStr">
-        <is>
-          <t>All negative status build-up</t>
-        </is>
-      </c>
-      <c r="D132" s="5" t="inlineStr"/>
-      <c r="E132" s="5" t="inlineStr">
-        <is>
-          <t>You and teammates within 15 m</t>
-        </is>
-      </c>
+      <c r="A132" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="B132" s="12" t="inlineStr">
+        <is>
+          <t>Medicinal Munchies</t>
+        </is>
+      </c>
+      <c r="C132" s="12" t="inlineStr">
+        <is>
+          <t>Injury removed</t>
+        </is>
+      </c>
+      <c r="D132" s="12" t="inlineStr"/>
+      <c r="E132" s="12" t="inlineStr"/>
       <c r="F132" s="13" t="n">
-        <v>-60</v>
-      </c>
-      <c r="G132" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H132" s="5" t="inlineStr">
-        <is>
-          <t>mod:2</t>
+        <v>7.5</v>
+      </c>
+      <c r="G132" s="12" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H132" s="12" t="inlineStr">
+        <is>
+          <t>param:heal</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>The Eternal Campfire</t>
+          <t>Budget Checkpoint Flag</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Injury after the revive</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr"/>
       <c r="E133" s="5" t="inlineStr"/>
       <c r="F133" s="13" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>metres</t>
+          <t>points</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>param:radius</t>
+          <t>param:injury</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B134" s="5" t="inlineStr">
-        <is>
-          <t>The Eternal Campfire</t>
-        </is>
-      </c>
-      <c r="C134" s="5" t="inlineStr">
-        <is>
-          <t>Injury after the revive</t>
-        </is>
-      </c>
-      <c r="D134" s="5" t="inlineStr"/>
-      <c r="E134" s="5" t="inlineStr"/>
+      <c r="A134" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="B134" s="12" t="inlineStr">
+        <is>
+          <t>Petrify Procrastination</t>
+        </is>
+      </c>
+      <c r="C134" s="12" t="inlineStr">
+        <is>
+          <t>Petrify build-up</t>
+        </is>
+      </c>
+      <c r="D134" s="12" t="inlineStr"/>
+      <c r="E134" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F134" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="G134" s="5" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H134" s="5" t="inlineStr">
-        <is>
-          <t>param:injury</t>
+        <v>-50</v>
+      </c>
+      <c r="G134" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H134" s="12" t="inlineStr">
+        <is>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>Fine Print</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>Max stamina</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr"/>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F135" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="G135" s="5" t="inlineStr">
+        <is>
+          <t>stamina points</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>Fine Print</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>Curse when the sacrifice is made</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr"/>
+      <c r="E136" s="5" t="inlineStr"/>
+      <c r="F136" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G136" s="5" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="inlineStr">
+        <is>
+          <t>param:curse</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="B137" s="12" t="inlineStr">
+        <is>
+          <t>Scoutmaster</t>
+        </is>
+      </c>
+      <c r="C137" s="12" t="inlineStr">
+        <is>
+          <t>Climbing stamina cost (set, ignores other cards)</t>
+        </is>
+      </c>
+      <c r="D137" s="12" t="inlineStr"/>
+      <c r="E137" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F137" s="13" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G137" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H137" s="12" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="B138" s="12" t="inlineStr">
+        <is>
+          <t>Scoutmaster</t>
+        </is>
+      </c>
+      <c r="C138" s="12" t="inlineStr">
+        <is>
+          <t>Fall Injury (set, ignores other cards)</t>
+        </is>
+      </c>
+      <c r="D138" s="12" t="inlineStr"/>
+      <c r="E138" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F138" s="13" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G138" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H138" s="12" t="inlineStr">
+        <is>
+          <t>mod:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="B139" s="12" t="inlineStr">
+        <is>
+          <t>Scoutmaster</t>
+        </is>
+      </c>
+      <c r="C139" s="12" t="inlineStr">
+        <is>
+          <t>Sprint speed</t>
+        </is>
+      </c>
+      <c r="D139" s="12" t="inlineStr"/>
+      <c r="E139" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F139" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G139" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H139" s="12" t="inlineStr">
+        <is>
+          <t>mod:2</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="n">
         <v>64</v>
       </c>
-      <c r="B135" s="5" t="inlineStr">
+      <c r="B140" s="5" t="inlineStr">
         <is>
           <t>The Eternal Campfire</t>
         </is>
       </c>
-      <c r="C135" s="5" t="inlineStr">
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>Max stamina</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr"/>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>You and teammates within 15 m</t>
+        </is>
+      </c>
+      <c r="F140" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="G140" s="5" t="inlineStr">
+        <is>
+          <t>stamina points</t>
+        </is>
+      </c>
+      <c r="H140" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>The Eternal Campfire</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>All Injury</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr"/>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>You and teammates within 15 m</t>
+        </is>
+      </c>
+      <c r="F141" s="13" t="n">
+        <v>-60</v>
+      </c>
+      <c r="G141" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H141" s="5" t="inlineStr">
+        <is>
+          <t>mod:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>The Eternal Campfire</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>All negative status build-up</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr"/>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>You and teammates within 15 m</t>
+        </is>
+      </c>
+      <c r="F142" s="13" t="n">
+        <v>-60</v>
+      </c>
+      <c r="G142" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H142" s="5" t="inlineStr">
+        <is>
+          <t>mod:2</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>The Eternal Campfire</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr"/>
+      <c r="E143" s="5" t="inlineStr"/>
+      <c r="F143" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="G143" s="5" t="inlineStr">
+        <is>
+          <t>metres</t>
+        </is>
+      </c>
+      <c r="H143" s="5" t="inlineStr">
+        <is>
+          <t>param:radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>The Eternal Campfire</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>Injury after the revive</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="inlineStr"/>
+      <c r="E144" s="5" t="inlineStr"/>
+      <c r="F144" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="G144" s="5" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H144" s="5" t="inlineStr">
+        <is>
+          <t>param:injury</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>The Eternal Campfire</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
         <is>
           <t>Stamina after the revive (at least)</t>
         </is>
       </c>
-      <c r="D135" s="5" t="inlineStr"/>
-      <c r="E135" s="5" t="inlineStr"/>
-      <c r="F135" s="13" t="n">
+      <c r="D145" s="5" t="inlineStr"/>
+      <c r="E145" s="5" t="inlineStr"/>
+      <c r="F145" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="G135" s="5" t="inlineStr">
+      <c r="G145" s="5" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="H135" s="5" t="inlineStr">
+      <c r="H145" s="5" t="inlineStr">
         <is>
           <t>param:stamina</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H135"/>
+  <autoFilter ref="A1:H145"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/design/editable/card-sheet.xlsx
+++ b/design/editable/card-sheet.xlsx
@@ -1032,7 +1032,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Hanging still on a wall costs no stamina, and you slip and slide 40% less.</t>
+          <t>Hanging still on a wall costs almost no stamina, and you slip and slide 40% less.</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr"/>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>New Thorns add 80% less status, thorns take 50% less time to remove, and hits that are not falls hurt 20% less.</t>
+          <t>New Thorns add 80% less status (at least one thorn always counts), thorns take 50% less time to remove, and hits that are not falls hurt 20% less.</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr"/>

--- a/design/editable/card-sheet.xlsx
+++ b/design/editable/card-sheet.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cards'!$A$1:$G$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Numbers'!$A$1:$H$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Numbers'!$A$1:$H$134</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -699,12 +699,12 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>Climbing uses 12% less stamina.</t>
+          <t>Climbing uses 18% less stamina.</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
-          <t>Sprinting uses 5% more stamina.</t>
+          <t>Sprinting uses 10% more stamina.</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>Take 15% more fall Injury.</t>
+          <t>Take 5% more fall Injury.</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Hang still on a wall to recover 10 stamina per second.</t>
+          <t>Hang still on a wall to recover 5 stamina per second.</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Bing BOING</t>
+          <t>Bing Double Boing</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -822,11 +822,7 @@
           <t>Jump again in mid-air for a double jump. Cooldown: 15s.</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Each double jump adds 5 Drowsy.</t>
-        </is>
-      </c>
+      <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -855,7 +851,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Climbing uses 20% more stamina.</t>
+          <t>Climbing uses 10% more stamina.</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr"/>
@@ -866,7 +862,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Tenderfoot Insurance</t>
+          <t>Tendiefoot</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -897,7 +893,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Daddy</t>
+          <t>Daddy Long Arms</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -943,7 +939,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Gain 25 maximum stamina.</t>
+          <t>Gain 30 maximum stamina.</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -974,7 +970,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Press {key} below 20 stamina to recover 30. Cooldown: 3 min.</t>
+          <t>Press {key} to recover 30 stamina. Cooldown: 5 min.</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr"/>
@@ -986,7 +982,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Hasty Badge Training</t>
+          <t>Leg Day Skip</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -1017,7 +1013,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>HOOOOLLLD</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -1059,7 +1055,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Crouch and stay still for 3s to gain 25 yellow stamina. Once per biome.</t>
+          <t>Crouch and stay still for 3s to gain a full bar of yellow stamina. Once per biome.</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr"/>
@@ -1093,11 +1089,7 @@
           <t>Sprint 35% faster.</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Lose 2.5 maximum stamina.</t>
-        </is>
-      </c>
+      <c r="F15" s="6" t="inlineStr"/>
       <c r="G15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1121,7 +1113,7 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Climb for 2s straight: climbing uses 40% less stamina for the next 2s.</t>
+          <t>Climb for 2s straight: climbing uses 40% less stamina for the next 3.5s.</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr"/>
@@ -1133,7 +1125,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Marshmallow Morale</t>
+          <t>Campfire++</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -1151,11 +1143,7 @@
           <t>Each new campfire clears your Hunger.</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>Cooked food removes 10% less Hunger.</t>
-        </is>
-      </c>
+      <c r="F17" s="6" t="inlineStr"/>
       <c r="G17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1272,7 +1260,7 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Spores build 80% slower, and Poison 15% slower.</t>
+          <t>Spores build 80% slower, and Poison 45% slower.</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr"/>
@@ -1284,7 +1272,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Cactus? What Cactus?</t>
+          <t>Almost Climbable Cactus</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1299,7 +1287,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>New Thorns add 80% less status (at least one thorn always counts), thorns take 50% less time to remove, and hits that are not falls hurt 20% less.</t>
+          <t>Thorns hurt 80% less, and can be removed 50% faster.</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr"/>
@@ -1388,12 +1376,12 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Above 20 Poison, climbing uses 40% less stamina.</t>
+          <t>Poison that builds up over time (gas, venom, vile food) doesn't affect you.</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Poison wears off 10% slower.</t>
+          <t>Instant poison hits hurt 20% more.</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr"/>
@@ -1404,12 +1392,12 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>BingBong</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>Common</t>
+          <t>Bing Boing</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -1431,7 +1419,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Tara</t>
+          <t>TechTara</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -1446,7 +1434,7 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Healing removes 60% more Injury from you.</t>
+          <t>Reduces fall damage by 20% and every bandage in your inventory reduces it by 20% more. (Limit 3)</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr"/>
@@ -1473,7 +1461,7 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>At 20+ Injury, climbing and sprinting use 25% less stamina.</t>
+          <t>At 20+ Injury, climbing and sprinting use 35% less stamina.</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -1534,11 +1522,7 @@
           <t>Once per run, cancel a fatal fall and return to safe ground.</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>Using it skips your next card pick.</t>
-        </is>
-      </c>
+      <c r="F30" s="6" t="inlineStr"/>
       <c r="G30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1547,7 +1531,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Gourmand's Gut</t>
+          <t>Perma-Cooking</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -1562,7 +1546,7 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Food removes 20% more Hunger.</t>
+          <t>Food removes 25% more Hunger.</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr"/>
@@ -1589,7 +1573,7 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Reviving does not add Curse.</t>
+          <t>You receive a Book of Bones right now.</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr"/>
@@ -1616,7 +1600,7 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Medical items also remove 7.5 from your highest other status.</t>
+          <t>Medical and food items also remove a random amount from your highest other negative status.</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr"/>
@@ -1643,7 +1627,7 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>All carried weight is 50% lighter, including backpacks and scouts.</t>
+          <t>All carried weight is 60% lighter, including backpacks and scouts.</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -1690,7 +1674,7 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Idol Hands</t>
+          <t>Super Idol Hands</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
@@ -1705,7 +1689,7 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Held items weigh 65% less, and climbing with an item in hand uses 15% less stamina.</t>
+          <t>Held items weigh 75% less.</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr"/>
@@ -1732,7 +1716,7 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Cooked food fills you up 30% more, and once per biome your first cooked meal is not consumed.</t>
+          <t>Cooked food fills you up 40% more, and once per biome your first cooked meal is not consumed.</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -1748,7 +1732,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Cooking Badge Deluxe</t>
+          <t>Cooked</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
@@ -1763,12 +1747,12 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Cooked food removes 50% more Hunger.</t>
+          <t>Cooked food removes 60% more Hunger.</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>Eating cookable food raw adds 5 Poison.</t>
+          <t>Eating uncooked food adds 5 Poison.</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr"/>
@@ -1794,7 +1778,7 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Get one Balloon Bunch at the next campfire. Once per run.</t>
+          <t>Get a mythic item (of your choice) at the next campfire. Once per run.</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr"/>
@@ -1821,7 +1805,7 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Get a Bandage at each new campfire after picking this card.</t>
+          <t>Get a bandage, random food item, and a random item at each new campfire after picking this card.</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr"/>
@@ -1848,14 +1832,10 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Immediately gain 2 random bonus cards.</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>One permanent random penalty: climbing or sprinting cost +10%, Injury +10%, or Hunger buildup +10%. It stays even if you give this card up.</t>
-        </is>
-      </c>
+          <t>Immediately gain 2 random bonus cards right now.</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr"/>
       <c r="G41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
@@ -1879,7 +1859,7 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>You and teammates within 8 m use 10% less climbing stamina.</t>
+          <t>You and teammates within 8 m use 20% less climbing stamina.</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -1910,7 +1890,7 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Healing items used on teammates remove 100% more Injury.</t>
+          <t>Healing items used on teammates and yourself remove 100% more Injury.</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr"/>
@@ -1922,7 +1902,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Human Carry-On</t>
+          <t>Carry-On Scout</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
@@ -1949,7 +1929,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Happy Camper Huddle</t>
+          <t>Ascent 5+</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
@@ -1991,7 +1971,7 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>First teammate revive by feeding or statue each biome: both gain 100 yellow stamina.</t>
+          <t>First teammate revive by feeding or statue each biome: both gain a full bar of yellow stamina.</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr"/>
@@ -2018,7 +1998,7 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Pull teammates up from 30% farther away.</t>
+          <t>Pull teammates up from 40% farther away.</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
@@ -2049,12 +2029,12 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Teammates within 6 m take 30% less Injury.</t>
+          <t>Teammates within 8 m take 50% less Injury.</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>You take a quarter of the prevented Injury, up to 5 per hit.</t>
+          <t>You take a tiny amount of the prevented Injury, up to 5 per hit.</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr"/>
@@ -2065,7 +2045,7 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Friendship Bugle Choir</t>
+          <t>Friendship Bugles</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
@@ -2138,7 +2118,7 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Gain 40 yellow stamina now, then 30 at each later campfire.</t>
+          <t>Gain a full bar of yellow stamina now, then again at each later campfire.</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
@@ -2154,7 +2134,7 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Pandora's Pocket Gamble</t>
+          <t>Pandora's HotPocket</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
@@ -2169,14 +2149,10 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Inventory items weigh 10% less. Each biome: 65% chance of 25 yellow stamina.</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>A failed roll adds 7.5 Injury instead.</t>
-        </is>
-      </c>
+          <t>Inventory items weigh 25% less, and you gain 37.5 yellow stamina at each new biome.</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr"/>
       <c r="G52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
@@ -2200,7 +2176,7 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Press {key} to gain 60 yellow stamina. Once per biome.</t>
+          <t>Press {key} to gain a full bar of yellow stamina. Once per biome.</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
@@ -2234,11 +2210,7 @@
           <t>Sprint for 2s to move 30% faster until you stop.</t>
         </is>
       </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>Stopping after a boost adds 2.5 Drowsy, at most once every 60s.</t>
-        </is>
-      </c>
+      <c r="F54" s="6" t="inlineStr"/>
       <c r="G54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
@@ -2323,11 +2295,7 @@
           <t>Without a backpack: sprint 30% faster and jump 20% higher.</t>
         </is>
       </c>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t>With a backpack: sprint 5% slower.</t>
-        </is>
-      </c>
+      <c r="F57" s="6" t="inlineStr"/>
       <c r="G57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
@@ -2367,7 +2335,7 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>BingBong Baggage Scanner</t>
+          <t>TSA</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
@@ -2382,7 +2350,7 @@
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>Mark food, items and luggage within 12 m, even through terrain.</t>
+          <t>Mark food, items and luggage within 56 m, even through terrain.</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr"/>
@@ -2409,7 +2377,7 @@
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>At 20+ Injury, eating food removes 7.5 Injury.</t>
+          <t>At 20+ Injury, eating food heals 7.5 health.</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr"/>
@@ -2439,11 +2407,7 @@
           <t>Press {key} on flat ground: your next pass-out revives you here. Once per biome.</t>
         </is>
       </c>
-      <c r="F61" s="6" t="inlineStr">
-        <is>
-          <t>The revival leaves 40 Injury.</t>
-        </is>
-      </c>
+      <c r="F61" s="6" t="inlineStr"/>
       <c r="G61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
@@ -2494,7 +2458,7 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>Sacrifice one of your cards to gain 35 maximum stamina.</t>
+          <t>Sacrifice one of your cards to gain 35 (MORE) maximum stamina.</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
@@ -2583,7 +2547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H145"/>
+  <dimension ref="A1:H134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2659,7 +2623,7 @@
         </is>
       </c>
       <c r="F2" s="13" t="n">
-        <v>-12</v>
+        <v>-18</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -2693,7 +2657,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -2761,7 +2725,7 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
@@ -2897,7 +2861,7 @@
       <c r="D9" s="5" t="inlineStr"/>
       <c r="E9" s="5" t="inlineStr"/>
       <c r="F9" s="13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
@@ -2916,7 +2880,7 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Bing BOING</t>
+          <t>Bing Double Boing</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
@@ -2941,32 +2905,36 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Bing BOING</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>Drowsy added</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr"/>
-      <c r="E11" s="12" t="inlineStr"/>
+      <c r="A11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Energy Drink Overdose</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Climb speed</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F11" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>param:drowsy</t>
+        <v>30</v>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2949,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Climb speed</t>
+          <t>Climbing stamina cost</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr"/>
@@ -2991,7 +2959,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
@@ -3000,41 +2968,41 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
+          <t>mod:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Tendiefoot</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Fall Injury</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr"/>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>-25</v>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
           <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Energy Drink Overdose</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Climbing stamina cost</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>mod:1</t>
         </is>
       </c>
     </row>
@@ -3044,12 +3012,12 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>Tenderfoot Insurance</t>
+          <t>Tendiefoot</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Fall Injury</t>
+          <t>Dynamite Injury</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr"/>
@@ -3059,7 +3027,7 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>-25</v>
+        <v>50</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -3068,41 +3036,41 @@
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
+          <t>mod:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Daddy Long Arms</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Wall-grab reach</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
           <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>Tenderfoot Insurance</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>Dynamite Injury</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr"/>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H15" s="12" t="inlineStr">
-        <is>
-          <t>mod:1</t>
         </is>
       </c>
     </row>
@@ -3112,12 +3080,12 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Daddy</t>
+          <t>Daddy Long Arms</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Wall-grab reach</t>
+          <t>All stamina costs</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr"/>
@@ -3127,7 +3095,7 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
@@ -3136,41 +3104,41 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
+          <t>mod:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Cookie Addiction</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Max stamina</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr"/>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>stamina points</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
           <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Daddy</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>All stamina costs</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>mod:1</t>
         </is>
       </c>
     </row>
@@ -3185,7 +3153,7 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Max stamina</t>
+          <t>Hunger build-up</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr"/>
@@ -3195,50 +3163,46 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>stamina points</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>mod:0</t>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>Cookie Addiction</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>Hunger build-up</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr"/>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="A19" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Nic of Time</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Stamina recovered</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
       <c r="F19" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
-          <t>mod:1</t>
+        <v>30</v>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>param:restore</t>
         </is>
       </c>
     </row>
@@ -3253,371 +3217,371 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Works below this much stamina</t>
+          <t>Cooldown</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr"/>
       <c r="E20" s="5" t="inlineStr"/>
       <c r="F20" s="13" t="n">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>seconds</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>param:threshold</t>
+          <t>param:cooldown</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>Leg Day Skip</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Sprint stamina cost</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr"/>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>-30</v>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Leg Day Skip</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Hunger build-up</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr"/>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Nic of Time</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Stamina recovered</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="inlineStr"/>
-      <c r="F21" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>param:restore</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Nic of Time</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Cooldown</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="13" t="n">
-        <v>180</v>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>mod:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>HOOOOLLLD</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Slip and slide force</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>-40</v>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>HOOOOLLLD</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Hanging drain refunded</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>param:refund</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Meditation</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Crouch time required</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr"/>
+      <c r="E25" s="12" t="inlineStr"/>
+      <c r="F25" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
         <is>
           <t>seconds</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>param:cooldown</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>Hasty Badge Training</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>Sprint stamina cost</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr"/>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="n">
-        <v>-30</v>
-      </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H23" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>Hasty Badge Training</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>Hunger build-up</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr"/>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F24" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G24" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H24" s="12" t="inlineStr">
-        <is>
-          <t>mod:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Slip and slide force</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr"/>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F25" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>param:hold</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Hanging drain refunded</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr"/>
-      <c r="E26" s="5" t="inlineStr"/>
+      <c r="A26" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>Meditation</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>Yellow stamina gained</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr"/>
+      <c r="E26" s="12" t="inlineStr"/>
       <c r="F26" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>param:refund</t>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>param:bonus</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>Meditation</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>Crouch time required</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr"/>
-      <c r="E27" s="12" t="inlineStr"/>
+      <c r="A27" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>I'm getting Scoutmastered</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Sprint speed</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F27" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>seconds</t>
-        </is>
-      </c>
-      <c r="H27" s="12" t="inlineStr">
-        <is>
-          <t>param:hold</t>
+        <v>35</v>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>Meditation</t>
+          <t>Endurance Badge</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>Yellow stamina gained</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="inlineStr"/>
-      <c r="E28" s="12" t="inlineStr"/>
+          <t>Climbing stamina cost</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>while your climbing boost is on</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F28" s="13" t="n">
-        <v>25</v>
+        <v>-40</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>param:bonus</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>I'm getting Scoutmastered</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Sprint speed</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="A29" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Endurance Badge</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>Climbing time before the boost</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr"/>
+      <c r="E29" s="12" t="inlineStr"/>
       <c r="F29" s="13" t="n">
-        <v>35</v>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
+        <v>2</v>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>seconds</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
+          <t>param:buildup</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>I'm getting Scoutmastered</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Max stamina</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="A30" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>Endurance Badge</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>Boost length</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr"/>
+      <c r="E30" s="12" t="inlineStr"/>
       <c r="F30" s="13" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>stamina points</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>mod:1</t>
+        <v>3.5</v>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>seconds</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>param:boost</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Endurance Badge</t>
+          <t>Cool, Calm, and Collected.</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Climbing stamina cost</t>
-        </is>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>while your climbing boost is on</t>
-        </is>
-      </c>
+          <t>Heat build-up</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr"/>
       <c r="E31" s="12" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>-40</v>
+        <v>-70</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -3632,76 +3596,84 @@
     </row>
     <row r="32">
       <c r="A32" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>Endurance Badge</t>
+          <t>Cool, Calm, and Collected.</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Climbing time before the boost</t>
+          <t>Drowsy build-up</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr"/>
-      <c r="E32" s="12" t="inlineStr"/>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F32" s="13" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>seconds</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>param:buildup</t>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Endurance Badge</t>
+          <t>Cool, Calm, and Collected.</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Boost length</t>
+          <t>Cold build-up</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr"/>
-      <c r="E33" s="12" t="inlineStr"/>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F33" s="13" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>seconds</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>param:boost</t>
+          <t>mod:2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Marshmallow Morale</t>
+          <t>Just hot.</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Hunger removed by cooked food</t>
+          <t>Cold build-up</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr"/>
@@ -3711,7 +3683,7 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>-10</v>
+        <v>-70</v>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
@@ -3725,85 +3697,85 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>Cool, Calm, and Collected.</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="inlineStr">
+      <c r="A35" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Just hot.</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Huddle radius and cold removal</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr"/>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>mod:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Just hot.</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>Heat build-up</t>
         </is>
       </c>
-      <c r="D35" s="12" t="inlineStr"/>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F35" s="13" t="n">
-        <v>-70</v>
-      </c>
-      <c r="G35" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H35" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="B36" s="12" t="inlineStr">
-        <is>
-          <t>Cool, Calm, and Collected.</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="inlineStr">
-        <is>
-          <t>Drowsy build-up</t>
-        </is>
-      </c>
-      <c r="D36" s="12" t="inlineStr"/>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>-30</v>
-      </c>
-      <c r="G36" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H36" s="12" t="inlineStr">
-        <is>
-          <t>mod:1</t>
+        <v>10</v>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>mod:2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Cool, Calm, and Collected.</t>
+          <t>Antidote Enthusiast</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Cold build-up</t>
+          <t>Poison build-up</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr"/>
@@ -3813,103 +3785,103 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
+        <v>-70</v>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>Antidote Enthusiast</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>Poison decay</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr"/>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>mod:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>Antidote Enthusiast</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>Heat build-up</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr"/>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F39" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="G37" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H37" s="12" t="inlineStr">
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H39" s="12" t="inlineStr">
         <is>
           <t>mod:2</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>Just hot.</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>Antidote Enthusiast</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
         <is>
           <t>Cold build-up</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr"/>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F38" s="13" t="n">
-        <v>-70</v>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>Just hot.</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>Huddle radius and cold removal</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr"/>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F39" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>mod:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>Just hot.</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>Heat build-up</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr"/>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="D40" s="12" t="inlineStr"/>
+      <c r="E40" s="12" t="inlineStr">
         <is>
           <t>You</t>
         </is>
@@ -3917,80 +3889,80 @@
       <c r="F40" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>mod:2</t>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>mod:3</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="B41" s="12" t="inlineStr">
-        <is>
-          <t>Antidote Enthusiast</t>
-        </is>
-      </c>
-      <c r="C41" s="12" t="inlineStr">
+      <c r="A41" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>ROOTS Survivor</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Spores build-up</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr"/>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>-80</v>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>ROOTS Survivor</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>Poison build-up</t>
         </is>
       </c>
-      <c r="D41" s="12" t="inlineStr"/>
-      <c r="E41" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F41" s="13" t="n">
-        <v>-70</v>
-      </c>
-      <c r="G41" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H41" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="B42" s="12" t="inlineStr">
-        <is>
-          <t>Antidote Enthusiast</t>
-        </is>
-      </c>
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>Poison decay</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="inlineStr"/>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr"/>
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="G42" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H42" s="12" t="inlineStr">
+        <v>-45</v>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
         <is>
           <t>mod:1</t>
         </is>
@@ -3998,16 +3970,16 @@
     </row>
     <row r="43">
       <c r="A43" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Antidote Enthusiast</t>
+          <t>Almost Climbable Cactus</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Heat build-up</t>
+          <t>Thorns build-up</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr"/>
@@ -4017,7 +3989,7 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>10</v>
+        <v>-80</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -4026,22 +3998,22 @@
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>mod:2</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>Antidote Enthusiast</t>
+          <t>Almost Climbable Cactus</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>Cold build-up</t>
+          <t>Thorn removal time</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr"/>
@@ -4051,7 +4023,7 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>10</v>
+        <v>-50</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -4060,22 +4032,22 @@
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>mod:3</t>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>ROOTS Survivor</t>
+          <t>Aloe</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Spores build-up</t>
+          <t>Heat decay</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr"/>
@@ -4085,7 +4057,7 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>-80</v>
+        <v>150</v>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
@@ -4100,16 +4072,16 @@
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>ROOTS Survivor</t>
+          <t>Aloe</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Poison build-up</t>
+          <t>Heat build-up</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr"/>
@@ -4119,7 +4091,7 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>-15</v>
+        <v>5</v>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
@@ -4134,16 +4106,16 @@
     </row>
     <row r="47">
       <c r="A47" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Cactus? What Cactus?</t>
+          <t>Heat Pack</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Thorns build-up</t>
+          <t>Cold decay</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr"/>
@@ -4153,7 +4125,7 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>-80</v>
+        <v>150</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -4168,16 +4140,16 @@
     </row>
     <row r="48">
       <c r="A48" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>Cactus? What Cactus?</t>
+          <t>Heat Pack</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>Thorn removal time</t>
+          <t>Cold build-up</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr"/>
@@ -4187,7 +4159,7 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>-50</v>
+        <v>5</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -4201,61 +4173,53 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="B49" s="12" t="inlineStr">
-        <is>
-          <t>Cactus? What Cactus?</t>
-        </is>
-      </c>
-      <c r="C49" s="12" t="inlineStr">
-        <is>
-          <t>Non-fall Injury</t>
-        </is>
-      </c>
-      <c r="D49" s="12" t="inlineStr"/>
-      <c r="E49" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="A49" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Fartberry Fitness</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Poison below this is gas</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr"/>
+      <c r="E49" s="5" t="inlineStr"/>
       <c r="F49" s="13" t="n">
-        <v>-20</v>
-      </c>
-      <c r="G49" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H49" s="12" t="inlineStr">
-        <is>
-          <t>mod:2</t>
+        <v>2</v>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>param:gasThreshold</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Aloe</t>
+          <t>Fartberry Fitness</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Heat decay</t>
+          <t>Poison hits hurt</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr"/>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="E50" s="5" t="inlineStr"/>
       <c r="F50" s="13" t="n">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
@@ -4264,436 +4228,412 @@
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>mod:0</t>
+          <t>param:hit</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>Aloe</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>Heat build-up</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr"/>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="A51" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>Bing Boing</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>Time between powers</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr"/>
+      <c r="E51" s="12" t="inlineStr"/>
       <c r="F51" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>mod:1</t>
+        <v>300</v>
+      </c>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>seconds</t>
+        </is>
+      </c>
+      <c r="H51" s="12" t="inlineStr">
+        <is>
+          <t>param:interval</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>Heat Pack</t>
+          <t>Bing Boing</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>Cold decay</t>
+          <t>Power length</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr"/>
-      <c r="E52" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="E52" s="12" t="inlineStr"/>
       <c r="F52" s="13" t="n">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>seconds</t>
         </is>
       </c>
       <c r="H52" s="12" t="inlineStr">
         <is>
-          <t>mod:0</t>
+          <t>param:duration</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>Heat Pack</t>
+          <t>Bing Boing</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Cold build-up</t>
+          <t>Low Gravity strength (the mushroom is 3)</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr"/>
-      <c r="E53" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="E53" s="12" t="inlineStr"/>
       <c r="F53" s="13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>strength</t>
         </is>
       </c>
       <c r="H53" s="12" t="inlineStr">
         <is>
-          <t>mod:1</t>
+          <t>param:lowGravity</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Fartberry Fitness</t>
+          <t>TechTara</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Climbing stamina cost</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>while you have more than 20 Poison</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+          <t>Fall damage reduced</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr"/>
+      <c r="E54" s="5" t="inlineStr"/>
       <c r="F54" s="13" t="n">
-        <v>-40</v>
+        <v>20</v>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>mod:0</t>
+          <t>param:base</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Fartberry Fitness</t>
+          <t>TechTara</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Poison decay</t>
+          <t>Extra reduction per bandage</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr"/>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="E55" s="5" t="inlineStr"/>
       <c r="F55" s="13" t="n">
-        <v>-10</v>
+        <v>20</v>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>mod:1</t>
+          <t>param:perBandage</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="B56" s="12" t="inlineStr">
-        <is>
-          <t>BingBong</t>
-        </is>
-      </c>
-      <c r="C56" s="12" t="inlineStr">
-        <is>
-          <t>Time between powers</t>
-        </is>
-      </c>
-      <c r="D56" s="12" t="inlineStr"/>
-      <c r="E56" s="12" t="inlineStr"/>
+      <c r="A56" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>TechTara</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Bandages counted at most</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr"/>
+      <c r="E56" s="5" t="inlineStr"/>
       <c r="F56" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G56" s="12" t="inlineStr">
-        <is>
-          <t>seconds</t>
-        </is>
-      </c>
-      <c r="H56" s="12" t="inlineStr">
-        <is>
-          <t>param:interval</t>
+        <v>3</v>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>bandages</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>param:limit</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>BingBong</t>
+          <t>Walk It Off</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Power length</t>
-        </is>
-      </c>
-      <c r="D57" s="12" t="inlineStr"/>
-      <c r="E57" s="12" t="inlineStr"/>
+          <t>Climbing stamina cost</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>while you have 20+ Injury</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F57" s="13" t="n">
-        <v>20</v>
+        <v>-35</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>seconds</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H57" s="12" t="inlineStr">
         <is>
-          <t>param:duration</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>Walk It Off</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>Sprint stamina cost</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>while you have 20+ Injury</t>
+        </is>
+      </c>
+      <c r="E58" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F58" s="13" t="n">
+        <v>-35</v>
+      </c>
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H58" s="12" t="inlineStr">
+        <is>
+          <t>mod:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>Walk It Off</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>All Injury</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr"/>
+      <c r="E59" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F59" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G59" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H59" s="12" t="inlineStr">
+        <is>
+          <t>mod:2</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Discount Cure-All</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Needs at least this much of the status</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr"/>
+      <c r="E60" s="5" t="inlineStr"/>
+      <c r="F60" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="B58" s="12" t="inlineStr">
-        <is>
-          <t>BingBong</t>
-        </is>
-      </c>
-      <c r="C58" s="12" t="inlineStr">
-        <is>
-          <t>Low Gravity strength (the mushroom is 3)</t>
-        </is>
-      </c>
-      <c r="D58" s="12" t="inlineStr"/>
-      <c r="E58" s="12" t="inlineStr"/>
-      <c r="F58" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G58" s="12" t="inlineStr">
-        <is>
-          <t>strength</t>
-        </is>
-      </c>
-      <c r="H58" s="12" t="inlineStr">
-        <is>
-          <t>param:lowGravity</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>Injury healed by items (received)</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr"/>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F59" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H59" s="5" t="inlineStr">
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>param:threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Discount Cure-All</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Status removed</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr"/>
+      <c r="E61" s="5" t="inlineStr"/>
+      <c r="F61" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>param:remove</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Perma-Cooking</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Hunger removed by food</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr"/>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F62" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
         <is>
           <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="B60" s="12" t="inlineStr">
-        <is>
-          <t>Walk It Off</t>
-        </is>
-      </c>
-      <c r="C60" s="12" t="inlineStr">
-        <is>
-          <t>Climbing stamina cost</t>
-        </is>
-      </c>
-      <c r="D60" s="12" t="inlineStr">
-        <is>
-          <t>while you have 20+ Injury</t>
-        </is>
-      </c>
-      <c r="E60" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F60" s="13" t="n">
-        <v>-25</v>
-      </c>
-      <c r="G60" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H60" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="B61" s="12" t="inlineStr">
-        <is>
-          <t>Walk It Off</t>
-        </is>
-      </c>
-      <c r="C61" s="12" t="inlineStr">
-        <is>
-          <t>Sprint stamina cost</t>
-        </is>
-      </c>
-      <c r="D61" s="12" t="inlineStr">
-        <is>
-          <t>while you have 20+ Injury</t>
-        </is>
-      </c>
-      <c r="E61" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F61" s="13" t="n">
-        <v>-25</v>
-      </c>
-      <c r="G61" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H61" s="12" t="inlineStr">
-        <is>
-          <t>mod:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="B62" s="12" t="inlineStr">
-        <is>
-          <t>Walk It Off</t>
-        </is>
-      </c>
-      <c r="C62" s="12" t="inlineStr">
-        <is>
-          <t>All Injury</t>
-        </is>
-      </c>
-      <c r="D62" s="12" t="inlineStr"/>
-      <c r="E62" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F62" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="G62" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H62" s="12" t="inlineStr">
-        <is>
-          <t>mod:2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Discount Cure-All</t>
+          <t>Mini Tenacity</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Needs at least this much of the status</t>
+          <t>Least removed</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr"/>
       <c r="E63" s="5" t="inlineStr"/>
       <c r="F63" s="13" t="n">
-        <v>25</v>
+        <v>2.5</v>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
@@ -4702,28 +4642,28 @@
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>param:threshold</t>
+          <t>param:min</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Discount Cure-All</t>
+          <t>Mini Tenacity</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Status removed</t>
+          <t>Most removed</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr"/>
       <c r="E64" s="5" t="inlineStr"/>
       <c r="F64" s="13" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
@@ -4732,73 +4672,73 @@
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>param:remove</t>
+          <t>param:max</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>Gourmand's Gut</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>Hunger removed by food</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr"/>
-      <c r="E65" s="5" t="inlineStr">
+      <c r="A65" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>Bing Bong's Baggage</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>All carried weight</t>
+        </is>
+      </c>
+      <c r="D65" s="12" t="inlineStr"/>
+      <c r="E65" s="12" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H65" s="5" t="inlineStr">
+        <v>-60</v>
+      </c>
+      <c r="G65" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H65" s="12" t="inlineStr">
         <is>
           <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="B66" s="12" t="inlineStr">
-        <is>
-          <t>Book of Broken Bones</t>
-        </is>
-      </c>
-      <c r="C66" s="12" t="inlineStr">
-        <is>
-          <t>Curse added by revival</t>
-        </is>
-      </c>
-      <c r="D66" s="12" t="inlineStr"/>
-      <c r="E66" s="12" t="inlineStr">
+      <c r="A66" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Carry-On Only</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>Held item weight</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr"/>
+      <c r="E66" s="5" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G66" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H66" s="12" t="inlineStr">
+        <v>-45</v>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
         <is>
           <t>mod:0</t>
         </is>
@@ -4806,46 +4746,50 @@
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Mini Tenacity</t>
+          <t>Carry-On Only</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Extra status removed</t>
+          <t>Backpack content weight</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr"/>
-      <c r="E67" s="5" t="inlineStr"/>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F67" s="13" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>param:bonus</t>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B68" s="12" t="inlineStr">
         <is>
-          <t>Bing Bong's Baggage</t>
+          <t>Super Idol Hands</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>All carried weight</t>
+          <t>Held item weight</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr"/>
@@ -4855,7 +4799,7 @@
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
@@ -4870,16 +4814,16 @@
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Carry-On Only</t>
+          <t>Cook It, Keep It</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Held item weight</t>
+          <t>Hunger removed by cooked food</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr"/>
@@ -4889,7 +4833,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>-45</v>
+        <v>40</v>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
@@ -4904,16 +4848,16 @@
     </row>
     <row r="70">
       <c r="A70" s="5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Carry-On Only</t>
+          <t>Cook It, Keep It</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Backpack content weight</t>
+          <t>Uncooked food nutrition</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr"/>
@@ -4923,7 +4867,7 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>5</v>
+        <v>-15</v>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
@@ -4938,16 +4882,16 @@
     </row>
     <row r="71">
       <c r="A71" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>Idol Hands</t>
+          <t>Cooked</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Held item weight</t>
+          <t>Hunger removed by cooked food</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr"/>
@@ -4957,7 +4901,7 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>-65</v>
+        <v>60</v>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
@@ -4972,132 +4916,124 @@
     </row>
     <row r="72">
       <c r="A72" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B72" s="12" t="inlineStr">
         <is>
-          <t>Idol Hands</t>
+          <t>Cooked</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>Climbing stamina cost</t>
-        </is>
-      </c>
-      <c r="D72" s="12" t="inlineStr">
-        <is>
-          <t>while you climb with an item in your hands</t>
-        </is>
-      </c>
-      <c r="E72" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+          <t>Poison added</t>
+        </is>
+      </c>
+      <c r="D72" s="12" t="inlineStr"/>
+      <c r="E72" s="12" t="inlineStr"/>
       <c r="F72" s="13" t="n">
-        <v>-15</v>
+        <v>5</v>
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>points</t>
         </is>
       </c>
       <c r="H72" s="12" t="inlineStr">
         <is>
-          <t>mod:1</t>
+          <t>param:poison</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Cook It, Keep It</t>
+          <t>Clown Luggage Special</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Hunger removed by cooked food</t>
+          <t>Bonus cards</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr"/>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="E73" s="5" t="inlineStr"/>
       <c r="F73" s="13" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>cards</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
+          <t>param:bonusCards</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="B74" s="12" t="inlineStr">
+        <is>
+          <t>Rule Zero</t>
+        </is>
+      </c>
+      <c r="C74" s="12" t="inlineStr">
+        <is>
+          <t>Climbing stamina cost</t>
+        </is>
+      </c>
+      <c r="D74" s="12" t="inlineStr"/>
+      <c r="E74" s="12" t="inlineStr">
+        <is>
+          <t>Teammates within 8 m</t>
+        </is>
+      </c>
+      <c r="F74" s="13" t="n">
+        <v>-20</v>
+      </c>
+      <c r="G74" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H74" s="12" t="inlineStr">
+        <is>
           <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>Cook It, Keep It</t>
-        </is>
-      </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>Uncooked food nutrition</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr"/>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F74" s="13" t="n">
-        <v>-15</v>
-      </c>
-      <c r="G74" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H74" s="5" t="inlineStr">
-        <is>
-          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>Cooking Badge Deluxe</t>
+          <t>Rule Zero</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Hunger removed by cooked food</t>
-        </is>
-      </c>
-      <c r="D75" s="12" t="inlineStr"/>
+          <t>Climbing stamina cost</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>while a teammate is near you</t>
+        </is>
+      </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>50</v>
+        <v>-20</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
@@ -5106,88 +5042,100 @@
       </c>
       <c r="H75" s="12" t="inlineStr">
         <is>
-          <t>mod:0</t>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B76" s="12" t="inlineStr">
         <is>
-          <t>Cooking Badge Deluxe</t>
+          <t>Rule Zero</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>Poison added</t>
-        </is>
-      </c>
-      <c r="D76" s="12" t="inlineStr"/>
-      <c r="E76" s="12" t="inlineStr"/>
+          <t>Climbing stamina cost</t>
+        </is>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>while no teammate is near you</t>
+        </is>
+      </c>
+      <c r="E76" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F76" s="13" t="n">
         <v>5</v>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H76" s="12" t="inlineStr">
         <is>
-          <t>param:poison</t>
+          <t>mod:2</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="B77" s="5" t="inlineStr">
-        <is>
-          <t>Clown Luggage Special</t>
-        </is>
-      </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>Bonus cards</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="inlineStr"/>
-      <c r="E77" s="5" t="inlineStr"/>
+      <c r="A77" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="B77" s="12" t="inlineStr">
+        <is>
+          <t>Rule Zero</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="D77" s="12" t="inlineStr"/>
+      <c r="E77" s="12" t="inlineStr"/>
       <c r="F77" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G77" s="5" t="inlineStr">
-        <is>
-          <t>cards</t>
-        </is>
-      </c>
-      <c r="H77" s="5" t="inlineStr">
-        <is>
-          <t>param:bonusCards</t>
+        <v>8</v>
+      </c>
+      <c r="G77" s="12" t="inlineStr">
+        <is>
+          <t>metres</t>
+        </is>
+      </c>
+      <c r="H77" s="12" t="inlineStr">
+        <is>
+          <t>param:radius</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Clown Luggage Special</t>
+          <t>First Aid Badge</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Possible penalty: climbing stamina cost</t>
+          <t>Injury healed by items (given to teammates)</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr"/>
-      <c r="E78" s="5" t="inlineStr"/>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F78" s="13" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
@@ -5196,28 +5144,32 @@
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>param:climbPenalty</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Clown Luggage Special</t>
+          <t>First Aid Badge</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Possible penalty: sprint stamina cost</t>
+          <t>Injury healed by items (used on yourself)</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr"/>
-      <c r="E79" s="5" t="inlineStr"/>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F79" s="13" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
@@ -5226,137 +5178,141 @@
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>param:sprintPenalty</t>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="B80" s="5" t="inlineStr">
-        <is>
-          <t>Clown Luggage Special</t>
-        </is>
-      </c>
-      <c r="C80" s="5" t="inlineStr">
-        <is>
-          <t>Possible penalty: all Injury</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr"/>
-      <c r="E80" s="5" t="inlineStr"/>
+      <c r="A80" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="B80" s="12" t="inlineStr">
+        <is>
+          <t>Carry-On Scout</t>
+        </is>
+      </c>
+      <c r="C80" s="12" t="inlineStr">
+        <is>
+          <t>Carried scout weight</t>
+        </is>
+      </c>
+      <c r="D80" s="12" t="inlineStr"/>
+      <c r="E80" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F80" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G80" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H80" s="5" t="inlineStr">
-        <is>
-          <t>param:injuryPenalty</t>
+        <v>-75</v>
+      </c>
+      <c r="G80" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H80" s="12" t="inlineStr">
+        <is>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>Clown Luggage Special</t>
-        </is>
-      </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>Possible penalty: Hunger build-up</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="inlineStr"/>
-      <c r="E81" s="5" t="inlineStr"/>
+      <c r="A81" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="B81" s="12" t="inlineStr">
+        <is>
+          <t>Carry-On Scout</t>
+        </is>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>Helping-hand reach</t>
+        </is>
+      </c>
+      <c r="D81" s="12" t="inlineStr"/>
+      <c r="E81" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F81" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G81" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H81" s="5" t="inlineStr">
-        <is>
-          <t>param:hungerPenalty</t>
+        <v>20</v>
+      </c>
+      <c r="G81" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H81" s="12" t="inlineStr">
+        <is>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="B82" s="12" t="inlineStr">
-        <is>
-          <t>Rule Zero</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="inlineStr">
-        <is>
-          <t>Climbing stamina cost</t>
-        </is>
-      </c>
-      <c r="D82" s="12" t="inlineStr"/>
-      <c r="E82" s="12" t="inlineStr">
-        <is>
-          <t>Teammates within 8 m</t>
+      <c r="A82" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>Ascent 5+</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>Huddle radius and cold removal</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr"/>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>-10</v>
-      </c>
-      <c r="G82" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H82" s="12" t="inlineStr">
+        <v>75</v>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
         <is>
           <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="B83" s="12" t="inlineStr">
-        <is>
-          <t>Rule Zero</t>
-        </is>
-      </c>
-      <c r="C83" s="12" t="inlineStr">
-        <is>
-          <t>Climbing stamina cost</t>
-        </is>
-      </c>
-      <c r="D83" s="12" t="inlineStr">
-        <is>
-          <t>while a teammate is near you</t>
-        </is>
-      </c>
-      <c r="E83" s="12" t="inlineStr">
+      <c r="A83" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>Ascent 5+</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>Cold build-up</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr"/>
+      <c r="E83" s="5" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>-10</v>
-      </c>
-      <c r="G83" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H83" s="12" t="inlineStr">
+        <v>-20</v>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
         <is>
           <t>mod:1</t>
         </is>
@@ -5364,128 +5320,120 @@
     </row>
     <row r="84">
       <c r="A84" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B84" s="12" t="inlineStr">
         <is>
-          <t>Rule Zero</t>
+          <t>Otto-Matic Clutch</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>Climbing stamina cost</t>
-        </is>
-      </c>
-      <c r="D84" s="12" t="inlineStr">
-        <is>
-          <t>while no teammate is near you</t>
-        </is>
-      </c>
-      <c r="E84" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+          <t>Yellow stamina for both scouts</t>
+        </is>
+      </c>
+      <c r="D84" s="12" t="inlineStr"/>
+      <c r="E84" s="12" t="inlineStr"/>
       <c r="F84" s="13" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>points</t>
         </is>
       </c>
       <c r="H84" s="12" t="inlineStr">
         <is>
-          <t>mod:2</t>
+          <t>param:bonus</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="B85" s="12" t="inlineStr">
-        <is>
-          <t>Rule Zero</t>
-        </is>
-      </c>
-      <c r="C85" s="12" t="inlineStr">
-        <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="D85" s="12" t="inlineStr"/>
-      <c r="E85" s="12" t="inlineStr"/>
+      <c r="A85" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>You're alright, you're alright</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Helping-hand reach</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr"/>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F85" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="G85" s="12" t="inlineStr">
-        <is>
-          <t>metres</t>
-        </is>
-      </c>
-      <c r="H85" s="12" t="inlineStr">
-        <is>
-          <t>param:radius</t>
+        <v>40</v>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>First Aid Badge</t>
+          <t>You're alright, you're alright</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Injury healed by items (given to teammates)</t>
+          <t>Stamina cost to start a pull</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr"/>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="E86" s="5" t="inlineStr"/>
       <c r="F86" s="13" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>points</t>
         </is>
       </c>
       <c r="H86" s="5" t="inlineStr">
         <is>
-          <t>mod:0</t>
+          <t>param:stamina</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>Human Carry-On</t>
+          <t>Take One for the Troop</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>Carried scout weight</t>
+          <t>All Injury</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr"/>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Teammates within 8 m</t>
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
@@ -5500,222 +5448,218 @@
     </row>
     <row r="88">
       <c r="A88" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B88" s="12" t="inlineStr">
         <is>
-          <t>Human Carry-On</t>
+          <t>Take One for the Troop</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>Helping-hand reach</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr"/>
-      <c r="E88" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="E88" s="12" t="inlineStr"/>
       <c r="F88" s="13" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>metres</t>
         </is>
       </c>
       <c r="H88" s="12" t="inlineStr">
         <is>
-          <t>mod:1</t>
+          <t>param:radius</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="B89" s="5" t="inlineStr">
-        <is>
-          <t>Happy Camper Huddle</t>
-        </is>
-      </c>
-      <c r="C89" s="5" t="inlineStr">
-        <is>
-          <t>Huddle radius and cold removal</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="inlineStr"/>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="A89" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="B89" s="12" t="inlineStr">
+        <is>
+          <t>Take One for the Troop</t>
+        </is>
+      </c>
+      <c r="C89" s="12" t="inlineStr">
+        <is>
+          <t>Share of the prevented Injury you take</t>
+        </is>
+      </c>
+      <c r="D89" s="12" t="inlineStr"/>
+      <c r="E89" s="12" t="inlineStr"/>
       <c r="F89" s="13" t="n">
-        <v>75</v>
-      </c>
-      <c r="G89" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H89" s="5" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="G89" s="12" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H89" s="12" t="inlineStr">
+        <is>
+          <t>param:absorb</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="B90" s="12" t="inlineStr">
+        <is>
+          <t>Take One for the Troop</t>
+        </is>
+      </c>
+      <c r="C90" s="12" t="inlineStr">
+        <is>
+          <t>Most Injury you take per hit</t>
+        </is>
+      </c>
+      <c r="D90" s="12" t="inlineStr"/>
+      <c r="E90" s="12" t="inlineStr"/>
+      <c r="F90" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G90" s="12" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H90" s="12" t="inlineStr">
+        <is>
+          <t>param:cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>Friendship Bugles</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Max stamina</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr"/>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>Teammates within 8 m</t>
+        </is>
+      </c>
+      <c r="F91" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>stamina points</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
         <is>
           <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="B90" s="5" t="inlineStr">
-        <is>
-          <t>Happy Camper Huddle</t>
-        </is>
-      </c>
-      <c r="C90" s="5" t="inlineStr">
-        <is>
-          <t>Cold build-up</t>
-        </is>
-      </c>
-      <c r="D90" s="5" t="inlineStr"/>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F90" s="13" t="n">
-        <v>-20</v>
-      </c>
-      <c r="G90" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H90" s="5" t="inlineStr">
-        <is>
-          <t>mod:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="B91" s="12" t="inlineStr">
-        <is>
-          <t>Otto-Matic Clutch</t>
-        </is>
-      </c>
-      <c r="C91" s="12" t="inlineStr">
-        <is>
-          <t>Yellow stamina for both scouts</t>
-        </is>
-      </c>
-      <c r="D91" s="12" t="inlineStr"/>
-      <c r="E91" s="12" t="inlineStr"/>
-      <c r="F91" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="G91" s="12" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H91" s="12" t="inlineStr">
-        <is>
-          <t>param:bonus</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>You're alright, you're alright</t>
+          <t>Friendship Bugles</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>Helping-hand reach</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr"/>
+          <t>Max stamina</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>while a teammate is near you</t>
+        </is>
+      </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>stamina points</t>
         </is>
       </c>
       <c r="H92" s="5" t="inlineStr">
         <is>
-          <t>mod:0</t>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>You're alright, you're alright</t>
+          <t>Friendship Bugles</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Stamina cost to start a pull</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr"/>
       <c r="E93" s="5" t="inlineStr"/>
       <c r="F93" s="13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>metres</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>param:stamina</t>
+          <t>param:radius</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B94" s="12" t="inlineStr">
         <is>
-          <t>Take One for the Troop</t>
+          <t>Scout Cannon Legs</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>All Injury</t>
+          <t>Sprint speed</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr"/>
       <c r="E94" s="12" t="inlineStr">
         <is>
-          <t>Teammates within 6 m</t>
+          <t>You</t>
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>-30</v>
+        <v>35</v>
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
@@ -5730,242 +5674,234 @@
     </row>
     <row r="95">
       <c r="A95" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>Take One for the Troop</t>
+          <t>Scout Cannon Legs</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Jump height</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr"/>
-      <c r="E95" s="12" t="inlineStr"/>
+      <c r="E95" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F95" s="13" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
-          <t>metres</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H95" s="12" t="inlineStr">
         <is>
-          <t>param:radius</t>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B96" s="12" t="inlineStr">
         <is>
-          <t>Take One for the Troop</t>
+          <t>Scout Cannon Legs</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>Share of the prevented Injury you take</t>
+          <t>Fall Injury</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr"/>
-      <c r="E96" s="12" t="inlineStr"/>
+      <c r="E96" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F96" s="13" t="n">
         <v>25</v>
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H96" s="12" t="inlineStr">
         <is>
-          <t>param:absorb</t>
+          <t>mod:2</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="B97" s="12" t="inlineStr">
-        <is>
-          <t>Take One for the Troop</t>
-        </is>
-      </c>
-      <c r="C97" s="12" t="inlineStr">
-        <is>
-          <t>Most Injury you take per hit</t>
-        </is>
-      </c>
-      <c r="D97" s="12" t="inlineStr"/>
-      <c r="E97" s="12" t="inlineStr"/>
+      <c r="A97" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>Crown of Bad Decisions</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Yellow stamina when picked</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr"/>
+      <c r="E97" s="5" t="inlineStr"/>
       <c r="F97" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="G97" s="12" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="H97" s="12" t="inlineStr">
-        <is>
-          <t>param:cap</t>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>param:bonusNow</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>Friendship Bugle Choir</t>
+          <t>Crown of Bad Decisions</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Max stamina</t>
+          <t>Yellow stamina at each later campfire</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr"/>
-      <c r="E98" s="5" t="inlineStr">
-        <is>
-          <t>Teammates within 8 m</t>
-        </is>
-      </c>
+      <c r="E98" s="5" t="inlineStr"/>
       <c r="F98" s="13" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>stamina points</t>
+          <t>points</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
         <is>
-          <t>mod:0</t>
+          <t>param:bonusFire</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>Friendship Bugle Choir</t>
+          <t>Crown of Bad Decisions</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Max stamina</t>
-        </is>
-      </c>
-      <c r="D99" s="5" t="inlineStr">
-        <is>
-          <t>while a teammate is near you</t>
-        </is>
-      </c>
-      <c r="E99" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+          <t>Curse when picked</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr"/>
+      <c r="E99" s="5" t="inlineStr"/>
       <c r="F99" s="13" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>stamina points</t>
+          <t>points</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>mod:1</t>
+          <t>param:curseNow</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>Friendship Bugle Choir</t>
+          <t>Crown of Bad Decisions</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Curse at each later campfire</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr"/>
       <c r="E100" s="5" t="inlineStr"/>
       <c r="F100" s="13" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>metres</t>
+          <t>points</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
         <is>
-          <t>param:radius</t>
+          <t>param:curseFire</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="B101" s="12" t="inlineStr">
-        <is>
-          <t>Scout Cannon Legs</t>
-        </is>
-      </c>
-      <c r="C101" s="12" t="inlineStr">
-        <is>
-          <t>Sprint speed</t>
-        </is>
-      </c>
-      <c r="D101" s="12" t="inlineStr"/>
-      <c r="E101" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="A101" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>Crown of Bad Decisions</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>Most Curse this card can ever add</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr"/>
+      <c r="E101" s="5" t="inlineStr"/>
       <c r="F101" s="13" t="n">
-        <v>35</v>
-      </c>
-      <c r="G101" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H101" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
+        <v>5</v>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>param:curseBudget</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B102" s="12" t="inlineStr">
         <is>
-          <t>Scout Cannon Legs</t>
+          <t>Pandora's HotPocket</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>Jump height</t>
+          <t>Carried item weight</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr"/>
@@ -5975,7 +5911,7 @@
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>25</v>
+        <v>-25</v>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
@@ -5984,92 +5920,88 @@
       </c>
       <c r="H102" s="12" t="inlineStr">
         <is>
-          <t>mod:1</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>Scout Cannon Legs</t>
+          <t>Pandora's HotPocket</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>Fall Injury</t>
+          <t>Chance of a lucky roll</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr"/>
-      <c r="E103" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="E103" s="12" t="inlineStr"/>
       <c r="F103" s="13" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H103" s="12" t="inlineStr">
         <is>
-          <t>mod:2</t>
+          <t>param:chance</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B104" s="5" t="inlineStr">
-        <is>
-          <t>Crown of Bad Decisions</t>
-        </is>
-      </c>
-      <c r="C104" s="5" t="inlineStr">
-        <is>
-          <t>Yellow stamina when picked</t>
-        </is>
-      </c>
-      <c r="D104" s="5" t="inlineStr"/>
-      <c r="E104" s="5" t="inlineStr"/>
+      <c r="A104" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="B104" s="12" t="inlineStr">
+        <is>
+          <t>Pandora's HotPocket</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t>Yellow stamina on a lucky roll</t>
+        </is>
+      </c>
+      <c r="D104" s="12" t="inlineStr"/>
+      <c r="E104" s="12" t="inlineStr"/>
       <c r="F104" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="G104" s="5" t="inlineStr">
+        <v>37.5</v>
+      </c>
+      <c r="G104" s="12" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="H104" s="5" t="inlineStr">
-        <is>
-          <t>param:bonusNow</t>
+      <c r="H104" s="12" t="inlineStr">
+        <is>
+          <t>param:bonus</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>Crown of Bad Decisions</t>
+          <t>Bootleg Scoutmaster Bugle</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Yellow stamina at each later campfire</t>
+          <t>Yellow stamina per use</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr"/>
       <c r="E105" s="5" t="inlineStr"/>
       <c r="F105" s="13" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
@@ -6078,28 +6010,28 @@
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>param:bonusFire</t>
+          <t>param:bonus</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>Crown of Bad Decisions</t>
+          <t>Bootleg Scoutmaster Bugle</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>Curse when picked</t>
+          <t>Injury per use</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr"/>
       <c r="E106" s="5" t="inlineStr"/>
       <c r="F106" s="13" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
@@ -6108,304 +6040,324 @@
       </c>
       <c r="H106" s="5" t="inlineStr">
         <is>
-          <t>param:curseNow</t>
+          <t>param:injury</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B107" s="5" t="inlineStr">
-        <is>
-          <t>Crown of Bad Decisions</t>
-        </is>
-      </c>
-      <c r="C107" s="5" t="inlineStr">
-        <is>
-          <t>Curse at each later campfire</t>
-        </is>
-      </c>
-      <c r="D107" s="5" t="inlineStr"/>
-      <c r="E107" s="5" t="inlineStr"/>
+      <c r="A107" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="B107" s="12" t="inlineStr">
+        <is>
+          <t>Big Lollipop Crash</t>
+        </is>
+      </c>
+      <c r="C107" s="12" t="inlineStr">
+        <is>
+          <t>Sprint speed</t>
+        </is>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>while your sprint speed-up is on</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F107" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G107" s="5" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H107" s="5" t="inlineStr">
-        <is>
-          <t>param:curseFire</t>
+        <v>30</v>
+      </c>
+      <c r="G107" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H107" s="12" t="inlineStr">
+        <is>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B108" s="5" t="inlineStr">
-        <is>
-          <t>Crown of Bad Decisions</t>
-        </is>
-      </c>
-      <c r="C108" s="5" t="inlineStr">
-        <is>
-          <t>Most Curse this card can ever add</t>
-        </is>
-      </c>
-      <c r="D108" s="5" t="inlineStr"/>
-      <c r="E108" s="5" t="inlineStr"/>
+      <c r="A108" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="B108" s="12" t="inlineStr">
+        <is>
+          <t>Big Lollipop Crash</t>
+        </is>
+      </c>
+      <c r="C108" s="12" t="inlineStr">
+        <is>
+          <t>Sprint time before the speed-up</t>
+        </is>
+      </c>
+      <c r="D108" s="12" t="inlineStr"/>
+      <c r="E108" s="12" t="inlineStr"/>
       <c r="F108" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="G108" s="5" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H108" s="5" t="inlineStr">
-        <is>
-          <t>param:curseBudget</t>
+        <v>2</v>
+      </c>
+      <c r="G108" s="12" t="inlineStr">
+        <is>
+          <t>seconds</t>
+        </is>
+      </c>
+      <c r="H108" s="12" t="inlineStr">
+        <is>
+          <t>param:buildup</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="B109" s="12" t="inlineStr">
-        <is>
-          <t>Pandora's Pocket Gamble</t>
-        </is>
-      </c>
-      <c r="C109" s="12" t="inlineStr">
-        <is>
-          <t>Carried item weight</t>
-        </is>
-      </c>
-      <c r="D109" s="12" t="inlineStr"/>
-      <c r="E109" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="A109" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>Piton Payment Plan</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>Share of each fall's Injury that is delayed</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr"/>
+      <c r="E109" s="5" t="inlineStr"/>
       <c r="F109" s="13" t="n">
-        <v>-10</v>
-      </c>
-      <c r="G109" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H109" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
+        <v>75</v>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>param:defer</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="B110" s="12" t="inlineStr">
-        <is>
-          <t>Pandora's Pocket Gamble</t>
-        </is>
-      </c>
-      <c r="C110" s="12" t="inlineStr">
-        <is>
-          <t>Chance of a lucky roll</t>
-        </is>
-      </c>
-      <c r="D110" s="12" t="inlineStr"/>
-      <c r="E110" s="12" t="inlineStr"/>
+      <c r="A110" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>Piton Payment Plan</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>Delay before the rest lands</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr"/>
+      <c r="E110" s="5" t="inlineStr"/>
       <c r="F110" s="13" t="n">
-        <v>65</v>
-      </c>
-      <c r="G110" s="12" t="inlineStr">
+        <v>20</v>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>seconds</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="inlineStr">
+        <is>
+          <t>param:delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>Piton Payment Plan</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>Share of the delayed Injury that still lands</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr"/>
+      <c r="E111" s="5" t="inlineStr"/>
+      <c r="F111" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H110" s="12" t="inlineStr">
-        <is>
-          <t>param:chance</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="B111" s="12" t="inlineStr">
-        <is>
-          <t>Pandora's Pocket Gamble</t>
-        </is>
-      </c>
-      <c r="C111" s="12" t="inlineStr">
-        <is>
-          <t>Yellow stamina on a lucky roll</t>
-        </is>
-      </c>
-      <c r="D111" s="12" t="inlineStr"/>
-      <c r="E111" s="12" t="inlineStr"/>
-      <c r="F111" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="G111" s="12" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H111" s="12" t="inlineStr">
-        <is>
-          <t>param:bonus</t>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>param:keep</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B112" s="12" t="inlineStr">
         <is>
-          <t>Pandora's Pocket Gamble</t>
+          <t>Glass Scout Cannon</t>
         </is>
       </c>
       <c r="C112" s="12" t="inlineStr">
         <is>
-          <t>Injury on an unlucky roll</t>
+          <t>Max stamina</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr"/>
-      <c r="E112" s="12" t="inlineStr"/>
+      <c r="E112" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F112" s="13" t="n">
-        <v>7.5</v>
+        <v>40</v>
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>stamina points</t>
         </is>
       </c>
       <c r="H112" s="12" t="inlineStr">
         <is>
-          <t>param:injury</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="n">
-        <v>52</v>
-      </c>
-      <c r="B113" s="5" t="inlineStr">
-        <is>
-          <t>Bootleg Scoutmaster Bugle</t>
-        </is>
-      </c>
-      <c r="C113" s="5" t="inlineStr">
-        <is>
-          <t>Yellow stamina per use</t>
-        </is>
-      </c>
-      <c r="D113" s="5" t="inlineStr"/>
-      <c r="E113" s="5" t="inlineStr"/>
+      <c r="A113" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="B113" s="12" t="inlineStr">
+        <is>
+          <t>Glass Scout Cannon</t>
+        </is>
+      </c>
+      <c r="C113" s="12" t="inlineStr">
+        <is>
+          <t>All Injury</t>
+        </is>
+      </c>
+      <c r="D113" s="12" t="inlineStr"/>
+      <c r="E113" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F113" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="G113" s="5" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H113" s="5" t="inlineStr">
-        <is>
-          <t>param:bonus</t>
+        <v>25</v>
+      </c>
+      <c r="G113" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H113" s="12" t="inlineStr">
+        <is>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>Bootleg Scoutmaster Bugle</t>
+          <t>Baggage Claim Escapee</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>Injury per use</t>
-        </is>
-      </c>
-      <c r="D114" s="5" t="inlineStr"/>
-      <c r="E114" s="5" t="inlineStr"/>
+          <t>Sprint speed</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>while you don't wear a backpack</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F114" s="13" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H114" s="5" t="inlineStr">
         <is>
-          <t>param:injury</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="B115" s="12" t="inlineStr">
-        <is>
-          <t>Big Lollipop Crash</t>
-        </is>
-      </c>
-      <c r="C115" s="12" t="inlineStr">
-        <is>
-          <t>Sprint speed</t>
-        </is>
-      </c>
-      <c r="D115" s="12" t="inlineStr">
-        <is>
-          <t>while your sprint speed-up is on</t>
-        </is>
-      </c>
-      <c r="E115" s="12" t="inlineStr">
+      <c r="A115" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>Baggage Claim Escapee</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>Jump height</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>while you don't wear a backpack</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F115" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="G115" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H115" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
+        <v>20</v>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B116" s="12" t="inlineStr">
         <is>
-          <t>Big Lollipop Crash</t>
+          <t>Scout's Dishonor</t>
         </is>
       </c>
       <c r="C116" s="12" t="inlineStr">
         <is>
-          <t>Sprint time before the speed-up</t>
+          <t>Bonus cards (Common to Rare)</t>
         </is>
       </c>
       <c r="D116" s="12" t="inlineStr"/>
@@ -6415,33 +6367,33 @@
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
-          <t>seconds</t>
+          <t>cards</t>
         </is>
       </c>
       <c r="H116" s="12" t="inlineStr">
         <is>
-          <t>param:buildup</t>
+          <t>param:bonusCards</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>Big Lollipop Crash</t>
+          <t>Scout's Dishonor</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Drowsy added</t>
+          <t>Curse when picked</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr"/>
       <c r="E117" s="12" t="inlineStr"/>
       <c r="F117" s="13" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
@@ -6450,176 +6402,172 @@
       </c>
       <c r="H117" s="12" t="inlineStr">
         <is>
-          <t>param:drowsy</t>
+          <t>param:curse</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B118" s="12" t="inlineStr">
         <is>
-          <t>Big Lollipop Crash</t>
+          <t>Scout's Dishonor</t>
         </is>
       </c>
       <c r="C118" s="12" t="inlineStr">
         <is>
-          <t>Time between Drowsy penalties</t>
+          <t>Cards in your next offer</t>
         </is>
       </c>
       <c r="D118" s="12" t="inlineStr"/>
       <c r="E118" s="12" t="inlineStr"/>
       <c r="F118" s="13" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
-          <t>seconds</t>
+          <t>cards</t>
         </is>
       </c>
       <c r="H118" s="12" t="inlineStr">
         <is>
-          <t>param:cooldown</t>
+          <t>param:nextOffer</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>Piton Payment Plan</t>
+          <t>TSA</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>Share of each fall's Injury that is delayed</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr"/>
       <c r="E119" s="5" t="inlineStr"/>
       <c r="F119" s="13" t="n">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>metres</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>param:defer</t>
+          <t>param:radius</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="5" t="n">
-        <v>54</v>
-      </c>
-      <c r="B120" s="5" t="inlineStr">
-        <is>
-          <t>Piton Payment Plan</t>
-        </is>
-      </c>
-      <c r="C120" s="5" t="inlineStr">
-        <is>
-          <t>Delay before the rest lands</t>
-        </is>
-      </c>
-      <c r="D120" s="5" t="inlineStr"/>
-      <c r="E120" s="5" t="inlineStr"/>
+      <c r="A120" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="B120" s="12" t="inlineStr">
+        <is>
+          <t>Medicinal Munchies</t>
+        </is>
+      </c>
+      <c r="C120" s="12" t="inlineStr">
+        <is>
+          <t>Needs at least this much Injury</t>
+        </is>
+      </c>
+      <c r="D120" s="12" t="inlineStr"/>
+      <c r="E120" s="12" t="inlineStr"/>
       <c r="F120" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="G120" s="5" t="inlineStr">
-        <is>
-          <t>seconds</t>
-        </is>
-      </c>
-      <c r="H120" s="5" t="inlineStr">
-        <is>
-          <t>param:delay</t>
+      <c r="G120" s="12" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H120" s="12" t="inlineStr">
+        <is>
+          <t>param:threshold</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="5" t="n">
-        <v>54</v>
-      </c>
-      <c r="B121" s="5" t="inlineStr">
-        <is>
-          <t>Piton Payment Plan</t>
-        </is>
-      </c>
-      <c r="C121" s="5" t="inlineStr">
-        <is>
-          <t>Share of the delayed Injury that still lands</t>
-        </is>
-      </c>
-      <c r="D121" s="5" t="inlineStr"/>
-      <c r="E121" s="5" t="inlineStr"/>
+      <c r="A121" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="B121" s="12" t="inlineStr">
+        <is>
+          <t>Medicinal Munchies</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>Injury removed</t>
+        </is>
+      </c>
+      <c r="D121" s="12" t="inlineStr"/>
+      <c r="E121" s="12" t="inlineStr"/>
       <c r="F121" s="13" t="n">
-        <v>80</v>
-      </c>
-      <c r="G121" s="5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H121" s="5" t="inlineStr">
-        <is>
-          <t>param:keep</t>
+        <v>7.5</v>
+      </c>
+      <c r="G121" s="12" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H121" s="12" t="inlineStr">
+        <is>
+          <t>param:heal</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="B122" s="12" t="inlineStr">
-        <is>
-          <t>Glass Scout Cannon</t>
-        </is>
-      </c>
-      <c r="C122" s="12" t="inlineStr">
-        <is>
-          <t>Max stamina</t>
-        </is>
-      </c>
-      <c r="D122" s="12" t="inlineStr"/>
-      <c r="E122" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="A122" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>Budget Checkpoint Flag</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>Injury after the revive</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr"/>
+      <c r="E122" s="5" t="inlineStr"/>
       <c r="F122" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="G122" s="12" t="inlineStr">
-        <is>
-          <t>stamina points</t>
-        </is>
-      </c>
-      <c r="H122" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
+        <v>0</v>
+      </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="inlineStr">
+        <is>
+          <t>param:injury</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="12" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>Glass Scout Cannon</t>
+          <t>Petrify Procrastination</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>All Injury</t>
+          <t>Petrify build-up</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr"/>
@@ -6629,7 +6577,7 @@
         </is>
       </c>
       <c r="F123" s="13" t="n">
-        <v>25</v>
+        <v>-50</v>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
@@ -6638,40 +6586,36 @@
       </c>
       <c r="H123" s="12" t="inlineStr">
         <is>
-          <t>mod:1</t>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>Baggage Claim Escapee</t>
+          <t>Fine Print</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>Sprint speed</t>
-        </is>
-      </c>
-      <c r="D124" s="5" t="inlineStr">
-        <is>
-          <t>while you don't wear a backpack</t>
-        </is>
-      </c>
+          <t>Max stamina</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr"/>
       <c r="E124" s="5" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F124" s="13" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>stamina points</t>
         </is>
       </c>
       <c r="H124" s="5" t="inlineStr">
@@ -6682,267 +6626,275 @@
     </row>
     <row r="125">
       <c r="A125" s="5" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>Baggage Claim Escapee</t>
+          <t>Fine Print</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>Jump height</t>
-        </is>
-      </c>
-      <c r="D125" s="5" t="inlineStr">
-        <is>
-          <t>while you don't wear a backpack</t>
-        </is>
-      </c>
-      <c r="E125" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+          <t>Curse when the sacrifice is made</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr"/>
+      <c r="E125" s="5" t="inlineStr"/>
       <c r="F125" s="13" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>% change</t>
+          <t>points</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
-          <t>mod:1</t>
+          <t>param:curse</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="B126" s="5" t="inlineStr">
-        <is>
-          <t>Baggage Claim Escapee</t>
-        </is>
-      </c>
-      <c r="C126" s="5" t="inlineStr">
-        <is>
-          <t>Sprint speed</t>
-        </is>
-      </c>
-      <c r="D126" s="5" t="inlineStr">
-        <is>
-          <t>while you wear a backpack</t>
-        </is>
-      </c>
-      <c r="E126" s="5" t="inlineStr">
+      <c r="A126" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="B126" s="12" t="inlineStr">
+        <is>
+          <t>Scoutmaster</t>
+        </is>
+      </c>
+      <c r="C126" s="12" t="inlineStr">
+        <is>
+          <t>Climbing stamina cost (set, ignores other cards)</t>
+        </is>
+      </c>
+      <c r="D126" s="12" t="inlineStr"/>
+      <c r="E126" s="12" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
       <c r="F126" s="13" t="n">
-        <v>-5</v>
-      </c>
-      <c r="G126" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H126" s="5" t="inlineStr">
-        <is>
-          <t>mod:2</t>
+        <v>-100</v>
+      </c>
+      <c r="G126" s="12" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H126" s="12" t="inlineStr">
+        <is>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="12" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>Scout's Dishonor</t>
+          <t>Scoutmaster</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>Bonus cards (Common to Rare)</t>
+          <t>Fall Injury (set, ignores other cards)</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr"/>
-      <c r="E127" s="12" t="inlineStr"/>
+      <c r="E127" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F127" s="13" t="n">
-        <v>2</v>
+        <v>-100</v>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
-          <t>cards</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H127" s="12" t="inlineStr">
         <is>
-          <t>param:bonusCards</t>
+          <t>mod:1</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="12" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B128" s="12" t="inlineStr">
         <is>
-          <t>Scout's Dishonor</t>
+          <t>Scoutmaster</t>
         </is>
       </c>
       <c r="C128" s="12" t="inlineStr">
         <is>
-          <t>Curse when picked</t>
+          <t>Sprint speed</t>
         </is>
       </c>
       <c r="D128" s="12" t="inlineStr"/>
-      <c r="E128" s="12" t="inlineStr"/>
+      <c r="E128" s="12" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
       <c r="F128" s="13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>% change</t>
         </is>
       </c>
       <c r="H128" s="12" t="inlineStr">
         <is>
-          <t>param:curse</t>
+          <t>mod:2</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="B129" s="12" t="inlineStr">
-        <is>
-          <t>Scout's Dishonor</t>
-        </is>
-      </c>
-      <c r="C129" s="12" t="inlineStr">
-        <is>
-          <t>Cards in your next offer</t>
-        </is>
-      </c>
-      <c r="D129" s="12" t="inlineStr"/>
-      <c r="E129" s="12" t="inlineStr"/>
+      <c r="A129" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>The Eternal Campfire</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>Max stamina</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr"/>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>You and teammates within 15 m</t>
+        </is>
+      </c>
       <c r="F129" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G129" s="12" t="inlineStr">
-        <is>
-          <t>cards</t>
-        </is>
-      </c>
-      <c r="H129" s="12" t="inlineStr">
-        <is>
-          <t>param:nextOffer</t>
+        <v>35</v>
+      </c>
+      <c r="G129" s="5" t="inlineStr">
+        <is>
+          <t>stamina points</t>
+        </is>
+      </c>
+      <c r="H129" s="5" t="inlineStr">
+        <is>
+          <t>mod:0</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>BingBong Baggage Scanner</t>
+          <t>The Eternal Campfire</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
+          <t>All Injury</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr"/>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>You and teammates within 15 m</t>
+        </is>
+      </c>
+      <c r="F130" s="13" t="n">
+        <v>-60</v>
+      </c>
+      <c r="G130" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H130" s="5" t="inlineStr">
+        <is>
+          <t>mod:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>The Eternal Campfire</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>All negative status build-up</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr"/>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>You and teammates within 15 m</t>
+        </is>
+      </c>
+      <c r="F131" s="13" t="n">
+        <v>-60</v>
+      </c>
+      <c r="G131" s="5" t="inlineStr">
+        <is>
+          <t>% change</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="inlineStr">
+        <is>
+          <t>mod:2</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>The Eternal Campfire</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="D130" s="5" t="inlineStr"/>
-      <c r="E130" s="5" t="inlineStr"/>
-      <c r="F130" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="G130" s="5" t="inlineStr">
+      <c r="D132" s="5" t="inlineStr"/>
+      <c r="E132" s="5" t="inlineStr"/>
+      <c r="F132" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="G132" s="5" t="inlineStr">
         <is>
           <t>metres</t>
         </is>
       </c>
-      <c r="H130" s="5" t="inlineStr">
+      <c r="H132" s="5" t="inlineStr">
         <is>
           <t>param:radius</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="12" t="n">
-        <v>59</v>
-      </c>
-      <c r="B131" s="12" t="inlineStr">
-        <is>
-          <t>Medicinal Munchies</t>
-        </is>
-      </c>
-      <c r="C131" s="12" t="inlineStr">
-        <is>
-          <t>Needs at least this much Injury</t>
-        </is>
-      </c>
-      <c r="D131" s="12" t="inlineStr"/>
-      <c r="E131" s="12" t="inlineStr"/>
-      <c r="F131" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="G131" s="12" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H131" s="12" t="inlineStr">
-        <is>
-          <t>param:threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="12" t="n">
-        <v>59</v>
-      </c>
-      <c r="B132" s="12" t="inlineStr">
-        <is>
-          <t>Medicinal Munchies</t>
-        </is>
-      </c>
-      <c r="C132" s="12" t="inlineStr">
-        <is>
-          <t>Injury removed</t>
-        </is>
-      </c>
-      <c r="D132" s="12" t="inlineStr"/>
-      <c r="E132" s="12" t="inlineStr"/>
-      <c r="F132" s="13" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G132" s="12" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H132" s="12" t="inlineStr">
-        <is>
-          <t>param:heal</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>Budget Checkpoint Flag</t>
+          <t>The Eternal Campfire</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
@@ -6967,399 +6919,37 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="12" t="n">
-        <v>61</v>
-      </c>
-      <c r="B134" s="12" t="inlineStr">
-        <is>
-          <t>Petrify Procrastination</t>
-        </is>
-      </c>
-      <c r="C134" s="12" t="inlineStr">
-        <is>
-          <t>Petrify build-up</t>
-        </is>
-      </c>
-      <c r="D134" s="12" t="inlineStr"/>
-      <c r="E134" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
+      <c r="A134" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>The Eternal Campfire</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>Stamina after the revive (at least)</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr"/>
+      <c r="E134" s="5" t="inlineStr"/>
       <c r="F134" s="13" t="n">
-        <v>-50</v>
-      </c>
-      <c r="G134" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H134" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="B135" s="5" t="inlineStr">
-        <is>
-          <t>Fine Print</t>
-        </is>
-      </c>
-      <c r="C135" s="5" t="inlineStr">
-        <is>
-          <t>Max stamina</t>
-        </is>
-      </c>
-      <c r="D135" s="5" t="inlineStr"/>
-      <c r="E135" s="5" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F135" s="13" t="n">
-        <v>35</v>
-      </c>
-      <c r="G135" s="5" t="inlineStr">
-        <is>
-          <t>stamina points</t>
-        </is>
-      </c>
-      <c r="H135" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>Fine Print</t>
-        </is>
-      </c>
-      <c r="C136" s="5" t="inlineStr">
-        <is>
-          <t>Curse when the sacrifice is made</t>
-        </is>
-      </c>
-      <c r="D136" s="5" t="inlineStr"/>
-      <c r="E136" s="5" t="inlineStr"/>
-      <c r="F136" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="G136" s="5" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="G134" s="5" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="H136" s="5" t="inlineStr">
-        <is>
-          <t>param:curse</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="B137" s="12" t="inlineStr">
-        <is>
-          <t>Scoutmaster</t>
-        </is>
-      </c>
-      <c r="C137" s="12" t="inlineStr">
-        <is>
-          <t>Climbing stamina cost (set, ignores other cards)</t>
-        </is>
-      </c>
-      <c r="D137" s="12" t="inlineStr"/>
-      <c r="E137" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F137" s="13" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G137" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H137" s="12" t="inlineStr">
-        <is>
-          <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="B138" s="12" t="inlineStr">
-        <is>
-          <t>Scoutmaster</t>
-        </is>
-      </c>
-      <c r="C138" s="12" t="inlineStr">
-        <is>
-          <t>Fall Injury (set, ignores other cards)</t>
-        </is>
-      </c>
-      <c r="D138" s="12" t="inlineStr"/>
-      <c r="E138" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F138" s="13" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G138" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H138" s="12" t="inlineStr">
-        <is>
-          <t>mod:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="B139" s="12" t="inlineStr">
-        <is>
-          <t>Scoutmaster</t>
-        </is>
-      </c>
-      <c r="C139" s="12" t="inlineStr">
-        <is>
-          <t>Sprint speed</t>
-        </is>
-      </c>
-      <c r="D139" s="12" t="inlineStr"/>
-      <c r="E139" s="12" t="inlineStr">
-        <is>
-          <t>You</t>
-        </is>
-      </c>
-      <c r="F139" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="G139" s="12" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H139" s="12" t="inlineStr">
-        <is>
-          <t>mod:2</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B140" s="5" t="inlineStr">
-        <is>
-          <t>The Eternal Campfire</t>
-        </is>
-      </c>
-      <c r="C140" s="5" t="inlineStr">
-        <is>
-          <t>Max stamina</t>
-        </is>
-      </c>
-      <c r="D140" s="5" t="inlineStr"/>
-      <c r="E140" s="5" t="inlineStr">
-        <is>
-          <t>You and teammates within 15 m</t>
-        </is>
-      </c>
-      <c r="F140" s="13" t="n">
-        <v>35</v>
-      </c>
-      <c r="G140" s="5" t="inlineStr">
-        <is>
-          <t>stamina points</t>
-        </is>
-      </c>
-      <c r="H140" s="5" t="inlineStr">
-        <is>
-          <t>mod:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B141" s="5" t="inlineStr">
-        <is>
-          <t>The Eternal Campfire</t>
-        </is>
-      </c>
-      <c r="C141" s="5" t="inlineStr">
-        <is>
-          <t>All Injury</t>
-        </is>
-      </c>
-      <c r="D141" s="5" t="inlineStr"/>
-      <c r="E141" s="5" t="inlineStr">
-        <is>
-          <t>You and teammates within 15 m</t>
-        </is>
-      </c>
-      <c r="F141" s="13" t="n">
-        <v>-60</v>
-      </c>
-      <c r="G141" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H141" s="5" t="inlineStr">
-        <is>
-          <t>mod:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B142" s="5" t="inlineStr">
-        <is>
-          <t>The Eternal Campfire</t>
-        </is>
-      </c>
-      <c r="C142" s="5" t="inlineStr">
-        <is>
-          <t>All negative status build-up</t>
-        </is>
-      </c>
-      <c r="D142" s="5" t="inlineStr"/>
-      <c r="E142" s="5" t="inlineStr">
-        <is>
-          <t>You and teammates within 15 m</t>
-        </is>
-      </c>
-      <c r="F142" s="13" t="n">
-        <v>-60</v>
-      </c>
-      <c r="G142" s="5" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="H142" s="5" t="inlineStr">
-        <is>
-          <t>mod:2</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B143" s="5" t="inlineStr">
-        <is>
-          <t>The Eternal Campfire</t>
-        </is>
-      </c>
-      <c r="C143" s="5" t="inlineStr">
-        <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="D143" s="5" t="inlineStr"/>
-      <c r="E143" s="5" t="inlineStr"/>
-      <c r="F143" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="G143" s="5" t="inlineStr">
-        <is>
-          <t>metres</t>
-        </is>
-      </c>
-      <c r="H143" s="5" t="inlineStr">
-        <is>
-          <t>param:radius</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B144" s="5" t="inlineStr">
-        <is>
-          <t>The Eternal Campfire</t>
-        </is>
-      </c>
-      <c r="C144" s="5" t="inlineStr">
-        <is>
-          <t>Injury after the revive</t>
-        </is>
-      </c>
-      <c r="D144" s="5" t="inlineStr"/>
-      <c r="E144" s="5" t="inlineStr"/>
-      <c r="F144" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="G144" s="5" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H144" s="5" t="inlineStr">
-        <is>
-          <t>param:injury</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B145" s="5" t="inlineStr">
-        <is>
-          <t>The Eternal Campfire</t>
-        </is>
-      </c>
-      <c r="C145" s="5" t="inlineStr">
-        <is>
-          <t>Stamina after the revive (at least)</t>
-        </is>
-      </c>
-      <c r="D145" s="5" t="inlineStr"/>
-      <c r="E145" s="5" t="inlineStr"/>
-      <c r="F145" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="G145" s="5" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="H145" s="5" t="inlineStr">
+      <c r="H134" s="5" t="inlineStr">
         <is>
           <t>param:stamina</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H145"/>
+  <autoFilter ref="A1:H134"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/design/editable/card-sheet.xlsx
+++ b/design/editable/card-sheet.xlsx
@@ -69,7 +69,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00E4D2F7"/>
       </patternFill>
     </fill>
     <fill>
@@ -79,7 +79,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E4D2F7"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -718,9 +718,9 @@
           <t>Mini Scout Cannon</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -776,9 +776,9 @@
           <t>Pitonless Pit Stop</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Hang still on a wall to recover 5 stamina per second.</t>
+          <t>Hang still on a wall to recover 7.5 stamina per second.</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -834,7 +834,7 @@
           <t>Energy Drink Overdose</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
@@ -865,9 +865,9 @@
           <t>Tendiefoot</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -896,9 +896,9 @@
           <t>Daddy Long Arms</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>Common</t>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -927,9 +927,9 @@
           <t>Cookie Addiction</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -958,9 +958,9 @@
           <t>Nic of Time</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1043,7 +1043,7 @@
           <t>Meditation</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
@@ -1074,7 +1074,7 @@
           <t>I'm getting Scoutmastered</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
@@ -1101,9 +1101,9 @@
           <t>Endurance Badge</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1217,7 +1217,7 @@
           <t>Antidote Enthusiast</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
@@ -1248,7 +1248,7 @@
           <t>ROOTS Survivor</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
@@ -1302,9 +1302,9 @@
           <t>Aloe</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -1333,9 +1333,9 @@
           <t>Heat Pack</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1364,9 +1364,9 @@
           <t>Fartberry Fitness</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -1395,9 +1395,9 @@
           <t>Bing Boing</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -1422,7 +1422,7 @@
           <t>TechTara</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
@@ -1449,9 +1449,9 @@
           <t>Walk It Off</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -1480,9 +1480,9 @@
           <t>Discount Cure-All</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -1507,9 +1507,9 @@
           <t>BingBong Parachute</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>Legendary</t>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -1561,9 +1561,9 @@
           <t>Book of Broken Bones</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -1588,9 +1588,9 @@
           <t>Mini Tenacity</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -1646,9 +1646,9 @@
           <t>Carry-On Only</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -1677,9 +1677,9 @@
           <t>Super Idol Hands</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>Common</t>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Held items weigh 75% less.</t>
+          <t>Held items weigh 65% less.</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr"/>
@@ -1704,7 +1704,7 @@
           <t>Cook It, Keep It</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
@@ -1735,7 +1735,7 @@
           <t>Cooked</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
@@ -1793,7 +1793,7 @@
           <t>Scoutmaster's Care Package</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C40" s="10" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
@@ -1820,7 +1820,7 @@
           <t>Clown Luggage Special</t>
         </is>
       </c>
-      <c r="C41" s="10" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
@@ -1847,9 +1847,9 @@
           <t>Rule Zero</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -1878,7 +1878,7 @@
           <t>First Aid Badge</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
@@ -1959,9 +1959,9 @@
           <t>Otto-Matic Clutch</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -2048,7 +2048,7 @@
           <t>Friendship Bugles</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr">
+      <c r="C49" s="10" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
@@ -2106,9 +2106,9 @@
           <t>Crown of Bad Decisions</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -2137,7 +2137,7 @@
           <t>Pandora's HotPocket</t>
         </is>
       </c>
-      <c r="C52" s="8" t="inlineStr">
+      <c r="C52" s="10" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
@@ -2164,9 +2164,9 @@
           <t>Bootleg Scoutmaster Bugle</t>
         </is>
       </c>
-      <c r="C53" s="10" t="inlineStr">
-        <is>
-          <t>Legendary</t>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -2195,9 +2195,9 @@
           <t>Big Lollipop Crash</t>
         </is>
       </c>
-      <c r="C54" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -2222,9 +2222,9 @@
           <t>Piton Payment Plan</t>
         </is>
       </c>
-      <c r="C55" s="9" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -2249,9 +2249,9 @@
           <t>Glass Scout Cannon</t>
         </is>
       </c>
-      <c r="C56" s="10" t="inlineStr">
-        <is>
-          <t>Legendary</t>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -2280,7 +2280,7 @@
           <t>Baggage Claim Escapee</t>
         </is>
       </c>
-      <c r="C57" s="8" t="inlineStr">
+      <c r="C57" s="10" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
@@ -2307,9 +2307,9 @@
           <t>Scout's Dishonor</t>
         </is>
       </c>
-      <c r="C58" s="10" t="inlineStr">
-        <is>
-          <t>Legendary</t>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -2365,9 +2365,9 @@
           <t>Medicinal Munchies</t>
         </is>
       </c>
-      <c r="C60" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -2392,7 +2392,7 @@
           <t>Budget Checkpoint Flag</t>
         </is>
       </c>
-      <c r="C61" s="10" t="inlineStr">
+      <c r="C61" s="8" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
@@ -2419,9 +2419,9 @@
           <t>Petrify Procrastination</t>
         </is>
       </c>
-      <c r="C62" s="9" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>Common</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -2446,9 +2446,9 @@
           <t>Fine Print</t>
         </is>
       </c>
-      <c r="C63" s="10" t="inlineStr">
-        <is>
-          <t>Legendary</t>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -2861,7 +2861,7 @@
       <c r="D9" s="5" t="inlineStr"/>
       <c r="E9" s="5" t="inlineStr"/>
       <c r="F9" s="13" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>-75</v>
+        <v>-65</v>
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>

--- a/design/editable/card-sheet.xlsx
+++ b/design/editable/card-sheet.xlsx
@@ -2338,9 +2338,9 @@
           <t>TSA</t>
         </is>
       </c>
-      <c r="C59" s="9" t="inlineStr">
-        <is>
-          <t>Rare</t>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>Mark food, items and luggage within 56 m, even through terrain.</t>
+          <t>Hold {key} to mark food / luggage / other items within 56 m, even through terrain.</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr"/>

--- a/design/editable/card-sheet.xlsx
+++ b/design/editable/card-sheet.xlsx
@@ -2520,7 +2520,7 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>You and scouts within 15 m: maximum stamina +35; Injury and status buildup -60%. Share 1 auto-revive per biome.</t>
+          <t>You and scouts within 15 m: maximum stamina +35; Injury and status buildup -60%. Share 1 auto-revive on death per biome.</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr"/>
